--- a/Result/checksun_type/齒輪箱.xlsx
+++ b/Result/checksun_type/齒輪箱.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1420.148</t>
+          <t>661.456</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-54.58</t>
+          <t>-54.96</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>661</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,62 +1024,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-7.76</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>18.21</t>
+          <t>18.08</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>20.91</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-15.51</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-125.43</t>
+          <t>-126.30</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>80440136.02098408</t>
+          <t>80349397.20736995</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>25449498.0</t>
+          <t>11765918.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>19541232.0</t>
+          <t>18163238.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>19684784.3</t>
+          <t>18465394.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>35922462.82</t>
+          <t>35922851.76</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-143552</t>
+          <t>-302155</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3460046.369419766</t>
+          <t>-3351368.343323668</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-2381824.93</v>
+        <v>-2753639.2</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-21.37</t>
+          <t>-22.03</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1182,32 +1182,32 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-0.8321185105289325</t>
+          <t>-5.144408598338474</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>13.81099438127996</t>
+          <t>-0.037516559435726</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>18.57264348824741</t>
+          <t>14.85780924490866</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1070.122</t>
+          <t>1420.148</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-53.56</t>
+          <t>-54.58</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,17 +1440,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>661</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-7.76</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>18.34</t>
+          <t>18.21</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>19.99</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.91</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-17.95</t>
+          <t>-15.51</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-124.44</t>
+          <t>-125.43</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>80440136.02098408</t>
+          <t>80349397.20736995</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>19499217.0</t>
+          <t>25449498.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>17442458.6</t>
+          <t>19541232.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>18972660.0</t>
+          <t>19684784.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>35662849.28</t>
+          <t>35922462.82</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1530201</t>
+          <t>-143552</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3656086.631100463</t>
+          <t>-3460046.369419766</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-3231694.37</v>
+        <v>-2381824.93</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-19.60</t>
+          <t>-21.37</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1613,27 +1613,27 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-0.8321185105289325</t>
+          <t>-5.144408598338474</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>13.81099438127996</t>
+          <t>-0.037516559435726</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>18.57264348824741</t>
+          <t>14.85780924490866</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>684.997</t>
+          <t>1070.122</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-11.28</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-52.93</t>
+          <t>-53.56</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>11.58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,67 +1871,67 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>661</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>11.41</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>18.42</t>
+          <t>18.34</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>21.07</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-23.75</t>
+          <t>-17.95</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-123.34</t>
+          <t>-124.44</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>80440136.02098408</t>
+          <t>80349397.20736995</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>12621655.0</t>
+          <t>19499217.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>16932916.8</t>
+          <t>17442458.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>19086589.9</t>
+          <t>18972660.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>35528913.86</t>
+          <t>35662849.28</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2153673</t>
+          <t>-1530201</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3733248.860586376</t>
+          <t>-3656086.631100463</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-3692845.8</v>
+        <v>-3231694.37</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-19.60</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2044,22 +2044,22 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-0.8321185105289325</t>
+          <t>-5.144408598338474</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>13.81099438127996</t>
+          <t>-0.037516559435726</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>18.57264348824741</t>
+          <t>14.85780924490866</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1182.366</t>
+          <t>684.997</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-11.28</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-53.94</t>
+          <t>-52.93</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>661</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-9.84</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.21</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>21.07</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-33.34</t>
+          <t>-23.75</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-121.96</t>
+          <t>-123.34</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>80440136.02098408</t>
+          <t>80349397.20736995</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>21479903.0</t>
+          <t>12621655.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>18792119.0</t>
+          <t>16932916.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>20020069.3</t>
+          <t>19086589.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>35721023.22</t>
+          <t>35528913.86</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1227950</t>
+          <t>-2153673</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3740594.870880427</t>
+          <t>-3733248.860586376</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-3482864.58</v>
+        <v>-3692845.8</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-20.26</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-0.8321185105289325</t>
+          <t>-5.144408598338474</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>13.81099438127996</t>
+          <t>-0.037516559435726</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>18.57264348824741</t>
+          <t>14.85780924490866</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1015.264</t>
+          <t>1182.366</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-53.31</t>
+          <t>-53.94</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>661</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,22 +2748,22 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-10.20</t>
+          <t>-9.84</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2773,37 +2773,37 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>18.41</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>20.67</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.16</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-39.99</t>
+          <t>-33.34</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-120.13</t>
+          <t>-121.96</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>80440136.02098408</t>
+          <t>80349397.20736995</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>18655887.0</t>
+          <t>21479903.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>18767550.0</t>
+          <t>18792119.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>20738141.5</t>
+          <t>20020069.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>35528196.68</t>
+          <t>35721023.22</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1970591</t>
+          <t>-1227950</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3787454.924619648</t>
+          <t>-3740594.870880427</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-4007601.37</v>
+        <v>-3482864.58</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-19.16</t>
+          <t>-20.26</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2906,27 +2906,27 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-0.8321185105289325</t>
+          <t>-5.144408598338474</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>13.81099438127996</t>
+          <t>-0.037516559435726</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>18.57264348824741</t>
+          <t>14.85780924490866</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>802.151</t>
+          <t>1015.264</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-12.87</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-52.93</t>
+          <t>-53.31</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,17 +3164,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>661</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,57 +3184,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.20</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>20.67</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.23</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-49.58</t>
+          <t>-39.99</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-118.12</t>
+          <t>-120.13</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>80440136.02098408</t>
+          <t>80349397.20736995</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>14955631.0</t>
+          <t>18655887.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19828336.6</t>
+          <t>18767550.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22758167.7</t>
+          <t>20738141.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>35603248.8</t>
+          <t>35528196.68</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-2929831</t>
+          <t>-1970591</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3747428.298009444</t>
+          <t>-3787454.924619648</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-4311523.6</v>
+        <v>-4007601.37</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-19.16</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3337,22 +3337,22 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-0.8321185105289325</t>
+          <t>-5.144408598338474</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>13.81099438127996</t>
+          <t>-0.037516559435726</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>18.57264348824741</t>
+          <t>14.85780924490866</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>907.562</t>
+          <t>802.151</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-20.12</t>
+          <t>-12.87</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-52.54</t>
+          <t>-52.93</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>661</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>21.38</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>22.03</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-62.33</t>
+          <t>-49.58</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-115.87</t>
+          <t>-118.12</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>80440136.02098408</t>
+          <t>80349397.20736995</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>16951508.0</t>
+          <t>14955631.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>20502861.4</t>
+          <t>19828336.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>25668210.7</t>
+          <t>22758167.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>35501077.48</t>
+          <t>35603248.8</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-5165349</t>
+          <t>-2929831</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3644865.515551496</t>
+          <t>-3747428.298009444</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-4195259.23</v>
+        <v>-4311523.6</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-17.84</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3768,27 +3768,27 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-0.8321185105289325</t>
+          <t>-5.144408598338474</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>13.81099438127996</t>
+          <t>-0.037516559435726</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>18.57264348824741</t>
+          <t>14.85780924490866</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1187.434</t>
+          <t>907.562</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-21.78</t>
+          <t>-20.12</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-53.05</t>
+          <t>-52.54</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>661</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.81</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-9.77</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.03</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-80.07</t>
+          <t>-62.33</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-113.40</t>
+          <t>-115.87</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>80440136.02098408</t>
+          <t>80349397.20736995</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>21917666.0</t>
+          <t>16951508.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>21240263.0</t>
+          <t>20502861.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>27153029.8</t>
+          <t>25668210.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>35429938.48</t>
+          <t>35501077.48</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-5912766</t>
+          <t>-5165349</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3544793.930954653</t>
+          <t>-3644865.515551496</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-4093180.55</v>
+        <v>-4195259.23</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-18.72</t>
+          <t>-17.84</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4199,27 +4199,27 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-0.8321185105289325</t>
+          <t>-5.144408598338474</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>13.81099438127996</t>
+          <t>-0.037516559435726</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>18.57264348824741</t>
+          <t>14.85780924490866</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1114.995</t>
+          <t>1187.434</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.6</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-20.06</t>
+          <t>-21.78</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-52.04</t>
+          <t>-53.05</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.06</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4457,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>661</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4477,57 +4477,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-9.77</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>19.62</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.44</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-96.89</t>
+          <t>-80.07</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-110.72</t>
+          <t>-113.40</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>80440136.02098408</t>
+          <t>80349397.20736995</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>21357058.0</t>
+          <t>21917666.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>21248019.6</t>
+          <t>21240263.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>26579090.9</t>
+          <t>27153029.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>35172853.9</t>
+          <t>35429938.48</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-5331071</t>
+          <t>-5912766</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3445087.272915496</t>
+          <t>-3544793.930954653</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-4333257.2</v>
+        <v>-4093180.55</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-18.72</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4630,22 +4630,22 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-0.8321185105289325</t>
+          <t>-5.144408598338474</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>13.81099438127996</t>
+          <t>-0.037516559435726</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>18.57264348824741</t>
+          <t>14.85780924490866</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1227.878</t>
+          <t>1114.995</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-8.4</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-20.20</t>
+          <t>-20.06</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-50.76</t>
+          <t>-52.04</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>12.06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>661</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4908,57 +4908,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.62</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>21.63</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-122.91</t>
+          <t>-96.89</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-108.12</t>
+          <t>-110.72</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>80440136.02098408</t>
+          <t>80349397.20736995</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>23959820.0</t>
+          <t>21357058.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>22708733.0</t>
+          <t>21248019.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>28457310.4</t>
+          <t>26579090.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>35140870.58</t>
+          <t>35172853.9</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-5748577</t>
+          <t>-5331071</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3283601.831445419</t>
+          <t>-3445087.272915496</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-4461399.52</v>
+        <v>-4333257.2</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-14.76</t>
+          <t>-16.96</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5061,22 +5061,22 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-0.8321185105289325</t>
+          <t>-5.144408598338474</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>13.81099438127996</t>
+          <t>-0.037516559435726</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>18.57264348824741</t>
+          <t>14.85780924490866</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>922.468</t>
+          <t>1227.878</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-11.48</t>
+          <t>-9.32</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-11.17</t>
+          <t>-20.20</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-49.36</t>
+          <t>-50.76</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>661</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-9.04</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-175.18</t>
+          <t>-122.91</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-105.62</t>
+          <t>-108.12</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>80440136.02098408</t>
+          <t>80349397.20736995</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>18328255.0</t>
+          <t>23959820.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>25687998.8</t>
+          <t>22708733.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>28918920.8</t>
+          <t>28457310.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>34772613.66</t>
+          <t>35140870.58</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-3230922</t>
+          <t>-5748577</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3069456.797810421</t>
+          <t>-3283601.831445419</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-4763991.63</v>
+        <v>-4461399.52</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-12.33</t>
+          <t>-14.76</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5492,22 +5492,22 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-0.8321185105289325</t>
+          <t>-5.144408598338474</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>13.81099438127996</t>
+          <t>-0.037516559435726</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>18.57264348824741</t>
+          <t>14.85780924490866</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/齒輪箱.xlsx
+++ b/Result/checksun_type/齒輪箱.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>661.456</t>
+          <t>2045.558</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-54.96</t>
+          <t>-55.85</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.94</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-7.15</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -1049,37 +1049,37 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>18.08</t>
+          <t>17.93</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-12.70</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-126.30</t>
+          <t>-127.17</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>80349397.20736995</t>
+          <t>80311871.97186147</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>11765918.0</t>
+          <t>36229606.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>18163238.2</t>
+          <t>21113178.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>18465394.1</t>
+          <t>19952648.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>35922851.76</t>
+          <t>36367077.28</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-302155</t>
+          <t>1160529</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3351368.343323668</t>
+          <t>-3006587.307202132</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-2753639.2</v>
+        <v>-1110291.61</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-22.03</t>
+          <t>-23.57</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1420.148</t>
+          <t>661.456</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-54.58</t>
+          <t>-54.96</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,62 +1455,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-7.76</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>18.21</t>
+          <t>18.08</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>20.91</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-15.51</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-125.43</t>
+          <t>-126.30</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>80349397.20736995</t>
+          <t>80311871.97186147</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>25449498.0</t>
+          <t>11765918.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>19541232.0</t>
+          <t>18163238.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>19684784.3</t>
+          <t>18465394.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>35922462.82</t>
+          <t>35922851.76</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-143552</t>
+          <t>-302155</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3460046.369419766</t>
+          <t>-3351368.343323668</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-2381824.93</v>
+        <v>-2753639.2</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-21.37</t>
+          <t>-22.03</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1070.122</t>
+          <t>1420.148</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-53.56</t>
+          <t>-54.58</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,17 +1871,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-7.76</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>18.34</t>
+          <t>18.21</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>19.99</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.91</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-17.95</t>
+          <t>-15.51</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-124.44</t>
+          <t>-125.43</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>80349397.20736995</t>
+          <t>80311871.97186147</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>19499217.0</t>
+          <t>25449498.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>17442458.6</t>
+          <t>19541232.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>18972660.0</t>
+          <t>19684784.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>35662849.28</t>
+          <t>35922462.82</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1530201</t>
+          <t>-143552</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3656086.631100463</t>
+          <t>-3460046.369419766</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-3231694.37</v>
+        <v>-2381824.93</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-19.60</t>
+          <t>-21.37</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>684.997</t>
+          <t>1070.122</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-11.28</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-52.93</t>
+          <t>-53.56</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>11.58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,67 +2302,67 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>11.41</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>18.42</t>
+          <t>18.34</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>21.07</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-23.75</t>
+          <t>-17.95</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-123.34</t>
+          <t>-124.44</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>80349397.20736995</t>
+          <t>80311871.97186147</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>12621655.0</t>
+          <t>19499217.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>16932916.8</t>
+          <t>17442458.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>19086589.9</t>
+          <t>18972660.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>35528913.86</t>
+          <t>35662849.28</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2153673</t>
+          <t>-1530201</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3733248.860586376</t>
+          <t>-3656086.631100463</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-3692845.8</v>
+        <v>-3231694.37</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-19.60</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1182.366</t>
+          <t>684.997</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-11.28</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-53.94</t>
+          <t>-52.93</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-9.84</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.21</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>21.07</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-33.34</t>
+          <t>-23.75</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-121.96</t>
+          <t>-123.34</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>80349397.20736995</t>
+          <t>80311871.97186147</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>21479903.0</t>
+          <t>12621655.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>18792119.0</t>
+          <t>16932916.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>20020069.3</t>
+          <t>19086589.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>35721023.22</t>
+          <t>35528913.86</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1227950</t>
+          <t>-2153673</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3740594.870880427</t>
+          <t>-3733248.860586376</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-3482864.58</v>
+        <v>-3692845.8</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-20.26</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1015.264</t>
+          <t>1182.366</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-53.31</t>
+          <t>-53.94</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,22 +3179,22 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-10.20</t>
+          <t>-9.84</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -3204,37 +3204,37 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>18.41</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>20.67</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.16</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-39.99</t>
+          <t>-33.34</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-120.13</t>
+          <t>-121.96</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>80349397.20736995</t>
+          <t>80311871.97186147</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>18655887.0</t>
+          <t>21479903.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>18767550.0</t>
+          <t>18792119.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>20738141.5</t>
+          <t>20020069.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>35528196.68</t>
+          <t>35721023.22</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1970591</t>
+          <t>-1227950</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3787454.924619648</t>
+          <t>-3740594.870880427</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-4007601.37</v>
+        <v>-3482864.58</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-19.16</t>
+          <t>-20.26</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>802.151</t>
+          <t>1015.264</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-12.87</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-52.93</t>
+          <t>-53.31</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,17 +3595,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3615,57 +3615,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.20</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>20.67</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.23</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-49.58</t>
+          <t>-39.99</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-118.12</t>
+          <t>-120.13</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>80349397.20736995</t>
+          <t>80311871.97186147</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>14955631.0</t>
+          <t>18655887.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>19828336.6</t>
+          <t>18767550.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>22758167.7</t>
+          <t>20738141.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>35603248.8</t>
+          <t>35528196.68</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2929831</t>
+          <t>-1970591</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3747428.298009444</t>
+          <t>-3787454.924619648</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-4311523.6</v>
+        <v>-4007601.37</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-19.16</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>907.562</t>
+          <t>802.151</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-20.12</t>
+          <t>-12.87</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-52.54</t>
+          <t>-52.93</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>21.38</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>22.03</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-62.33</t>
+          <t>-49.58</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-115.87</t>
+          <t>-118.12</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>80349397.20736995</t>
+          <t>80311871.97186147</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>16951508.0</t>
+          <t>14955631.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>20502861.4</t>
+          <t>19828336.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>25668210.7</t>
+          <t>22758167.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>35501077.48</t>
+          <t>35603248.8</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-5165349</t>
+          <t>-2929831</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3644865.515551496</t>
+          <t>-3747428.298009444</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-4195259.23</v>
+        <v>-4311523.6</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-17.84</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,12 +4279,12 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1187.434</t>
+          <t>907.562</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-7.49</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-21.78</t>
+          <t>-20.12</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-53.05</t>
+          <t>-52.54</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.81</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-9.77</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.03</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-80.07</t>
+          <t>-62.33</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-113.40</t>
+          <t>-115.87</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>80349397.20736995</t>
+          <t>80311871.97186147</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>21917666.0</t>
+          <t>16951508.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>21240263.0</t>
+          <t>20502861.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>27153029.8</t>
+          <t>25668210.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>35429938.48</t>
+          <t>35501077.48</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-5912766</t>
+          <t>-5165349</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3544793.930954653</t>
+          <t>-3644865.515551496</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-4093180.55</v>
+        <v>-4195259.23</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-18.72</t>
+          <t>-17.84</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4715,17 +4715,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1114.995</t>
+          <t>1187.434</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-20.06</t>
+          <t>-21.78</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-52.04</t>
+          <t>-53.05</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12.06</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4908,57 +4908,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-9.77</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>19.62</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.44</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-96.89</t>
+          <t>-80.07</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-110.72</t>
+          <t>-113.40</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>80349397.20736995</t>
+          <t>80311871.97186147</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>21357058.0</t>
+          <t>21917666.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>21248019.6</t>
+          <t>21240263.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>26579090.9</t>
+          <t>27153029.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>35172853.9</t>
+          <t>35429938.48</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-5331071</t>
+          <t>-5912766</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3445087.272915496</t>
+          <t>-3544793.930954653</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-4333257.2</v>
+        <v>-4093180.55</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-18.72</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1227.878</t>
+          <t>1114.995</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-9.32</t>
+          <t>-8.65</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-20.20</t>
+          <t>-20.06</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-50.76</t>
+          <t>-52.04</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>12.06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-9.29</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.62</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>21.63</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-122.91</t>
+          <t>-96.89</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-108.12</t>
+          <t>-110.72</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>80349397.20736995</t>
+          <t>80311871.97186147</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>23959820.0</t>
+          <t>21357058.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>22708733.0</t>
+          <t>21248019.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>28457310.4</t>
+          <t>26579090.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>35140870.58</t>
+          <t>35172853.9</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-5748577</t>
+          <t>-5331071</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3283601.831445419</t>
+          <t>-3445087.272915496</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-4461399.52</v>
+        <v>-4333257.2</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-14.76</t>
+          <t>-16.96</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/齒輪箱.xlsx
+++ b/Result/checksun_type/齒輪箱.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2045.558</t>
+          <t>732.465</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-55.85</t>
+          <t>-56.62</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>732</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-7.15</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.93</t>
+          <t>17.64</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.37</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-12.70</t>
+          <t>-12.62</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-127.17</t>
+          <t>-128.05</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>80311871.97186147</t>
+          <t>80223265.70533141</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>36229606.0</t>
+          <t>12546082.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>21113178.8</t>
+          <t>21098064.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>19952648.9</t>
+          <t>19015490.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>36367077.28</t>
+          <t>36438805.22</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1160529</t>
+          <t>2082573</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3006587.307202132</t>
+          <t>-2806874.691392164</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-1110291.61</v>
+        <v>-1708455.3</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-23.57</t>
+          <t>-24.89</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>661.456</t>
+          <t>2045.558</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-54.96</t>
+          <t>-55.85</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>732</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,22 +1455,22 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.94</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-7.15</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1480,37 +1480,37 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>18.08</t>
+          <t>17.93</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-12.70</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-126.30</t>
+          <t>-127.17</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>80311871.97186147</t>
+          <t>80223265.70533141</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>11765918.0</t>
+          <t>36229606.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>18163238.2</t>
+          <t>21113178.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>18465394.1</t>
+          <t>19952648.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>35922851.76</t>
+          <t>36367077.28</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-302155</t>
+          <t>1160529</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3351368.343323668</t>
+          <t>-3006587.307202132</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-2753639.2</v>
+        <v>-1110291.61</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-22.03</t>
+          <t>-23.57</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,12 +1628,12 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1420.148</t>
+          <t>661.456</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-54.58</t>
+          <t>-54.96</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>732</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1886,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-7.76</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>18.21</t>
+          <t>18.08</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>20.91</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-15.51</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-125.43</t>
+          <t>-126.30</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>80311871.97186147</t>
+          <t>80223265.70533141</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>25449498.0</t>
+          <t>11765918.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>19541232.0</t>
+          <t>18163238.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>19684784.3</t>
+          <t>18465394.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>35922462.82</t>
+          <t>35922851.76</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-143552</t>
+          <t>-302155</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3460046.369419766</t>
+          <t>-3351368.343323668</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-2381824.93</v>
+        <v>-2753639.2</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-21.37</t>
+          <t>-22.03</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1070.122</t>
+          <t>1420.148</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-53.56</t>
+          <t>-54.58</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,17 +2302,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>732</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2322,57 +2322,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-7.76</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>18.34</t>
+          <t>18.21</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>19.99</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.91</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-17.95</t>
+          <t>-15.51</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-124.44</t>
+          <t>-125.43</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>80311871.97186147</t>
+          <t>80223265.70533141</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>19499217.0</t>
+          <t>25449498.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>17442458.6</t>
+          <t>19541232.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>18972660.0</t>
+          <t>19684784.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>35662849.28</t>
+          <t>35922462.82</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1530201</t>
+          <t>-143552</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3656086.631100463</t>
+          <t>-3460046.369419766</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-3231694.37</v>
+        <v>-2381824.93</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-19.60</t>
+          <t>-21.37</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>684.997</t>
+          <t>1070.122</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-7.04</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-11.28</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-52.93</t>
+          <t>-53.56</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>11.58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,67 +2733,67 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>732</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>11.41</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>18.42</t>
+          <t>18.34</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>21.07</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-23.75</t>
+          <t>-17.95</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-123.34</t>
+          <t>-124.44</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>80311871.97186147</t>
+          <t>80223265.70533141</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>12621655.0</t>
+          <t>19499217.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>16932916.8</t>
+          <t>17442458.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>19086589.9</t>
+          <t>18972660.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>35528913.86</t>
+          <t>35662849.28</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-2153673</t>
+          <t>-1530201</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3733248.860586376</t>
+          <t>-3656086.631100463</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-3692845.8</v>
+        <v>-3231694.37</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-19.60</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1182.366</t>
+          <t>684.997</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-8.5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-11.28</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-53.94</t>
+          <t>-52.93</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>732</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-9.84</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.21</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>21.07</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-33.34</t>
+          <t>-23.75</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-121.96</t>
+          <t>-123.34</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>80311871.97186147</t>
+          <t>80223265.70533141</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>21479903.0</t>
+          <t>12621655.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>18792119.0</t>
+          <t>16932916.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>20020069.3</t>
+          <t>19086589.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>35721023.22</t>
+          <t>35528913.86</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1227950</t>
+          <t>-2153673</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3740594.870880427</t>
+          <t>-3733248.860586376</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-3482864.58</v>
+        <v>-3692845.8</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-20.26</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,17 +3352,17 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1015.264</t>
+          <t>1182.366</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>-6.16</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-53.31</t>
+          <t>-53.94</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3595,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>732</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,22 +3610,22 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-10.20</t>
+          <t>-9.84</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -3635,37 +3635,37 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>18.41</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>20.67</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.16</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-39.99</t>
+          <t>-33.34</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-120.13</t>
+          <t>-121.96</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>80311871.97186147</t>
+          <t>80223265.70533141</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>18655887.0</t>
+          <t>21479903.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>18767550.0</t>
+          <t>18792119.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>20738141.5</t>
+          <t>20020069.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>35528196.68</t>
+          <t>35721023.22</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1970591</t>
+          <t>-1227950</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3787454.924619648</t>
+          <t>-3740594.870880427</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-4007601.37</v>
+        <v>-3482864.58</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-19.16</t>
+          <t>-20.26</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,12 +3783,12 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>802.151</t>
+          <t>1015.264</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-12.87</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-52.93</t>
+          <t>-53.31</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,17 +4026,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>732</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4046,57 +4046,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.20</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>20.67</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.23</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-49.58</t>
+          <t>-39.99</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-118.12</t>
+          <t>-120.13</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>80311871.97186147</t>
+          <t>80223265.70533141</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>14955631.0</t>
+          <t>18655887.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>19828336.6</t>
+          <t>18767550.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>22758167.7</t>
+          <t>20738141.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>35603248.8</t>
+          <t>35528196.68</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2929831</t>
+          <t>-1970591</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3747428.298009444</t>
+          <t>-3787454.924619648</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-4311523.6</v>
+        <v>-4007601.37</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-19.16</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>907.562</t>
+          <t>802.151</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-7.49</t>
+          <t>-8.5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-20.12</t>
+          <t>-12.87</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-52.54</t>
+          <t>-52.93</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>732</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>21.38</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>22.03</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-62.33</t>
+          <t>-49.58</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-115.87</t>
+          <t>-118.12</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>80311871.97186147</t>
+          <t>80223265.70533141</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>16951508.0</t>
+          <t>14955631.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>20502861.4</t>
+          <t>19828336.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>25668210.7</t>
+          <t>22758167.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>35501077.48</t>
+          <t>35603248.8</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-5165349</t>
+          <t>-2929831</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3644865.515551496</t>
+          <t>-3747428.298009444</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-4195259.23</v>
+        <v>-4311523.6</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-17.84</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1187.434</t>
+          <t>907.562</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-21.78</t>
+          <t>-20.12</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-53.05</t>
+          <t>-52.54</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>732</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.81</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-9.77</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.03</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-80.07</t>
+          <t>-62.33</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-113.40</t>
+          <t>-115.87</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>80311871.97186147</t>
+          <t>80223265.70533141</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>21917666.0</t>
+          <t>16951508.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>21240263.0</t>
+          <t>20502861.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>27153029.8</t>
+          <t>25668210.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>35429938.48</t>
+          <t>35501077.48</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-5912766</t>
+          <t>-5165349</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3544793.930954653</t>
+          <t>-3644865.515551496</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-4093180.55</v>
+        <v>-4195259.23</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-18.72</t>
+          <t>-17.84</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5146,17 +5146,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1114.995</t>
+          <t>1187.434</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-8.65</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-20.06</t>
+          <t>-21.78</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-52.04</t>
+          <t>-53.05</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.06</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>732</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-9.29</t>
+          <t>-9.77</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>19.62</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.44</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-96.89</t>
+          <t>-80.07</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-110.72</t>
+          <t>-113.40</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>80311871.97186147</t>
+          <t>80223265.70533141</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>21357058.0</t>
+          <t>21917666.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>21248019.6</t>
+          <t>21240263.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>26579090.9</t>
+          <t>27153029.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>35172853.9</t>
+          <t>35429938.48</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-5331071</t>
+          <t>-5912766</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3445087.272915496</t>
+          <t>-3544793.930954653</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-4333257.2</v>
+        <v>-4093180.55</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-18.72</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/齒輪箱.xlsx
+++ b/Result/checksun_type/齒輪箱.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>732.465</t>
+          <t>286.781</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-56.62</t>
+          <t>-56.11</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>287</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.79</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-7.11</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.64</t>
+          <t>17.44</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.77</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>21.37</t>
+          <t>21.29</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-12.62</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-128.05</t>
+          <t>-128.75</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>80223265.70533141</t>
+          <t>80118566.06546763</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>12546082.0</t>
+          <t>4971344.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>21098064.2</t>
+          <t>18192489.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>19015490.5</t>
+          <t>17817474.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>36438805.22</t>
+          <t>36286025.3</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>2082573</t>
+          <t>375015</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2806874.691392164</t>
+          <t>-2783134.563325516</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-1708455.3</v>
+        <v>-2652563.86</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-24.89</t>
+          <t>-24.01</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2045.558</t>
+          <t>732.465</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-55.85</t>
+          <t>-56.62</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>287</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-7.15</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.93</t>
+          <t>17.64</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.37</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-12.70</t>
+          <t>-12.62</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-127.17</t>
+          <t>-128.05</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>80223265.70533141</t>
+          <t>80118566.06546763</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>36229606.0</t>
+          <t>12546082.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>21113178.8</t>
+          <t>21098064.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>19952648.9</t>
+          <t>19015490.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>36367077.28</t>
+          <t>36438805.22</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1160529</t>
+          <t>2082573</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3006587.307202132</t>
+          <t>-2806874.691392164</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-1110291.61</v>
+        <v>-1708455.3</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-23.57</t>
+          <t>-24.89</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1633,12 +1633,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>661.456</t>
+          <t>2045.558</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-54.96</t>
+          <t>-55.85</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>287</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,22 +1886,22 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.94</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-7.15</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1911,37 +1911,37 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>18.08</t>
+          <t>17.93</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-12.70</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-126.30</t>
+          <t>-127.17</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>80223265.70533141</t>
+          <t>80118566.06546763</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>11765918.0</t>
+          <t>36229606.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>18163238.2</t>
+          <t>21113178.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>18465394.1</t>
+          <t>19952648.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>35922851.76</t>
+          <t>36367077.28</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-302155</t>
+          <t>1160529</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3351368.343323668</t>
+          <t>-3006587.307202132</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-2753639.2</v>
+        <v>-1110291.61</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-22.03</t>
+          <t>-23.57</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1420.148</t>
+          <t>661.456</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-54.58</t>
+          <t>-54.96</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>287</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-7.76</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>18.21</t>
+          <t>18.08</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>20.91</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-15.51</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-125.43</t>
+          <t>-126.30</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>80223265.70533141</t>
+          <t>80118566.06546763</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>25449498.0</t>
+          <t>11765918.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>19541232.0</t>
+          <t>18163238.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>19684784.3</t>
+          <t>18465394.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>35922462.82</t>
+          <t>35922851.76</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-143552</t>
+          <t>-302155</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3460046.369419766</t>
+          <t>-3351368.343323668</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-2381824.93</v>
+        <v>-2753639.2</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-21.37</t>
+          <t>-22.03</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1070.122</t>
+          <t>1420.148</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-7.04</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-53.56</t>
+          <t>-54.58</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,17 +2733,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>287</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2753,57 +2753,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-7.76</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>18.34</t>
+          <t>18.21</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>19.99</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.91</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-17.95</t>
+          <t>-15.51</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-124.44</t>
+          <t>-125.43</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>80223265.70533141</t>
+          <t>80118566.06546763</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>19499217.0</t>
+          <t>25449498.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>17442458.6</t>
+          <t>19541232.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>18972660.0</t>
+          <t>19684784.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>35662849.28</t>
+          <t>35922462.82</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1530201</t>
+          <t>-143552</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3656086.631100463</t>
+          <t>-3460046.369419766</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-3231694.37</v>
+        <v>-2381824.93</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-19.60</t>
+          <t>-21.37</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>684.997</t>
+          <t>1070.122</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-8.5</t>
+          <t>-5.8</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-11.28</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-52.93</t>
+          <t>-53.56</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>11.58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,67 +3164,67 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>287</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>11.41</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>18.42</t>
+          <t>18.34</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>21.07</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-23.75</t>
+          <t>-17.95</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-123.34</t>
+          <t>-124.44</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>80223265.70533141</t>
+          <t>80118566.06546763</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>12621655.0</t>
+          <t>19499217.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>16932916.8</t>
+          <t>17442458.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>19086589.9</t>
+          <t>18972660.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>35528913.86</t>
+          <t>35662849.28</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-2153673</t>
+          <t>-1530201</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3733248.860586376</t>
+          <t>-3656086.631100463</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-3692845.8</v>
+        <v>-3231694.37</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-19.60</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1182.366</t>
+          <t>684.997</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.16</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-11.28</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-53.94</t>
+          <t>-52.93</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>287</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-9.84</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.21</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>21.07</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-33.34</t>
+          <t>-23.75</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-121.96</t>
+          <t>-123.34</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>80223265.70533141</t>
+          <t>80118566.06546763</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>21479903.0</t>
+          <t>12621655.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>18792119.0</t>
+          <t>16932916.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>20020069.3</t>
+          <t>19086589.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>35721023.22</t>
+          <t>35528913.86</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1227950</t>
+          <t>-2153673</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3740594.870880427</t>
+          <t>-3733248.860586376</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-3482864.58</v>
+        <v>-3692845.8</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-20.26</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1015.264</t>
+          <t>1182.366</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-53.31</t>
+          <t>-53.94</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>287</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4041,22 +4041,22 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-10.20</t>
+          <t>-9.84</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -4066,37 +4066,37 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>18.41</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>20.67</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.16</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-39.99</t>
+          <t>-33.34</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-120.13</t>
+          <t>-121.96</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>80223265.70533141</t>
+          <t>80118566.06546763</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>18655887.0</t>
+          <t>21479903.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>18767550.0</t>
+          <t>18792119.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20738141.5</t>
+          <t>20020069.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>35528196.68</t>
+          <t>35721023.22</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1970591</t>
+          <t>-1227950</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3787454.924619648</t>
+          <t>-3740594.870880427</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-4007601.37</v>
+        <v>-3482864.58</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-19.16</t>
+          <t>-20.26</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>802.151</t>
+          <t>1015.264</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.5</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-12.87</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-52.93</t>
+          <t>-53.31</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,17 +4457,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>287</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4477,57 +4477,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.20</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>20.67</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.23</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-49.58</t>
+          <t>-39.99</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-118.12</t>
+          <t>-120.13</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>80223265.70533141</t>
+          <t>80118566.06546763</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>14955631.0</t>
+          <t>18655887.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>19828336.6</t>
+          <t>18767550.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>22758167.7</t>
+          <t>20738141.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>35603248.8</t>
+          <t>35528196.68</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2929831</t>
+          <t>-1970591</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3747428.298009444</t>
+          <t>-3787454.924619648</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-4311523.6</v>
+        <v>-4007601.37</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-19.16</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>907.562</t>
+          <t>802.151</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-9.38</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-20.12</t>
+          <t>-12.87</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-52.54</t>
+          <t>-52.93</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>287</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>21.38</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>22.03</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-62.33</t>
+          <t>-49.58</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-115.87</t>
+          <t>-118.12</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>80223265.70533141</t>
+          <t>80118566.06546763</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>16951508.0</t>
+          <t>14955631.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>20502861.4</t>
+          <t>19828336.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>25668210.7</t>
+          <t>22758167.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>35501077.48</t>
+          <t>35603248.8</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-5165349</t>
+          <t>-2929831</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3644865.515551496</t>
+          <t>-3747428.298009444</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-4195259.23</v>
+        <v>-4311523.6</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-17.84</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1187.434</t>
+          <t>907.562</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-8.12</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-21.78</t>
+          <t>-20.12</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-53.05</t>
+          <t>-52.54</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>287</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.81</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-9.77</t>
+          <t>-10.18</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>21.38</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.03</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-80.07</t>
+          <t>-62.33</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-113.40</t>
+          <t>-115.87</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>80223265.70533141</t>
+          <t>80118566.06546763</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>21917666.0</t>
+          <t>16951508.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>21240263.0</t>
+          <t>20502861.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>27153029.8</t>
+          <t>25668210.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>35429938.48</t>
+          <t>35501077.48</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-5912766</t>
+          <t>-5165349</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3544793.930954653</t>
+          <t>-3644865.515551496</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-4093180.55</v>
+        <v>-4195259.23</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-18.72</t>
+          <t>-17.84</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5577,17 +5577,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/齒輪箱.xlsx
+++ b/Result/checksun_type/齒輪箱.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI12"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>286.781</t>
+          <t>801.363</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>-10.56</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-56.11</t>
+          <t>-57.12</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,17 +1014,17 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1029,57 +1034,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-7.11</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>18.57</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-9.69</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-128.75</t>
+          <t>-129.41</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,198 +1104,203 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>80118566.06546763</t>
+          <t>80032605.91594827</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>4971344.0</t>
+          <t>13526868.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>18192489.6</t>
+          <t>15807963.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>17817474.1</t>
+          <t>17674597.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>36286025.3</t>
+          <t>36309850.68</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>375015</t>
+          <t>-1866634</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2783134.563325516</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-2652563.86</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-2755800.238298532</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-2605461.450650116</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>13526868</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-24.01</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>-25.77</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
       <c r="BM2" t="inlineStr">
         <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
           <t>-5.144408598338474</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-0.037516559435726</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>14.85780924490866</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>15.74</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>7.87%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>-5.22%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>2580</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>再生能源類鑄件45.14%、其他鑄件30.51%、注塑機鑄件24.35% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>永冠-KY-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>17.05</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
         <is>
           <t>17.15</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>17.6</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>17.15</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>16.85</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>58.42</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 電機機械 - 鋼鑄鐵元件** 風力發電 - 齒輪箱、其他配件、風場開發** 能源元件 - 原材料</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1309,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>732.465</t>
+          <t>286.781</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-56.62</t>
+          <t>-56.11</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.79</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-7.11</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.64</t>
+          <t>17.44</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.77</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>21.37</t>
+          <t>21.29</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-12.62</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-128.05</t>
+          <t>-128.75</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,198 +1540,203 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>80118566.06546763</t>
+          <t>80032605.91594827</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>12546082.0</t>
+          <t>4971344.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>21098064.2</t>
+          <t>18192489.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>19015490.5</t>
+          <t>17817474.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>36438805.22</t>
+          <t>36286025.3</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>2082573</t>
+          <t>375015</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2806874.691392164</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-1708455.3</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-2783134.563325516</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-2652563.858958956</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>4971344</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>-24.89</t>
-        </is>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>-24.01</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
       <c r="BM3" t="inlineStr">
         <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
           <t>-5.144408598338474</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-0.037516559435726</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>14.85780924490866</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ3" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>0.29</t>
-        </is>
-      </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>15.74</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
           <t>7.87%</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>-5.22%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>2580</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>再生能源類鑄件45.14%、其他鑄件30.51%、注塑機鑄件24.35% (2024年)</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>永冠-KY-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>17.35</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>17.25</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>58.42</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 電機機械 - 鋼鑄鐵元件** 風力發電 - 齒輪箱、其他配件、風場開發** 能源元件 - 原材料</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2045.558</t>
+          <t>732.465</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-55.85</t>
+          <t>-56.62</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1886,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1891,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-7.15</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.93</t>
+          <t>17.64</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.37</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-12.70</t>
+          <t>-12.62</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-127.17</t>
+          <t>-128.05</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,198 +1976,203 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>80118566.06546763</t>
+          <t>80032605.91594827</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>36229606.0</t>
+          <t>12546082.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>21113178.8</t>
+          <t>21098064.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>19952648.9</t>
+          <t>19015490.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>36367077.28</t>
+          <t>36438805.22</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1160529</t>
+          <t>2082573</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3006587.307202132</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-1110291.61</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-2806874.691392164</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-1708455.304437336</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>12546082</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>-23.57</t>
-        </is>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>-24.89</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
       <c r="BM4" t="inlineStr">
         <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
           <t>-5.144408598338474</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-0.037516559435726</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>14.85780924490866</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>15.74</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
           <t>7.87%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>-5.22%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>2580</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>再生能源類鑄件45.14%、其他鑄件30.51%、注塑機鑄件24.35% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>永冠-KY-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>17.75</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>17.35</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>17.0</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>17.35</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>17.05</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>58.42</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 電機機械 - 鋼鑄鐵元件** 風力發電 - 齒輪箱、其他配件、風場開發** 能源元件 - 原材料</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2171,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>661.456</t>
+          <t>2045.558</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-54.96</t>
+          <t>-55.85</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,22 +2337,22 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.94</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-7.15</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2342,37 +2362,37 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>18.08</t>
+          <t>17.93</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-12.70</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-126.30</t>
+          <t>-127.17</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,198 +2412,203 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>80118566.06546763</t>
+          <t>80032605.91594827</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>11765918.0</t>
+          <t>36229606.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>18163238.2</t>
+          <t>21113178.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>18465394.1</t>
+          <t>19952648.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>35922851.76</t>
+          <t>36367077.28</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-302155</t>
+          <t>1160529</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3351368.343323668</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>-2753639.2</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-3006587.307202132</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-1110291.608533688</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>36229606</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-22.03</t>
-        </is>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>-23.57</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
       <c r="BM5" t="inlineStr">
         <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
           <t>-5.144408598338474</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-0.037516559435726</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>14.85780924490866</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
           <t>0.30</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BT5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>15.74</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
           <t>7.87%</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>-5.22%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>2580</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>再生能源類鑄件45.14%、其他鑄件30.51%、注塑機鑄件24.35% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>永冠-KY-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>17.85</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>17.35</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>58.42</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 電機機械 - 鋼鑄鐵元件** 風力發電 - 齒輪箱、其他配件、風場開發** 能源元件 - 原材料</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2602,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1420.148</t>
+          <t>661.456</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-54.58</t>
+          <t>-54.96</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2773,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-7.76</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>18.21</t>
+          <t>18.08</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>20.91</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-15.51</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-125.43</t>
+          <t>-126.30</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,198 +2848,203 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>80118566.06546763</t>
+          <t>80032605.91594827</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>25449498.0</t>
+          <t>11765918.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>19541232.0</t>
+          <t>18163238.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>19684784.3</t>
+          <t>18465394.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>35922462.82</t>
+          <t>35922851.76</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-143552</t>
+          <t>-302155</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3460046.369419766</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>-2381824.93</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-3351368.343323668</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-2753639.199795127</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>11765918</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>-21.37</t>
-        </is>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
+          <t>-22.03</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BL6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
       <c r="BM6" t="inlineStr">
         <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
           <t>-5.144408598338474</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-0.037516559435726</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>14.85780924490866</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>15.74</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
           <t>7.87%</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>-5.22%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>2580</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>再生能源類鑄件45.14%、其他鑄件30.51%、注塑機鑄件24.35% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>永冠-KY-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>18.1</t>
-        </is>
-      </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>17.7</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>58.42</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 電機機械 - 鋼鑄鐵元件** 風力發電 - 齒輪箱、其他配件、風場開發** 能源元件 - 原材料</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3033,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1070.122</t>
+          <t>1420.148</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.8</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-53.56</t>
+          <t>-54.58</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,17 +3194,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-7.76</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>18.34</t>
+          <t>18.21</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>19.99</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.91</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-17.95</t>
+          <t>-15.51</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-124.44</t>
+          <t>-125.43</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,198 +3284,203 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>80118566.06546763</t>
+          <t>80032605.91594827</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>19499217.0</t>
+          <t>25449498.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>17442458.6</t>
+          <t>19541232.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>18972660.0</t>
+          <t>19684784.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>35662849.28</t>
+          <t>35922462.82</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1530201</t>
+          <t>-143552</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3656086.631100463</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>-3231694.37</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-3460046.369419766</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-2381824.930175934</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>25449498</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>-19.60</t>
-        </is>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
+          <t>-21.37</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
       <c r="BM7" t="inlineStr">
         <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
           <t>-5.144408598338474</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-0.037516559435726</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>14.85780924490866</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
           <t>0.31</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>15.74</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
           <t>7.87%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>-5.22%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>2580</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>再生能源類鑄件45.14%、其他鑄件30.51%、注塑機鑄件24.35% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>永冠-KY-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>18.5</t>
-        </is>
-      </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
+          <t>17.85</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>58.42</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 電機機械 - 鋼鑄鐵元件** 風力發電 - 齒輪箱、其他配件、風場開發** 能源元件 - 原材料</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3464,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>684.997</t>
+          <t>1070.122</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-8.31</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-11.28</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-52.93</t>
+          <t>-53.56</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>11.58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,67 +3630,67 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>11.41</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.42</t>
+          <t>18.34</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>21.07</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-23.75</t>
+          <t>-17.95</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3665,7 +3700,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-123.34</t>
+          <t>-124.44</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,198 +3720,203 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>80118566.06546763</t>
+          <t>80032605.91594827</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>12621655.0</t>
+          <t>19499217.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>16932916.8</t>
+          <t>17442458.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>19086589.9</t>
+          <t>18972660.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>35528913.86</t>
+          <t>35662849.28</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2153673</t>
+          <t>-1530201</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3733248.860586376</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-3692845.8</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-3656086.631100463</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-3231694.368927941</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>19499217</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>-18.50</t>
-        </is>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
+          <t>-19.60</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
       <c r="BM8" t="inlineStr">
         <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
           <t>-5.144408598338474</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-0.037516559435726</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>14.85780924490866</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>15.74</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
           <t>7.87%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>-5.22%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>2580</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>再生能源類鑄件45.14%、其他鑄件30.51%、注塑機鑄件24.35% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>永冠-KY-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>18.15</t>
-        </is>
-      </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
+          <t>18.25</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>58.42</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 電機機械 - 鋼鑄鐵元件** 風力發電 - 齒輪箱、其他配件、風場開發** 能源元件 - 原材料</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1182.366</t>
+          <t>684.997</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-9.79</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-11.28</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-53.94</t>
+          <t>-52.93</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-9.84</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.21</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>21.07</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-33.34</t>
+          <t>-23.75</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-121.96</t>
+          <t>-123.34</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,198 +4156,203 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>80118566.06546763</t>
+          <t>80032605.91594827</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>21479903.0</t>
+          <t>12621655.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>18792119.0</t>
+          <t>16932916.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20020069.3</t>
+          <t>19086589.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>35721023.22</t>
+          <t>35528913.86</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1227950</t>
+          <t>-2153673</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3740594.870880427</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-3482864.58</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-3733248.860586376</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-3692845.803969096</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>12621655</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-20.26</t>
-        </is>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>-18.50</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
       <c r="BM9" t="inlineStr">
         <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
           <t>-5.144408598338474</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-0.037516559435726</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>14.85780924490866</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>15.74</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
           <t>7.87%</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>-5.22%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>2580</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>再生能源類鑄件45.14%、其他鑄件30.51%、注塑機鑄件24.35% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>永冠-KY-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>18.35</t>
-        </is>
-      </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>58.42</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 電機機械 - 鋼鑄鐵元件** 風力發電 - 齒輪箱、其他配件、風場開發** 能源元件 - 原材料</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1015.264</t>
+          <t>1182.366</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-7.42</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-53.31</t>
+          <t>-53.94</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4472,22 +4517,22 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-10.20</t>
+          <t>-9.84</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -4497,37 +4542,37 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>18.41</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>20.67</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.16</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-39.99</t>
+          <t>-33.34</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-120.13</t>
+          <t>-121.96</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,198 +4592,203 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>80118566.06546763</t>
+          <t>80032605.91594827</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>18655887.0</t>
+          <t>21479903.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>18767550.0</t>
+          <t>18792119.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>20738141.5</t>
+          <t>20020069.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>35528196.68</t>
+          <t>35721023.22</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1970591</t>
+          <t>-1227950</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3787454.924619648</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-4007601.37</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-3740594.870880427</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-3482864.575314708</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>21479903</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-19.16</t>
-        </is>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>-20.26</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
       <c r="BM10" t="inlineStr">
         <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
           <t>-5.144408598338474</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-0.037516559435726</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>14.85780924490866</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ10" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>0.31</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BT10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
           <t>15.74</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
           <t>7.87%</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>-5.22%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
+          <t>2580</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
           <t>再生能源類鑄件45.14%、其他鑄件30.51%、注塑機鑄件24.35% (2024年)</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>永冠-KY-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>18.1</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>58.42</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 電機機械 - 鋼鑄鐵元件** 風力發電 - 齒輪箱、其他配件、風場開發** 能源元件 - 原材料</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4762,7 +4812,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>802.151</t>
+          <t>1015.264</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-8.9</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-12.87</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-52.93</t>
+          <t>-53.31</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,17 +4938,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4908,57 +4958,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.20</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>20.67</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.23</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-49.58</t>
+          <t>-39.99</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-118.12</t>
+          <t>-120.13</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,198 +5028,203 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>80118566.06546763</t>
+          <t>80032605.91594827</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>14955631.0</t>
+          <t>18655887.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>19828336.6</t>
+          <t>18767550.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>22758167.7</t>
+          <t>20738141.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>35603248.8</t>
+          <t>35528196.68</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2929831</t>
+          <t>-1970591</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3747428.298009444</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-4311523.6</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-3787454.924619648</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-4007601.37097577</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>18655887</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-18.50</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>-19.16</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
       <c r="BM11" t="inlineStr">
         <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
           <t>-5.144408598338474</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-0.037516559435726</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>14.85780924490866</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>15.74</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
           <t>7.87%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>-5.22%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>2580</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>再生能源類鑄件45.14%、其他鑄件30.51%、注塑機鑄件24.35% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>永冠-KY-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>18.65</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
+          <t>18.35</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>58.42</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 電機機械 - 鋼鑄鐵元件** 風力發電 - 齒輪箱、其他配件、風場開發** 能源元件 - 原材料</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>907.562</t>
+          <t>802.151</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-8.12</t>
+          <t>-9.79</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-20.12</t>
+          <t>-12.87</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-52.54</t>
+          <t>-52.93</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>801</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>10.81</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-10.18</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>18.76</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>21.38</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>22.03</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-62.33</t>
+          <t>-49.58</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-115.87</t>
+          <t>-118.12</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,198 +5464,203 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>80118566.06546763</t>
+          <t>80032605.91594827</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>16951508.0</t>
+          <t>14955631.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>20502861.4</t>
+          <t>19828336.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>25668210.7</t>
+          <t>22758167.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>35501077.48</t>
+          <t>35603248.8</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-5165349</t>
+          <t>-2929831</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3644865.515551496</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-4195259.23</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-3747428.298009444</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-4311523.60152816</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>14955631</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-17.84</t>
-        </is>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
+          <t>-18.50</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
       <c r="BM12" t="inlineStr">
         <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
           <t>-5.144408598338474</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-0.037516559435726</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>14.85780924490866</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ12" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>0.32</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BT12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
           <t>15.74</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BV12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
           <t>7.87%</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>-5.22%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>40.81</t>
-        </is>
-      </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
+          <t>2580</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
           <t>再生能源類鑄件45.14%、其他鑄件30.51%、注塑機鑄件24.35% (2024年)</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>永冠-KY-電機機械-上市</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>18.5</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>18.65</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>58.42</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 電機機械 - 鋼鑄鐵元件** 風力發電 - 齒輪箱、其他配件、風場開發** 能源元件 - 原材料</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/齒輪箱.xlsx
+++ b/Result/checksun_type/齒輪箱.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>801.363</t>
+          <t>659.489</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-10.56</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-57.12</t>
+          <t>-56.36</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>659</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-6.94</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.91</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>18.57</t>
+          <t>18.41</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-129.41</t>
+          <t>-129.81</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>80032605.91594827</t>
+          <t>79942030.28909613</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>13526868.0</t>
+          <t>11267596.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>15807963.6</t>
+          <t>15708299.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>17674597.8</t>
+          <t>16935768.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>36309850.68</t>
+          <t>36089158.58</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1866634</t>
+          <t>-1227469</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2755800.238298532</t>
+          <t>-2743646.144493785</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-2605461.450650116</t>
+          <t>-2676798.628567677</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>13526868</v>
+        <v>11267596</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-25.77</t>
+          <t>-24.45</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>16.7</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>17.15</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>16.7</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>16.85</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>286.781</t>
+          <t>801.363</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>-10.56</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-56.11</t>
+          <t>-57.12</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>659</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>13.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1470,57 +1470,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-7.11</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>18.57</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-9.69</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-128.75</t>
+          <t>-129.41</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>80032605.91594827</t>
+          <t>79942030.28909613</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4971344.0</t>
+          <t>13526868.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>18192489.6</t>
+          <t>15807963.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>17817474.1</t>
+          <t>17674597.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>36286025.3</t>
+          <t>36309850.68</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>375015</t>
+          <t>-1866634</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2783134.563325516</t>
+          <t>-2755800.238298532</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-2652563.858958956</t>
+          <t>-2605461.450650116</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>4971344</v>
+        <v>13526868</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-24.01</t>
+          <t>-25.77</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,17 +1643,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>17.05</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>17.15</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>17.6</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>732.465</t>
+          <t>286.781</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-56.62</t>
+          <t>-56.11</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>659</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.79</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-7.11</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.64</t>
+          <t>17.44</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.77</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>21.37</t>
+          <t>21.29</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-12.62</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-128.05</t>
+          <t>-128.75</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>80032605.91594827</t>
+          <t>79942030.28909613</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>12546082.0</t>
+          <t>4971344.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>21098064.2</t>
+          <t>18192489.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>19015490.5</t>
+          <t>17817474.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>36438805.22</t>
+          <t>36286025.3</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>2082573</t>
+          <t>375015</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-2806874.691392164</t>
+          <t>-2783134.563325516</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1708455.304437336</t>
+          <t>-2652563.858958956</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>12546082</v>
+        <v>4971344</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-24.89</t>
+          <t>-24.01</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2045.558</t>
+          <t>732.465</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-55.85</t>
+          <t>-56.62</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>659</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-7.15</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.93</t>
+          <t>17.64</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.37</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-12.70</t>
+          <t>-12.62</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-127.17</t>
+          <t>-128.05</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>80032605.91594827</t>
+          <t>79942030.28909613</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>36229606.0</t>
+          <t>12546082.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>21113178.8</t>
+          <t>21098064.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>19952648.9</t>
+          <t>19015490.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>36367077.28</t>
+          <t>36438805.22</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1160529</t>
+          <t>2082573</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3006587.307202132</t>
+          <t>-2806874.691392164</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1110291.608533688</t>
+          <t>-1708455.304437336</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>36229606</v>
+        <v>12546082</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-23.57</t>
+          <t>-24.89</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,12 +2580,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>661.456</t>
+          <t>2045.558</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-54.96</t>
+          <t>-55.85</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>659</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2773,22 +2773,22 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.94</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-7.15</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2798,37 +2798,37 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>18.08</t>
+          <t>17.93</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-12.70</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-126.30</t>
+          <t>-127.17</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>80032605.91594827</t>
+          <t>79942030.28909613</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>11765918.0</t>
+          <t>36229606.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>18163238.2</t>
+          <t>21113178.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>18465394.1</t>
+          <t>19952648.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>35922851.76</t>
+          <t>36367077.28</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-302155</t>
+          <t>1160529</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3351368.343323668</t>
+          <t>-3006587.307202132</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-2753639.199795127</t>
+          <t>-1110291.608533688</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>11765918</v>
+        <v>36229606</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-22.03</t>
+          <t>-23.57</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1420.148</t>
+          <t>661.456</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-54.58</t>
+          <t>-54.96</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>659</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,62 +3209,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-7.76</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>18.21</t>
+          <t>18.08</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>20.91</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-15.51</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-125.43</t>
+          <t>-126.30</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>80032605.91594827</t>
+          <t>79942030.28909613</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>25449498.0</t>
+          <t>11765918.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19541232.0</t>
+          <t>18163238.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>19684784.3</t>
+          <t>18465394.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>35922462.82</t>
+          <t>35922851.76</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-143552</t>
+          <t>-302155</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3460046.369419766</t>
+          <t>-3351368.343323668</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-2381824.930175934</t>
+          <t>-2753639.199795127</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>25449498</v>
+        <v>11765918</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-21.37</t>
+          <t>-22.03</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1070.122</t>
+          <t>1420.148</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-8.31</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-53.56</t>
+          <t>-54.58</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,17 +3630,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>659</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3650,57 +3650,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-7.76</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.34</t>
+          <t>18.21</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>19.99</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.91</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-17.95</t>
+          <t>-15.51</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-124.44</t>
+          <t>-125.43</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>80032605.91594827</t>
+          <t>79942030.28909613</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>19499217.0</t>
+          <t>25449498.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>17442458.6</t>
+          <t>19541232.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>18972660.0</t>
+          <t>19684784.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>35662849.28</t>
+          <t>35922462.82</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1530201</t>
+          <t>-143552</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3656086.631100463</t>
+          <t>-3460046.369419766</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-3231694.368927941</t>
+          <t>-2381824.930175934</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>19499217</v>
+        <v>25449498</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-19.60</t>
+          <t>-21.37</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>684.997</t>
+          <t>1070.122</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-9.79</t>
+          <t>-6.41</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-11.28</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-52.93</t>
+          <t>-53.56</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>11.58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,67 +4066,67 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>659</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>11.41</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.42</t>
+          <t>18.34</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>21.07</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-23.75</t>
+          <t>-17.95</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-123.34</t>
+          <t>-124.44</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>80032605.91594827</t>
+          <t>79942030.28909613</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>12621655.0</t>
+          <t>19499217.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>16932916.8</t>
+          <t>17442458.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>19086589.9</t>
+          <t>18972660.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>35528913.86</t>
+          <t>35662849.28</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2153673</t>
+          <t>-1530201</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3733248.860586376</t>
+          <t>-3656086.631100463</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-3692845.803969096</t>
+          <t>-3231694.368927941</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>12621655</v>
+        <v>19499217</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-19.60</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1182.366</t>
+          <t>684.997</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-7.42</t>
+          <t>-7.87</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-11.28</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-53.94</t>
+          <t>-52.93</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>659</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-9.84</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.21</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>21.07</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-33.34</t>
+          <t>-23.75</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-121.96</t>
+          <t>-123.34</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>80032605.91594827</t>
+          <t>79942030.28909613</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>21479903.0</t>
+          <t>12621655.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>18792119.0</t>
+          <t>16932916.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>20020069.3</t>
+          <t>19086589.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>35721023.22</t>
+          <t>35528913.86</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1227950</t>
+          <t>-2153673</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3740594.870880427</t>
+          <t>-3733248.860586376</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-3482864.575314708</t>
+          <t>-3692845.803969096</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>21479903</v>
+        <v>12621655</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-20.26</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1015.264</t>
+          <t>1182.366</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-8.9</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-53.31</t>
+          <t>-53.94</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>659</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4953,22 +4953,22 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-10.20</t>
+          <t>-9.84</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -4978,37 +4978,37 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>18.41</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>20.67</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.16</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-39.99</t>
+          <t>-33.34</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-120.13</t>
+          <t>-121.96</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>80032605.91594827</t>
+          <t>79942030.28909613</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>18655887.0</t>
+          <t>21479903.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>18767550.0</t>
+          <t>18792119.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>20738141.5</t>
+          <t>20020069.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>35528196.68</t>
+          <t>35721023.22</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1970591</t>
+          <t>-1227950</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3787454.924619648</t>
+          <t>-3740594.870880427</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-4007601.37097577</t>
+          <t>-3482864.575314708</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>18655887</v>
+        <v>21479903</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-19.16</t>
+          <t>-20.26</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>802.151</t>
+          <t>1015.264</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-9.79</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-12.87</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-52.93</t>
+          <t>-53.31</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,17 +5374,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>659</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5394,57 +5394,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.20</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>20.95</t>
+          <t>20.67</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.23</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-49.58</t>
+          <t>-39.99</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-118.12</t>
+          <t>-120.13</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>80032605.91594827</t>
+          <t>79942030.28909613</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>14955631.0</t>
+          <t>18655887.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>19828336.6</t>
+          <t>18767550.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>22758167.7</t>
+          <t>20738141.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>35603248.8</t>
+          <t>35528196.68</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2929831</t>
+          <t>-1970591</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3747428.298009444</t>
+          <t>-3787454.924619648</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-4311523.60152816</t>
+          <t>-4007601.37097577</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>14955631</v>
+        <v>18655887</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-19.16</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/齒輪箱.xlsx
+++ b/Result/checksun_type/齒輪箱.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>659.489</t>
+          <t>492.348</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-35.03</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-56.36</t>
+          <t>-56.49</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,17 +1019,17 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>492</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -1039,52 +1039,52 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-9.91</t>
+          <t>-10.33</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>18.26</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>20.36</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-129.81</t>
+          <t>-129.97</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>79942030.28909613</t>
+          <t>79845726.99283668</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>11267596.0</t>
+          <t>8481553.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>15708299.2</t>
+          <t>10158688.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>16935768.7</t>
+          <t>15635933.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>36089158.58</t>
+          <t>36006631.54</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1227469</t>
+          <t>-5477245</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2743646.144493785</t>
+          <t>-2762895.647247938</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-2676798.628567677</t>
+          <t>-2868767.912395775</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>11267596</v>
+        <v>8481553</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-24.45</t>
+          <t>-24.67</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>801.363</t>
+          <t>659.489</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-10.56</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-57.12</t>
+          <t>-56.36</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1455,72 +1455,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>492</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-6.94</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.91</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>18.57</t>
+          <t>18.41</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-129.41</t>
+          <t>-129.81</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>79942030.28909613</t>
+          <t>79845726.99283668</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>13526868.0</t>
+          <t>11267596.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>15807963.6</t>
+          <t>15708299.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>17674597.8</t>
+          <t>16935768.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>36309850.68</t>
+          <t>36089158.58</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1866634</t>
+          <t>-1227469</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2755800.238298532</t>
+          <t>-2743646.144493785</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-2605461.450650116</t>
+          <t>-2676798.628567677</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>13526868</v>
+        <v>11267596</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-25.77</t>
+          <t>-24.45</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>16.7</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>17.15</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>16.7</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>16.85</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>286.781</t>
+          <t>801.363</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>-10.56</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-56.11</t>
+          <t>-57.12</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1891,12 +1891,12 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>492</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>13.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1906,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-7.11</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>18.57</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-9.69</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-128.75</t>
+          <t>-129.41</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>79942030.28909613</t>
+          <t>79845726.99283668</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4971344.0</t>
+          <t>13526868.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>18192489.6</t>
+          <t>15807963.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>17817474.1</t>
+          <t>17674597.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>36286025.3</t>
+          <t>36309850.68</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>375015</t>
+          <t>-1866634</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-2783134.563325516</t>
+          <t>-2755800.238298532</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-2652563.858958956</t>
+          <t>-2605461.450650116</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>4971344</v>
+        <v>13526868</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-24.01</t>
+          <t>-25.77</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>17.05</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>17.15</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>17.6</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>732.465</t>
+          <t>286.781</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-56.62</t>
+          <t>-56.11</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2327,72 +2327,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>492</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.79</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-7.11</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.64</t>
+          <t>17.44</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.77</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>21.37</t>
+          <t>21.29</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-12.62</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-128.05</t>
+          <t>-128.75</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>79942030.28909613</t>
+          <t>79845726.99283668</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>12546082.0</t>
+          <t>4971344.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>21098064.2</t>
+          <t>18192489.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>19015490.5</t>
+          <t>17817474.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>36438805.22</t>
+          <t>36286025.3</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>2082573</t>
+          <t>375015</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-2806874.691392164</t>
+          <t>-2783134.563325516</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1708455.304437336</t>
+          <t>-2652563.858958956</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>12546082</v>
+        <v>4971344</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-24.89</t>
+          <t>-24.01</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2045.558</t>
+          <t>732.465</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-55.85</t>
+          <t>-56.62</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>492</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2778,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-7.15</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.93</t>
+          <t>17.64</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.37</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-12.70</t>
+          <t>-12.62</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-127.17</t>
+          <t>-128.05</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>79942030.28909613</t>
+          <t>79845726.99283668</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>36229606.0</t>
+          <t>12546082.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>21113178.8</t>
+          <t>21098064.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>19952648.9</t>
+          <t>19015490.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>36367077.28</t>
+          <t>36438805.22</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1160529</t>
+          <t>2082573</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3006587.307202132</t>
+          <t>-2806874.691392164</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1110291.608533688</t>
+          <t>-1708455.304437336</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>36229606</v>
+        <v>12546082</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-23.57</t>
+          <t>-24.89</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>661.456</t>
+          <t>2045.558</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-54.96</t>
+          <t>-55.85</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>492</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,22 +3209,22 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.94</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-7.15</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -3234,37 +3234,37 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>18.08</t>
+          <t>17.93</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-12.70</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-126.30</t>
+          <t>-127.17</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>79942030.28909613</t>
+          <t>79845726.99283668</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>11765918.0</t>
+          <t>36229606.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>18163238.2</t>
+          <t>21113178.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>18465394.1</t>
+          <t>19952648.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>35922851.76</t>
+          <t>36367077.28</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-302155</t>
+          <t>1160529</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3351368.343323668</t>
+          <t>-3006587.307202132</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-2753639.199795127</t>
+          <t>-1110291.608533688</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>11765918</v>
+        <v>36229606</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-22.03</t>
+          <t>-23.57</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1420.148</t>
+          <t>661.456</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-54.58</t>
+          <t>-54.96</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>492</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,62 +3645,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-7.76</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.21</t>
+          <t>18.08</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>20.91</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-15.51</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-125.43</t>
+          <t>-126.30</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>79942030.28909613</t>
+          <t>79845726.99283668</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>25449498.0</t>
+          <t>11765918.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>19541232.0</t>
+          <t>18163238.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>19684784.3</t>
+          <t>18465394.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>35922462.82</t>
+          <t>35922851.76</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-143552</t>
+          <t>-302155</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3460046.369419766</t>
+          <t>-3351368.343323668</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-2381824.930175934</t>
+          <t>-2753639.199795127</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>25449498</v>
+        <v>11765918</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-21.37</t>
+          <t>-22.03</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1070.122</t>
+          <t>1420.148</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-6.41</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-53.56</t>
+          <t>-54.58</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>492</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4086,57 +4086,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-7.76</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.34</t>
+          <t>18.21</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>19.99</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.91</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-17.95</t>
+          <t>-15.51</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-124.44</t>
+          <t>-125.43</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>79942030.28909613</t>
+          <t>79845726.99283668</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>19499217.0</t>
+          <t>25449498.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>17442458.6</t>
+          <t>19541232.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>18972660.0</t>
+          <t>19684784.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>35662849.28</t>
+          <t>35922462.82</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1530201</t>
+          <t>-143552</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3656086.631100463</t>
+          <t>-3460046.369419766</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-3231694.368927941</t>
+          <t>-2381824.930175934</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>19499217</v>
+        <v>25449498</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-19.60</t>
+          <t>-21.37</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>684.997</t>
+          <t>1070.122</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>-6.73</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-11.28</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-52.93</t>
+          <t>-53.56</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>11.58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4507,62 +4507,62 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>492</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>11.41</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.42</t>
+          <t>18.34</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>21.07</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-23.75</t>
+          <t>-17.95</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-123.34</t>
+          <t>-124.44</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>79942030.28909613</t>
+          <t>79845726.99283668</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>12621655.0</t>
+          <t>19499217.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>16932916.8</t>
+          <t>17442458.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>19086589.9</t>
+          <t>18972660.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>35528913.86</t>
+          <t>35662849.28</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2153673</t>
+          <t>-1530201</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3733248.860586376</t>
+          <t>-3656086.631100463</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-3692845.803969096</t>
+          <t>-3231694.368927941</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>12621655</v>
+        <v>19499217</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-19.60</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1182.366</t>
+          <t>684.997</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-11.28</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-53.94</t>
+          <t>-52.93</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4943,72 +4943,72 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>492</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-9.84</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.21</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>21.07</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-33.34</t>
+          <t>-23.75</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-121.96</t>
+          <t>-123.34</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>79942030.28909613</t>
+          <t>79845726.99283668</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>21479903.0</t>
+          <t>12621655.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>18792119.0</t>
+          <t>16932916.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>20020069.3</t>
+          <t>19086589.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>35721023.22</t>
+          <t>35528913.86</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1227950</t>
+          <t>-2153673</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3740594.870880427</t>
+          <t>-3733248.860586376</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-3482864.575314708</t>
+          <t>-3692845.803969096</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>21479903</v>
+        <v>12621655</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-20.26</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1015.264</t>
+          <t>1182.366</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-7.0</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-53.31</t>
+          <t>-53.94</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>492</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5389,22 +5389,22 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-10.20</t>
+          <t>-9.84</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -5414,37 +5414,37 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>18.41</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>20.67</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.16</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-39.99</t>
+          <t>-33.34</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-120.13</t>
+          <t>-121.96</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>79942030.28909613</t>
+          <t>79845726.99283668</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>18655887.0</t>
+          <t>21479903.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>18767550.0</t>
+          <t>18792119.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>20738141.5</t>
+          <t>20020069.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>35528196.68</t>
+          <t>35721023.22</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1970591</t>
+          <t>-1227950</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3787454.924619648</t>
+          <t>-3740594.870880427</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-4007601.37097577</t>
+          <t>-3482864.575314708</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>18655887</v>
+        <v>21479903</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-19.16</t>
+          <t>-20.26</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/齒輪箱.xlsx
+++ b/Result/checksun_type/齒輪箱.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>492.348</t>
+          <t>766.683</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-35.03</t>
+          <t>-34.08</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-56.49</t>
+          <t>-54.45</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>767</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-10.33</t>
+          <t>-10.68</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>18.26</t>
+          <t>18.16</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>20.36</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,56 +1094,56 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-129.97</t>
+          <t>-129.55</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/09/22</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>79845726.99283668</t>
+          <t>79760712.92274678</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>8481553.0</t>
+          <t>13613928.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>10158688.6</t>
+          <t>10372257.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>15635933.7</t>
+          <t>15735161.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>36006631.54</t>
+          <t>35709154.84</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-5477245</t>
+          <t>-5362903</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2762895.647247938</t>
+          <t>-2729603.868942955</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-2868767.912395775</t>
+          <t>-2546499.088265551</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>8481553</v>
+        <v>13613928</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-24.67</t>
+          <t>-21.15</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,17 +1207,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>659.489</t>
+          <t>492.348</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-35.03</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-56.36</t>
+          <t>-56.49</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,22 +1450,22 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>767</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -1475,52 +1475,52 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-9.91</t>
+          <t>-10.33</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>18.26</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>20.36</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,56 +1530,56 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-129.81</t>
+          <t>-129.97</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/09/22</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>79845726.99283668</t>
+          <t>79760712.92274678</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>11267596.0</t>
+          <t>8481553.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>15708299.2</t>
+          <t>10158688.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>16935768.7</t>
+          <t>15635933.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>36089158.58</t>
+          <t>36006631.54</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1227469</t>
+          <t>-5477245</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2743646.144493785</t>
+          <t>-2762895.647247938</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-2676798.628567677</t>
+          <t>-2868767.912395775</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>11267596</v>
+        <v>8481553</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-24.45</t>
+          <t>-24.67</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>801.363</t>
+          <t>659.489</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-10.56</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-57.12</t>
+          <t>-56.36</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>767</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-6.94</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.91</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>18.57</t>
+          <t>18.41</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,56 +1966,56 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-129.41</t>
+          <t>-129.81</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/09/22</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>79845726.99283668</t>
+          <t>79760712.92274678</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>13526868.0</t>
+          <t>11267596.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>15807963.6</t>
+          <t>15708299.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>17674597.8</t>
+          <t>16935768.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>36309850.68</t>
+          <t>36089158.58</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1866634</t>
+          <t>-1227469</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-2755800.238298532</t>
+          <t>-2743646.144493785</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-2605461.450650116</t>
+          <t>-2676798.628567677</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>13526868</v>
+        <v>11267596</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-25.77</t>
+          <t>-24.45</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>16.7</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>17.15</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>16.7</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>16.85</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>286.781</t>
+          <t>801.363</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,102 +2216,102 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>5.87</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-0.76</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-10.56</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-02-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2024-09-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2024-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>40.65</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>39.3</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>44.9</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-57.12</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>-7.61</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>8.67</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>-0.88</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-1.37</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-02-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-03-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2024-09-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2024-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>40.65</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>39.3</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>44.9</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>44.0</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-56.11</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>-7.61</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>-1.45</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,17 +2322,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>767</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>13.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-7.11</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>18.57</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-9.69</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,56 +2402,56 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-128.75</t>
+          <t>-129.41</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/09/22</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>79845726.99283668</t>
+          <t>79760712.92274678</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4971344.0</t>
+          <t>13526868.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>18192489.6</t>
+          <t>15807963.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>17817474.1</t>
+          <t>17674597.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>36286025.3</t>
+          <t>36309850.68</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>375015</t>
+          <t>-1866634</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-2783134.563325516</t>
+          <t>-2755800.238298532</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-2652563.858958956</t>
+          <t>-2605461.450650116</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>4971344</v>
+        <v>13526868</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-24.01</t>
+          <t>-25.77</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,17 +2515,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>17.05</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
           <t>17.15</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>17.6</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>732.465</t>
+          <t>286.781</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-56.62</t>
+          <t>-56.11</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>767</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.79</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-7.11</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.64</t>
+          <t>17.44</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.77</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>21.37</t>
+          <t>21.29</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-12.62</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,56 +2838,56 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-128.05</t>
+          <t>-128.75</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/09/22</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>79845726.99283668</t>
+          <t>79760712.92274678</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>12546082.0</t>
+          <t>4971344.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>21098064.2</t>
+          <t>18192489.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>19015490.5</t>
+          <t>17817474.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>36438805.22</t>
+          <t>36286025.3</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>2082573</t>
+          <t>375015</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-2806874.691392164</t>
+          <t>-2783134.563325516</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1708455.304437336</t>
+          <t>-2652563.858958956</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>12546082</v>
+        <v>4971344</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-24.89</t>
+          <t>-24.01</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2045.558</t>
+          <t>732.465</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-55.85</t>
+          <t>-56.62</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>767</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-7.15</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17.93</t>
+          <t>17.64</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.37</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-12.70</t>
+          <t>-12.62</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,56 +3274,56 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-127.17</t>
+          <t>-128.05</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/09/22</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>79845726.99283668</t>
+          <t>79760712.92274678</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>36229606.0</t>
+          <t>12546082.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>21113178.8</t>
+          <t>21098064.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>19952648.9</t>
+          <t>19015490.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>36367077.28</t>
+          <t>36438805.22</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1160529</t>
+          <t>2082573</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3006587.307202132</t>
+          <t>-2806874.691392164</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1110291.608533688</t>
+          <t>-1708455.304437336</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>36229606</v>
+        <v>12546082</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-23.57</t>
+          <t>-24.89</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>661.456</t>
+          <t>2045.558</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-54.96</t>
+          <t>-55.85</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>767</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,22 +3645,22 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.94</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-7.15</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -3670,37 +3670,37 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.08</t>
+          <t>17.93</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-12.70</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,56 +3710,56 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-126.30</t>
+          <t>-127.17</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/09/22</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>79845726.99283668</t>
+          <t>79760712.92274678</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>11765918.0</t>
+          <t>36229606.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>18163238.2</t>
+          <t>21113178.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>18465394.1</t>
+          <t>19952648.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>35922851.76</t>
+          <t>36367077.28</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-302155</t>
+          <t>1160529</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3351368.343323668</t>
+          <t>-3006587.307202132</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-2753639.199795127</t>
+          <t>-1110291.608533688</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>11765918</v>
+        <v>36229606</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-22.03</t>
+          <t>-23.57</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1420.148</t>
+          <t>661.456</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-54.58</t>
+          <t>-54.96</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>767</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,62 +4081,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-7.76</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.21</t>
+          <t>18.08</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>20.91</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-15.51</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,56 +4146,56 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-125.43</t>
+          <t>-126.30</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/09/22</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>79845726.99283668</t>
+          <t>79760712.92274678</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>25449498.0</t>
+          <t>11765918.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>19541232.0</t>
+          <t>18163238.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>19684784.3</t>
+          <t>18465394.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>35922462.82</t>
+          <t>35922851.76</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-143552</t>
+          <t>-302155</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3460046.369419766</t>
+          <t>-3351368.343323668</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-2381824.930175934</t>
+          <t>-2753639.199795127</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>25449498</v>
+        <v>11765918</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-21.37</t>
+          <t>-22.03</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,17 +4259,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1070.122</t>
+          <t>1420.148</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.73</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-53.56</t>
+          <t>-54.58</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,17 +4502,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>767</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4522,57 +4522,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-7.76</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.34</t>
+          <t>18.21</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>19.99</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.91</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-17.95</t>
+          <t>-15.51</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,56 +4582,56 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-124.44</t>
+          <t>-125.43</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/09/22</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>79845726.99283668</t>
+          <t>79760712.92274678</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>19499217.0</t>
+          <t>25449498.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>17442458.6</t>
+          <t>19541232.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>18972660.0</t>
+          <t>19684784.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>35662849.28</t>
+          <t>35922462.82</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1530201</t>
+          <t>-143552</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3656086.631100463</t>
+          <t>-3460046.369419766</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-3231694.368927941</t>
+          <t>-2381824.930175934</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>19499217</v>
+        <v>25449498</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-19.60</t>
+          <t>-21.37</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>684.997</t>
+          <t>1070.122</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-11.28</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-52.93</t>
+          <t>-53.56</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>11.58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,67 +4938,67 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>767</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>11.41</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.42</t>
+          <t>18.34</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>21.07</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-23.75</t>
+          <t>-17.95</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,56 +5018,56 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-123.34</t>
+          <t>-124.44</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/09/22</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>79845726.99283668</t>
+          <t>79760712.92274678</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>12621655.0</t>
+          <t>19499217.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>16932916.8</t>
+          <t>17442458.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>19086589.9</t>
+          <t>18972660.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>35528913.86</t>
+          <t>35662849.28</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2153673</t>
+          <t>-1530201</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3733248.860586376</t>
+          <t>-3656086.631100463</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-3692845.803969096</t>
+          <t>-3231694.368927941</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>12621655</v>
+        <v>19499217</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-19.60</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1182.366</t>
+          <t>684.997</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-11.28</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-53.94</t>
+          <t>-52.93</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>767</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-9.84</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>20.21</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>21.07</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-33.34</t>
+          <t>-23.75</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,56 +5454,56 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-121.96</t>
+          <t>-123.34</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/09/22</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>79845726.99283668</t>
+          <t>79760712.92274678</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>21479903.0</t>
+          <t>12621655.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>18792119.0</t>
+          <t>16932916.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>20020069.3</t>
+          <t>19086589.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>35721023.22</t>
+          <t>35528913.86</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1227950</t>
+          <t>-2153673</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3740594.870880427</t>
+          <t>-3733248.860586376</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-3482864.575314708</t>
+          <t>-3692845.803969096</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>21479903</v>
+        <v>12621655</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-20.26</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/齒輪箱.xlsx
+++ b/Result/checksun_type/齒輪箱.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>17.25</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>18.16</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>20.33</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>13613928.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>10372257.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>10372257.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>15735161.0</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>35709154.84</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>35709154.84</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-2546499.088265551</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>13613928</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>13613928.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>17.08</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>18.26</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>20.36</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>20.36</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>8481553.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>10158688.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>10158688.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>15635933.7</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>36006631.54</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>36006631.54</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-2868767.912395775</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>8481553</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>8481553.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>17.13</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>18.41</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>20.43</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>20.43</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>11267596.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>15708299.2</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>15708299.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>16935768.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>36089158.58</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>36089158.58</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-2676798.628567677</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>11267596</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>11267596.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>17.24</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>18.57</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>20.5</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>20.5</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>13526868.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>15807963.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>15807963.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>17674597.8</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>36309850.68</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>36309850.68</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-2605461.450650116</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>13526868</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>13526868.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>17.44</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>18.77</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>20.58</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>20.58</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>4971344.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>18192489.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>18192489.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>17817474.1</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>36286025.3</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>36286025.3</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-2652563.858958956</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>4971344</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>4971344.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>17.64</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>20.66</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>20.66</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>12546082.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>21098064.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>21098064.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>19015490.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>36438805.22</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>36438805.22</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-1708455.304437336</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>12546082</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>12546082.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>17.93</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>19.27</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>20.75</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>20.75</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>36229606.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>21113178.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>21113178.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>19952648.9</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>36367077.28</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>36367077.28</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-1110291.608533688</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>36229606</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>36229606.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>18.08</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>19.51</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>20.83</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>20.83</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>11765918.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>18163238.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>18163238.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>18465394.1</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>35922851.76</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>35922851.76</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-2753639.199795127</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>11765918</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>11765918.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>18.21</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>19.74</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>20.91</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>19.74</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>20.91</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>25449498.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>19541232.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>19541232</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>19684784.3</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>35922462.82</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>35922462.82</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-2381824.930175934</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>25449498</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>25449498.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>18.34</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>21</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>19499217.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>17442458.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>17442458.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>18972660.0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>35662849.28</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>35662849.28</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-3231694.368927941</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>19499217</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>19499217.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>18.42</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>20.21</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>21.07</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>20.21</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>21.07</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>12621655.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>16932916.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>16932916.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>19086589.9</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>35528913.86</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>35528913.86</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-3692845.803969096</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>12621655</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>12621655.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>

--- a/Result/checksun_type/齒輪箱.xlsx
+++ b/Result/checksun_type/齒輪箱.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>766.683</t>
+          <t>473.845</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-34.08</t>
+          <t>-24.46</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-54.45</t>
+          <t>-55.34</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>474</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>61.51</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-10.68</t>
+          <t>-11.09</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.31</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>18.16</v>
+        <v>18.03</v>
       </c>
       <c r="AN2" t="n">
-        <v>20.33</v>
+        <v>20.28</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>20.93</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-129.55</t>
+          <t>-128.88</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>79760712.92274678</t>
+          <t>79664598.62142856</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>13613928.0</t>
+          <t>8320468.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>10372257.8</v>
+        <v>11042082.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>15735161.0</t>
+          <t>14617286.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>35709154.84</v>
+        <v>35513356.96</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-5362903</t>
+          <t>-3575203</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2729603.868942955</t>
+          <t>-2718012.186669847</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-2546499.088265551</t>
+          <t>-2654257.934167756</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>13613928.0</t>
+          <t>8320468.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-21.15</t>
+          <t>-22.69</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>492.348</t>
+          <t>766.683</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-35.03</t>
+          <t>-34.08</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-56.49</t>
+          <t>-54.45</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>474</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-10.33</t>
+          <t>-10.68</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>18.26</v>
+        <v>18.16</v>
       </c>
       <c r="AN3" t="n">
-        <v>20.36</v>
+        <v>20.33</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-129.97</t>
+          <t>-129.55</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>79760712.92274678</t>
+          <t>79664598.62142856</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>8481553.0</t>
+          <t>13613928.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>10158688.6</v>
+        <v>10372257.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>15635933.7</t>
+          <t>15735161.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>36006631.54</v>
+        <v>35709154.84</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-5477245</t>
+          <t>-5362903</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2762895.647247938</t>
+          <t>-2729603.868942955</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-2868767.912395775</t>
+          <t>-2546499.088265551</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>8481553.0</t>
+          <t>13613928.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-24.67</t>
+          <t>-21.15</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>659.489</t>
+          <t>492.348</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-35.03</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-56.36</t>
+          <t>-56.49</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,22 +1874,22 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>474</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1899,48 +1899,48 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-9.91</t>
+          <t>-10.33</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>18.41</v>
+        <v>18.26</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.43</v>
+        <v>20.36</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-129.81</t>
+          <t>-129.97</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>79760712.92274678</t>
+          <t>79664598.62142856</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>11267596.0</t>
+          <t>8481553.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>15708299.2</v>
+        <v>10158688.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>16935768.7</t>
+          <t>15635933.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>36089158.58</v>
+        <v>36006631.54</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1227469</t>
+          <t>-5477245</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-2743646.144493785</t>
+          <t>-2762895.647247938</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-2676798.628567677</t>
+          <t>-2868767.912395775</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>11267596.0</t>
+          <t>8481553.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-24.45</t>
+          <t>-24.67</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>801.363</t>
+          <t>659.489</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-10.56</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-57.12</t>
+          <t>-56.36</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>474</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-6.94</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.91</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>18.57</v>
+        <v>18.41</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.5</v>
+        <v>20.43</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-129.41</t>
+          <t>-129.81</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>79760712.92274678</t>
+          <t>79664598.62142856</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>13526868.0</t>
+          <t>11267596.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>15807963.6</v>
+        <v>15708299.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>17674597.8</t>
+          <t>16935768.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>36309850.68</v>
+        <v>36089158.58</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1866634</t>
+          <t>-1227469</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-2755800.238298532</t>
+          <t>-2743646.144493785</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-2605461.450650116</t>
+          <t>-2676798.628567677</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>13526868.0</t>
+          <t>11267596.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-25.77</t>
+          <t>-24.45</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>16.7</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>17.15</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>16.7</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>16.85</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>286.781</t>
+          <t>801.363</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>-10.56</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-56.11</t>
+          <t>-57.12</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,17 +2734,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>474</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>13.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2754,53 +2754,53 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-7.11</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>18.77</v>
+        <v>18.57</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.58</v>
+        <v>20.5</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-9.69</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-128.75</t>
+          <t>-129.41</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>79760712.92274678</t>
+          <t>79664598.62142856</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4971344.0</t>
+          <t>13526868.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>18192489.6</v>
+        <v>15807963.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17817474.1</t>
+          <t>17674597.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>36286025.3</v>
+        <v>36309850.68</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>375015</t>
+          <t>-1866634</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-2783134.563325516</t>
+          <t>-2755800.238298532</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-2652563.858958956</t>
+          <t>-2605461.450650116</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>4971344.0</t>
+          <t>13526868.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-24.01</t>
+          <t>-25.77</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>17.05</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>17.15</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>17.6</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>732.465</t>
+          <t>286.781</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-56.62</t>
+          <t>-56.11</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>474</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.79</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-7.11</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17.64</t>
+          <t>17.44</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>19</v>
+        <v>18.77</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.66</v>
+        <v>20.58</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>21.37</t>
+          <t>21.29</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-12.62</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-128.05</t>
+          <t>-128.75</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>79760712.92274678</t>
+          <t>79664598.62142856</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>12546082.0</t>
+          <t>4971344.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>21098064.2</v>
+        <v>18192489.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>19015490.5</t>
+          <t>17817474.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>36438805.22</v>
+        <v>36286025.3</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>2082573</t>
+          <t>375015</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-2806874.691392164</t>
+          <t>-2783134.563325516</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1708455.304437336</t>
+          <t>-2652563.858958956</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>12546082.0</t>
+          <t>4971344.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-24.89</t>
+          <t>-24.01</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2045.558</t>
+          <t>732.465</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-55.85</t>
+          <t>-56.62</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>474</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-7.15</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>17.93</t>
+          <t>17.64</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>19.27</v>
+        <v>19</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.75</v>
+        <v>20.66</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.37</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-12.70</t>
+          <t>-12.62</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-127.17</t>
+          <t>-128.05</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>79760712.92274678</t>
+          <t>79664598.62142856</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>36229606.0</t>
+          <t>12546082.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>21113178.8</v>
+        <v>21098064.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>19952648.9</t>
+          <t>19015490.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>36367077.28</v>
+        <v>36438805.22</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1160529</t>
+          <t>2082573</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3006587.307202132</t>
+          <t>-2806874.691392164</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1110291.608533688</t>
+          <t>-1708455.304437336</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>36229606.0</t>
+          <t>12546082.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-23.57</t>
+          <t>-24.89</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>661.456</t>
+          <t>2045.558</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-54.96</t>
+          <t>-55.85</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>474</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,22 +4039,22 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.94</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-7.15</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -4064,33 +4064,33 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>18.08</t>
+          <t>17.93</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>19.51</v>
+        <v>19.27</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.83</v>
+        <v>20.75</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-12.70</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-126.30</t>
+          <t>-127.17</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>79760712.92274678</t>
+          <t>79664598.62142856</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>11765918.0</t>
+          <t>36229606.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>18163238.2</v>
+        <v>21113178.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>18465394.1</t>
+          <t>19952648.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>35922851.76</v>
+        <v>36367077.28</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-302155</t>
+          <t>1160529</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3351368.343323668</t>
+          <t>-3006587.307202132</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-2753639.199795127</t>
+          <t>-1110291.608533688</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>11765918.0</t>
+          <t>36229606.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-22.03</t>
+          <t>-23.57</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1420.148</t>
+          <t>661.456</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-54.58</t>
+          <t>-54.96</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>474</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-7.76</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.21</t>
+          <t>18.08</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>19.74</v>
+        <v>19.51</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.91</v>
+        <v>20.83</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-15.51</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-125.43</t>
+          <t>-126.30</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>79760712.92274678</t>
+          <t>79664598.62142856</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>25449498.0</t>
+          <t>11765918.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>19541232</v>
+        <v>18163238.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>19684784.3</t>
+          <t>18465394.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>35922462.82</v>
+        <v>35922851.76</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-143552</t>
+          <t>-302155</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3460046.369419766</t>
+          <t>-3351368.343323668</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-2381824.930175934</t>
+          <t>-2753639.199795127</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>25449498.0</t>
+          <t>11765918.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-21.37</t>
+          <t>-22.03</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1070.122</t>
+          <t>1420.148</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-53.56</t>
+          <t>-54.58</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,17 +4884,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>474</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-7.76</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.34</t>
+          <t>18.21</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>19.99</v>
+        <v>19.74</v>
       </c>
       <c r="AN11" t="n">
-        <v>21</v>
+        <v>20.91</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-17.95</t>
+          <t>-15.51</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-124.44</t>
+          <t>-125.43</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>79760712.92274678</t>
+          <t>79664598.62142856</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>19499217.0</t>
+          <t>25449498.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>17442458.6</v>
+        <v>19541232</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>18972660.0</t>
+          <t>19684784.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>35662849.28</v>
+        <v>35922462.82</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1530201</t>
+          <t>-143552</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3656086.631100463</t>
+          <t>-3460046.369419766</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-3231694.368927941</t>
+          <t>-2381824.930175934</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>19499217.0</t>
+          <t>25449498.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-19.60</t>
+          <t>-21.37</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>684.997</t>
+          <t>1070.122</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-11.28</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-52.93</t>
+          <t>-53.56</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>11.58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,63 +5314,63 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>474</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>11.41</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.42</t>
+          <t>18.34</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>20.21</v>
+        <v>19.99</v>
       </c>
       <c r="AN12" t="n">
-        <v>21.07</v>
+        <v>21</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-23.75</t>
+          <t>-17.95</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-123.34</t>
+          <t>-124.44</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>79760712.92274678</t>
+          <t>79664598.62142856</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>12621655.0</t>
+          <t>19499217.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>16932916.8</v>
+        <v>17442458.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>19086589.9</t>
+          <t>18972660.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>35528913.86</v>
+        <v>35662849.28</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2153673</t>
+          <t>-1530201</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3733248.860586376</t>
+          <t>-3656086.631100463</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-3692845.803969096</t>
+          <t>-3231694.368927941</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>12621655.0</t>
+          <t>19499217.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-19.60</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/齒輪箱.xlsx
+++ b/Result/checksun_type/齒輪箱.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>473.845</t>
+          <t>412.077</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-24.46</t>
+          <t>-23.56</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-55.34</t>
+          <t>-55.22</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>412</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>61.51</t>
+          <t>79.37</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.09</t>
+          <t>-11.5</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.31</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>18.03</v>
+        <v>17.92</v>
       </c>
       <c r="AN2" t="n">
-        <v>20.28</v>
+        <v>20.25</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>20.86</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-128.88</t>
+          <t>-127.99</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>79664598.62142856</t>
+          <t>79566401.83523537</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>8320468.0</t>
+          <t>7219101.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>11042082.6</v>
+        <v>9780529.199999999</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>14617286.1</t>
+          <t>12794246.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>35513356.96</v>
+        <v>35322706.48</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-3575203</t>
+          <t>-3013717</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2718012.186669847</t>
+          <t>-2722308.035327579</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-2654257.934167756</t>
+          <t>-2745935.202945104</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>8320468.0</t>
+          <t>7219101.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-22.69</t>
+          <t>-22.47</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>766.683</t>
+          <t>473.845</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-34.08</t>
+          <t>-24.46</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-54.45</t>
+          <t>-55.34</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>412</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>61.51</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-10.68</t>
+          <t>-11.09</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.31</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>18.16</v>
+        <v>18.03</v>
       </c>
       <c r="AN3" t="n">
-        <v>20.33</v>
+        <v>20.28</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>20.93</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-129.55</t>
+          <t>-128.88</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>79664598.62142856</t>
+          <t>79566401.83523537</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>13613928.0</t>
+          <t>8320468.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>10372257.8</v>
+        <v>11042082.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>15735161.0</t>
+          <t>14617286.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>35709154.84</v>
+        <v>35513356.96</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-5362903</t>
+          <t>-3575203</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2729603.868942955</t>
+          <t>-2718012.186669847</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-2546499.088265551</t>
+          <t>-2654257.934167756</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>13613928.0</t>
+          <t>8320468.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-21.15</t>
+          <t>-22.69</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>492.348</t>
+          <t>766.683</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-35.03</t>
+          <t>-34.08</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-56.49</t>
+          <t>-54.45</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>412</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-10.33</t>
+          <t>-10.68</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>18.26</v>
+        <v>18.16</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.36</v>
+        <v>20.33</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-129.97</t>
+          <t>-129.55</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>79664598.62142856</t>
+          <t>79566401.83523537</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>8481553.0</t>
+          <t>13613928.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>10158688.6</v>
+        <v>10372257.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>15635933.7</t>
+          <t>15735161.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>36006631.54</v>
+        <v>35709154.84</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-5477245</t>
+          <t>-5362903</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-2762895.647247938</t>
+          <t>-2729603.868942955</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-2868767.912395775</t>
+          <t>-2546499.088265551</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>8481553.0</t>
+          <t>13613928.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-24.67</t>
+          <t>-21.15</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>659.489</t>
+          <t>492.348</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-35.03</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-56.36</t>
+          <t>-56.49</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,22 +2304,22 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>412</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -2329,48 +2329,48 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-9.91</t>
+          <t>-10.33</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>18.41</v>
+        <v>18.26</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.43</v>
+        <v>20.36</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-129.81</t>
+          <t>-129.97</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>79664598.62142856</t>
+          <t>79566401.83523537</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>11267596.0</t>
+          <t>8481553.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>15708299.2</v>
+        <v>10158688.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>16935768.7</t>
+          <t>15635933.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>36089158.58</v>
+        <v>36006631.54</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1227469</t>
+          <t>-5477245</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-2743646.144493785</t>
+          <t>-2762895.647247938</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-2676798.628567677</t>
+          <t>-2868767.912395775</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>11267596.0</t>
+          <t>8481553.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-24.45</t>
+          <t>-24.67</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>801.363</t>
+          <t>659.489</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-10.56</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-57.12</t>
+          <t>-56.36</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>412</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-6.94</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.91</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>18.57</v>
+        <v>18.41</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.5</v>
+        <v>20.43</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-129.41</t>
+          <t>-129.81</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>79664598.62142856</t>
+          <t>79566401.83523537</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>13526868.0</t>
+          <t>11267596.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>15807963.6</v>
+        <v>15708299.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17674597.8</t>
+          <t>16935768.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>36309850.68</v>
+        <v>36089158.58</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1866634</t>
+          <t>-1227469</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-2755800.238298532</t>
+          <t>-2743646.144493785</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-2605461.450650116</t>
+          <t>-2676798.628567677</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>13526868.0</t>
+          <t>11267596.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-25.77</t>
+          <t>-24.45</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>16.7</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>17.15</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>16.7</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>16.85</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>286.781</t>
+          <t>801.363</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>-10.56</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-56.11</t>
+          <t>-57.12</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,17 +3164,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>412</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>13.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,53 +3184,53 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-7.11</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>18.77</v>
+        <v>18.57</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.58</v>
+        <v>20.5</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-9.69</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-128.75</t>
+          <t>-129.41</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>79664598.62142856</t>
+          <t>79566401.83523537</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>4971344.0</t>
+          <t>13526868.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>18192489.6</v>
+        <v>15807963.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>17817474.1</t>
+          <t>17674597.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>36286025.3</v>
+        <v>36309850.68</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>375015</t>
+          <t>-1866634</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-2783134.563325516</t>
+          <t>-2755800.238298532</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-2652563.858958956</t>
+          <t>-2605461.450650116</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>4971344.0</t>
+          <t>13526868.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-24.01</t>
+          <t>-25.77</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>17.05</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
           <t>17.15</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>17.6</t>
-        </is>
-      </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>732.465</t>
+          <t>286.781</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-56.62</t>
+          <t>-56.11</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>412</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.79</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-7.11</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>17.64</t>
+          <t>17.44</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>19</v>
+        <v>18.77</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.66</v>
+        <v>20.58</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>21.37</t>
+          <t>21.29</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-12.62</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-128.05</t>
+          <t>-128.75</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>79664598.62142856</t>
+          <t>79566401.83523537</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>12546082.0</t>
+          <t>4971344.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>21098064.2</v>
+        <v>18192489.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>19015490.5</t>
+          <t>17817474.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>36438805.22</v>
+        <v>36286025.3</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>2082573</t>
+          <t>375015</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-2806874.691392164</t>
+          <t>-2783134.563325516</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1708455.304437336</t>
+          <t>-2652563.858958956</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>12546082.0</t>
+          <t>4971344.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-24.89</t>
+          <t>-24.01</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2045.558</t>
+          <t>732.465</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-55.85</t>
+          <t>-56.62</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>412</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-7.15</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>17.93</t>
+          <t>17.64</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>19.27</v>
+        <v>19</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.75</v>
+        <v>20.66</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.37</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-12.70</t>
+          <t>-12.62</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-127.17</t>
+          <t>-128.05</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>79664598.62142856</t>
+          <t>79566401.83523537</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>36229606.0</t>
+          <t>12546082.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>21113178.8</v>
+        <v>21098064.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>19952648.9</t>
+          <t>19015490.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>36367077.28</v>
+        <v>36438805.22</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1160529</t>
+          <t>2082573</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3006587.307202132</t>
+          <t>-2806874.691392164</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1110291.608533688</t>
+          <t>-1708455.304437336</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>36229606.0</t>
+          <t>12546082.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-23.57</t>
+          <t>-24.89</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>661.456</t>
+          <t>2045.558</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-54.96</t>
+          <t>-55.85</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>412</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,22 +4469,22 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.94</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-7.15</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -4494,33 +4494,33 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>18.08</t>
+          <t>17.93</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>19.51</v>
+        <v>19.27</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.83</v>
+        <v>20.75</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-12.70</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-126.30</t>
+          <t>-127.17</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>79664598.62142856</t>
+          <t>79566401.83523537</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>11765918.0</t>
+          <t>36229606.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>18163238.2</v>
+        <v>21113178.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>18465394.1</t>
+          <t>19952648.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>35922851.76</v>
+        <v>36367077.28</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-302155</t>
+          <t>1160529</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3351368.343323668</t>
+          <t>-3006587.307202132</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-2753639.199795127</t>
+          <t>-1110291.608533688</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>11765918.0</t>
+          <t>36229606.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-22.03</t>
+          <t>-23.57</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1420.148</t>
+          <t>661.456</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-54.58</t>
+          <t>-54.96</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>412</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-7.76</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.21</t>
+          <t>18.08</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>19.74</v>
+        <v>19.51</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.91</v>
+        <v>20.83</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-15.51</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-125.43</t>
+          <t>-126.30</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>79664598.62142856</t>
+          <t>79566401.83523537</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>25449498.0</t>
+          <t>11765918.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>19541232</v>
+        <v>18163238.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>19684784.3</t>
+          <t>18465394.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>35922462.82</v>
+        <v>35922851.76</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-143552</t>
+          <t>-302155</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3460046.369419766</t>
+          <t>-3351368.343323668</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-2381824.930175934</t>
+          <t>-2753639.199795127</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>25449498.0</t>
+          <t>11765918.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-21.37</t>
+          <t>-22.03</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1070.122</t>
+          <t>1420.148</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-53.56</t>
+          <t>-54.58</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11.58</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,17 +5314,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>412</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-7.76</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.34</t>
+          <t>18.21</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>19.99</v>
+        <v>19.74</v>
       </c>
       <c r="AN12" t="n">
-        <v>21</v>
+        <v>20.91</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-17.95</t>
+          <t>-15.51</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-124.44</t>
+          <t>-125.43</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>79664598.62142856</t>
+          <t>79566401.83523537</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>19499217.0</t>
+          <t>25449498.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>17442458.6</v>
+        <v>19541232</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>18972660.0</t>
+          <t>19684784.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>35662849.28</v>
+        <v>35922462.82</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1530201</t>
+          <t>-143552</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3656086.631100463</t>
+          <t>-3460046.369419766</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-3231694.368927941</t>
+          <t>-2381824.930175934</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>19499217.0</t>
+          <t>25449498.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-19.60</t>
+          <t>-21.37</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/齒輪箱.xlsx
+++ b/Result/checksun_type/齒輪箱.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>412.077</t>
+          <t>360.254</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-23.56</t>
+          <t>-28.20</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>360</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>79.37</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.5</t>
+          <t>-11.77</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>17.92</v>
+        <v>17.83</v>
       </c>
       <c r="AN2" t="n">
-        <v>20.25</v>
+        <v>20.21</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.86</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>15.41</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-127.99</t>
+          <t>-126.95</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>79566401.83523537</t>
+          <t>79466637.12606837</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>7219101.0</t>
+          <t>6354384.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>9780529.199999999</v>
+        <v>8797886.800000001</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>12794246.4</t>
+          <t>12253093.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>35322706.48</v>
+        <v>35217518.76</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-3013717</t>
+          <t>-3455206</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2722308.035327579</t>
+          <t>-2735232.135433431</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-2745935.202945104</t>
+          <t>-2806314.686015621</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>7219101.0</t>
+          <t>6354384.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>473.845</t>
+          <t>412.077</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-24.46</t>
+          <t>-23.56</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-55.34</t>
+          <t>-55.22</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>360</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>61.51</t>
+          <t>79.37</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.09</t>
+          <t>-11.5</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.31</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>18.03</v>
+        <v>17.92</v>
       </c>
       <c r="AN3" t="n">
-        <v>20.28</v>
+        <v>20.25</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>20.86</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-128.88</t>
+          <t>-127.99</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>79566401.83523537</t>
+          <t>79466637.12606837</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>8320468.0</t>
+          <t>7219101.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>11042082.6</v>
+        <v>9780529.199999999</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>14617286.1</t>
+          <t>12794246.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>35513356.96</v>
+        <v>35322706.48</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-3575203</t>
+          <t>-3013717</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2718012.186669847</t>
+          <t>-2722308.035327579</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-2654257.934167756</t>
+          <t>-2745935.202945104</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>8320468.0</t>
+          <t>7219101.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-22.69</t>
+          <t>-22.47</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>766.683</t>
+          <t>473.845</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-34.08</t>
+          <t>-24.46</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-54.45</t>
+          <t>-55.34</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>360</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>61.51</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-10.68</t>
+          <t>-11.09</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.31</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>18.16</v>
+        <v>18.03</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.33</v>
+        <v>20.28</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>20.93</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-129.55</t>
+          <t>-128.88</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>79566401.83523537</t>
+          <t>79466637.12606837</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>13613928.0</t>
+          <t>8320468.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>10372257.8</v>
+        <v>11042082.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>15735161.0</t>
+          <t>14617286.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>35709154.84</v>
+        <v>35513356.96</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-5362903</t>
+          <t>-3575203</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-2729603.868942955</t>
+          <t>-2718012.186669847</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-2546499.088265551</t>
+          <t>-2654257.934167756</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>13613928.0</t>
+          <t>8320468.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-21.15</t>
+          <t>-22.69</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>492.348</t>
+          <t>766.683</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-35.03</t>
+          <t>-34.08</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-56.49</t>
+          <t>-54.45</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>360</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-10.33</t>
+          <t>-10.68</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>18.26</v>
+        <v>18.16</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.36</v>
+        <v>20.33</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-129.97</t>
+          <t>-129.55</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>79566401.83523537</t>
+          <t>79466637.12606837</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>8481553.0</t>
+          <t>13613928.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>10158688.6</v>
+        <v>10372257.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>15635933.7</t>
+          <t>15735161.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>36006631.54</v>
+        <v>35709154.84</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-5477245</t>
+          <t>-5362903</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-2762895.647247938</t>
+          <t>-2729603.868942955</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-2868767.912395775</t>
+          <t>-2546499.088265551</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>8481553.0</t>
+          <t>13613928.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-24.67</t>
+          <t>-21.15</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>659.489</t>
+          <t>492.348</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-35.03</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-56.36</t>
+          <t>-56.49</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,22 +2734,22 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>360</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -2759,48 +2759,48 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-9.91</t>
+          <t>-10.33</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>18.41</v>
+        <v>18.26</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.43</v>
+        <v>20.36</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-129.81</t>
+          <t>-129.97</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>79566401.83523537</t>
+          <t>79466637.12606837</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>11267596.0</t>
+          <t>8481553.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>15708299.2</v>
+        <v>10158688.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>16935768.7</t>
+          <t>15635933.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>36089158.58</v>
+        <v>36006631.54</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1227469</t>
+          <t>-5477245</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-2743646.144493785</t>
+          <t>-2762895.647247938</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-2676798.628567677</t>
+          <t>-2868767.912395775</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>11267596.0</t>
+          <t>8481553.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-24.45</t>
+          <t>-24.67</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>801.363</t>
+          <t>659.489</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-10.56</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-57.12</t>
+          <t>-56.36</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>360</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-6.94</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.91</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>18.57</v>
+        <v>18.41</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.5</v>
+        <v>20.43</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-129.41</t>
+          <t>-129.81</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>79566401.83523537</t>
+          <t>79466637.12606837</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>13526868.0</t>
+          <t>11267596.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>15807963.6</v>
+        <v>15708299.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>17674597.8</t>
+          <t>16935768.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>36309850.68</v>
+        <v>36089158.58</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1866634</t>
+          <t>-1227469</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-2755800.238298532</t>
+          <t>-2743646.144493785</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-2605461.450650116</t>
+          <t>-2676798.628567677</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>13526868.0</t>
+          <t>11267596.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-25.77</t>
+          <t>-24.45</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>16.7</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>17.15</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>16.7</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>16.85</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>286.781</t>
+          <t>801.363</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>-10.56</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-56.11</t>
+          <t>-57.12</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,17 +3594,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>360</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>13.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-7.11</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>18.77</v>
+        <v>18.57</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.58</v>
+        <v>20.5</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-9.69</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-128.75</t>
+          <t>-129.41</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>79566401.83523537</t>
+          <t>79466637.12606837</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4971344.0</t>
+          <t>13526868.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>18192489.6</v>
+        <v>15807963.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>17817474.1</t>
+          <t>17674597.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>36286025.3</v>
+        <v>36309850.68</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>375015</t>
+          <t>-1866634</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-2783134.563325516</t>
+          <t>-2755800.238298532</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-2652563.858958956</t>
+          <t>-2605461.450650116</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>4971344.0</t>
+          <t>13526868.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-24.01</t>
+          <t>-25.77</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>17.05</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
           <t>17.15</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>17.6</t>
-        </is>
-      </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>732.465</t>
+          <t>286.781</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-56.62</t>
+          <t>-56.11</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>360</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.79</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-7.11</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>17.64</t>
+          <t>17.44</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>19</v>
+        <v>18.77</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.66</v>
+        <v>20.58</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>21.37</t>
+          <t>21.29</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-12.62</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-128.05</t>
+          <t>-128.75</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>79566401.83523537</t>
+          <t>79466637.12606837</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>12546082.0</t>
+          <t>4971344.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>21098064.2</v>
+        <v>18192489.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>19015490.5</t>
+          <t>17817474.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>36438805.22</v>
+        <v>36286025.3</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>2082573</t>
+          <t>375015</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-2806874.691392164</t>
+          <t>-2783134.563325516</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1708455.304437336</t>
+          <t>-2652563.858958956</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>12546082.0</t>
+          <t>4971344.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-24.89</t>
+          <t>-24.01</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2045.558</t>
+          <t>732.465</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-55.85</t>
+          <t>-56.62</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>360</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-7.15</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>17.93</t>
+          <t>17.64</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>19.27</v>
+        <v>19</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.75</v>
+        <v>20.66</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.37</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-12.70</t>
+          <t>-12.62</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-127.17</t>
+          <t>-128.05</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>79566401.83523537</t>
+          <t>79466637.12606837</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>36229606.0</t>
+          <t>12546082.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>21113178.8</v>
+        <v>21098064.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>19952648.9</t>
+          <t>19015490.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>36367077.28</v>
+        <v>36438805.22</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1160529</t>
+          <t>2082573</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3006587.307202132</t>
+          <t>-2806874.691392164</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1110291.608533688</t>
+          <t>-1708455.304437336</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>36229606.0</t>
+          <t>12546082.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-23.57</t>
+          <t>-24.89</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>661.456</t>
+          <t>2045.558</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-54.96</t>
+          <t>-55.85</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>360</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,22 +4899,22 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.94</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-7.15</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -4924,33 +4924,33 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>18.08</t>
+          <t>17.93</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>19.51</v>
+        <v>19.27</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.83</v>
+        <v>20.75</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-12.70</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-126.30</t>
+          <t>-127.17</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>79566401.83523537</t>
+          <t>79466637.12606837</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>11765918.0</t>
+          <t>36229606.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>18163238.2</v>
+        <v>21113178.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>18465394.1</t>
+          <t>19952648.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>35922851.76</v>
+        <v>36367077.28</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-302155</t>
+          <t>1160529</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3351368.343323668</t>
+          <t>-3006587.307202132</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-2753639.199795127</t>
+          <t>-1110291.608533688</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>11765918.0</t>
+          <t>36229606.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-22.03</t>
+          <t>-23.57</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1420.148</t>
+          <t>661.456</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-54.58</t>
+          <t>-54.96</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>360</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>11.41</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-7.76</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.21</t>
+          <t>18.08</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>19.74</v>
+        <v>19.51</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.91</v>
+        <v>20.83</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-15.51</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-125.43</t>
+          <t>-126.30</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>79566401.83523537</t>
+          <t>79466637.12606837</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>25449498.0</t>
+          <t>11765918.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>19541232</v>
+        <v>18163238.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>19684784.3</t>
+          <t>18465394.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>35922462.82</v>
+        <v>35922851.76</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-143552</t>
+          <t>-302155</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3460046.369419766</t>
+          <t>-3351368.343323668</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-2381824.930175934</t>
+          <t>-2753639.199795127</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>25449498.0</t>
+          <t>11765918.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-21.37</t>
+          <t>-22.03</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/齒輪箱.xlsx
+++ b/Result/checksun_type/齒輪箱.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-0.57</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>236.914</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>17.5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>360.254</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>17.6</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-28.20</t>
+          <t>-12.30</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-55.22</t>
+          <t>-55.47</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>237</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.77</t>
+          <t>-11.92</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.63</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>17.83</v>
+        <v>17.76</v>
       </c>
       <c r="AN2" t="n">
-        <v>20.21</v>
+        <v>20.17</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>15.41</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-126.95</t>
+          <t>-125.86</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>79466637.12606837</t>
+          <t>79362471.89829303</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>6354384.0</t>
+          <t>4158988.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>8797886.800000001</v>
+        <v>7933373.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>12253093.0</t>
+          <t>9046031.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>35217518.76</v>
+        <v>35005618.2</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-3455206</t>
+          <t>-1112657</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2735232.135433431</t>
+          <t>-2767208.292599764</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-2806314.686015621</t>
+          <t>-2943077.157014593</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>6354384.0</t>
+          <t>4158988.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-22.47</t>
+          <t>-22.91</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>17.65</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>17.45</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>17.5</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>17.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>412.077</t>
+          <t>360.254</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-23.56</t>
+          <t>-28.20</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>237</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,58 +1459,58 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>79.37</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.5</t>
+          <t>-11.77</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>17.92</v>
+        <v>17.83</v>
       </c>
       <c r="AN3" t="n">
-        <v>20.25</v>
+        <v>20.21</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.86</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>15.41</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-127.99</t>
+          <t>-126.95</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>79466637.12606837</t>
+          <t>79362471.89829303</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>7219101.0</t>
+          <t>6354384.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>9780529.199999999</v>
+        <v>8797886.800000001</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>12794246.4</t>
+          <t>12253093.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>35322706.48</v>
+        <v>35217518.76</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-3013717</t>
+          <t>-3455206</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2722308.035327579</t>
+          <t>-2735232.135433431</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-2745935.202945104</t>
+          <t>-2806314.686015621</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>7219101.0</t>
+          <t>6354384.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>473.845</t>
+          <t>412.077</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-24.46</t>
+          <t>-23.56</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-55.34</t>
+          <t>-55.22</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>237</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>61.51</t>
+          <t>79.37</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.09</t>
+          <t>-11.5</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.31</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>18.03</v>
+        <v>17.92</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.28</v>
+        <v>20.25</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>20.86</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-128.88</t>
+          <t>-127.99</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>79466637.12606837</t>
+          <t>79362471.89829303</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>8320468.0</t>
+          <t>7219101.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>11042082.6</v>
+        <v>9780529.199999999</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>14617286.1</t>
+          <t>12794246.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>35513356.96</v>
+        <v>35322706.48</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-3575203</t>
+          <t>-3013717</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-2718012.186669847</t>
+          <t>-2722308.035327579</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-2654257.934167756</t>
+          <t>-2745935.202945104</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>8320468.0</t>
+          <t>7219101.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-22.69</t>
+          <t>-22.47</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>766.683</t>
+          <t>473.845</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-34.08</t>
+          <t>-24.46</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-54.45</t>
+          <t>-55.34</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>237</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>61.51</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-10.68</t>
+          <t>-11.09</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.31</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>18.16</v>
+        <v>18.03</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.33</v>
+        <v>20.28</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>20.93</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-129.55</t>
+          <t>-128.88</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>79466637.12606837</t>
+          <t>79362471.89829303</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>13613928.0</t>
+          <t>8320468.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>10372257.8</v>
+        <v>11042082.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>15735161.0</t>
+          <t>14617286.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>35709154.84</v>
+        <v>35513356.96</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-5362903</t>
+          <t>-3575203</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-2729603.868942955</t>
+          <t>-2718012.186669847</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-2546499.088265551</t>
+          <t>-2654257.934167756</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>13613928.0</t>
+          <t>8320468.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-21.15</t>
+          <t>-22.69</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>492.348</t>
+          <t>766.683</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-35.03</t>
+          <t>-34.08</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-56.49</t>
+          <t>-54.45</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>237</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-10.33</t>
+          <t>-10.68</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>18.26</v>
+        <v>18.16</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.36</v>
+        <v>20.33</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-129.97</t>
+          <t>-129.55</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>79466637.12606837</t>
+          <t>79362471.89829303</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>8481553.0</t>
+          <t>13613928.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>10158688.6</v>
+        <v>10372257.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>15635933.7</t>
+          <t>15735161.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>36006631.54</v>
+        <v>35709154.84</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-5477245</t>
+          <t>-5362903</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-2762895.647247938</t>
+          <t>-2729603.868942955</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-2868767.912395775</t>
+          <t>-2546499.088265551</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>8481553.0</t>
+          <t>13613928.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-24.67</t>
+          <t>-21.15</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>659.489</t>
+          <t>492.348</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-35.03</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-56.36</t>
+          <t>-56.49</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,22 +3164,22 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>237</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -3189,48 +3189,48 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-9.91</t>
+          <t>-10.33</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>18.41</v>
+        <v>18.26</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.43</v>
+        <v>20.36</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-129.81</t>
+          <t>-129.97</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>79466637.12606837</t>
+          <t>79362471.89829303</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>11267596.0</t>
+          <t>8481553.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>15708299.2</v>
+        <v>10158688.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>16935768.7</t>
+          <t>15635933.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>36089158.58</v>
+        <v>36006631.54</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1227469</t>
+          <t>-5477245</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-2743646.144493785</t>
+          <t>-2762895.647247938</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-2676798.628567677</t>
+          <t>-2868767.912395775</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>11267596.0</t>
+          <t>8481553.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-24.45</t>
+          <t>-24.67</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>801.363</t>
+          <t>659.489</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-10.56</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-57.12</t>
+          <t>-56.36</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>237</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-6.94</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.91</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>18.57</v>
+        <v>18.41</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.5</v>
+        <v>20.43</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-129.41</t>
+          <t>-129.81</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>79466637.12606837</t>
+          <t>79362471.89829303</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>13526868.0</t>
+          <t>11267596.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>15807963.6</v>
+        <v>15708299.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>17674597.8</t>
+          <t>16935768.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>36309850.68</v>
+        <v>36089158.58</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1866634</t>
+          <t>-1227469</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-2755800.238298532</t>
+          <t>-2743646.144493785</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-2605461.450650116</t>
+          <t>-2676798.628567677</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>13526868.0</t>
+          <t>11267596.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-25.77</t>
+          <t>-24.45</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>16.7</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>17.15</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>16.7</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>16.85</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>286.781</t>
+          <t>801.363</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>-10.56</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-56.11</t>
+          <t>-57.12</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,17 +4024,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>237</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>13.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-7.11</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>18.77</v>
+        <v>18.57</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.58</v>
+        <v>20.5</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-9.69</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-128.75</t>
+          <t>-129.41</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>79466637.12606837</t>
+          <t>79362471.89829303</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>4971344.0</t>
+          <t>13526868.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>18192489.6</v>
+        <v>15807963.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>17817474.1</t>
+          <t>17674597.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>36286025.3</v>
+        <v>36309850.68</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>375015</t>
+          <t>-1866634</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-2783134.563325516</t>
+          <t>-2755800.238298532</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-2652563.858958956</t>
+          <t>-2605461.450650116</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>4971344.0</t>
+          <t>13526868.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-24.01</t>
+          <t>-25.77</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>17.05</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>17.15</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>17.6</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>732.465</t>
+          <t>286.781</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-56.62</t>
+          <t>-56.11</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>237</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.79</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-7.11</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>17.64</t>
+          <t>17.44</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>19</v>
+        <v>18.77</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.66</v>
+        <v>20.58</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>21.37</t>
+          <t>21.29</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-12.62</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-128.05</t>
+          <t>-128.75</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>79466637.12606837</t>
+          <t>79362471.89829303</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>12546082.0</t>
+          <t>4971344.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>21098064.2</v>
+        <v>18192489.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>19015490.5</t>
+          <t>17817474.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>36438805.22</v>
+        <v>36286025.3</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>2082573</t>
+          <t>375015</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-2806874.691392164</t>
+          <t>-2783134.563325516</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1708455.304437336</t>
+          <t>-2652563.858958956</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>12546082.0</t>
+          <t>4971344.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-24.89</t>
+          <t>-24.01</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2045.558</t>
+          <t>732.465</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-55.85</t>
+          <t>-56.62</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>237</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-7.15</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>17.93</t>
+          <t>17.64</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>19.27</v>
+        <v>19</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.75</v>
+        <v>20.66</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.37</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-12.70</t>
+          <t>-12.62</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-127.17</t>
+          <t>-128.05</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>79466637.12606837</t>
+          <t>79362471.89829303</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>36229606.0</t>
+          <t>12546082.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>21113178.8</v>
+        <v>21098064.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>19952648.9</t>
+          <t>19015490.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>36367077.28</v>
+        <v>36438805.22</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1160529</t>
+          <t>2082573</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3006587.307202132</t>
+          <t>-2806874.691392164</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1110291.608533688</t>
+          <t>-1708455.304437336</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>36229606.0</t>
+          <t>12546082.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-23.57</t>
+          <t>-24.89</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>661.456</t>
+          <t>2045.558</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-54.96</t>
+          <t>-55.85</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>237</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,22 +5329,22 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.94</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-7.15</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -5354,33 +5354,33 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>18.08</t>
+          <t>17.93</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>19.51</v>
+        <v>19.27</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.83</v>
+        <v>20.75</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-12.70</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-126.30</t>
+          <t>-127.17</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>79466637.12606837</t>
+          <t>79362471.89829303</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>11765918.0</t>
+          <t>36229606.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>18163238.2</v>
+        <v>21113178.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>18465394.1</t>
+          <t>19952648.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>35922851.76</v>
+        <v>36367077.28</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-302155</t>
+          <t>1160529</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3351368.343323668</t>
+          <t>-3006587.307202132</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-2753639.199795127</t>
+          <t>-1110291.608533688</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>11765918.0</t>
+          <t>36229606.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-22.03</t>
+          <t>-23.57</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/齒輪箱.xlsx
+++ b/Result/checksun_type/齒輪箱.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>236.914</t>
+          <t>289.07</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-12.30</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-55.47</t>
+          <t>-55.34</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>289</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.92</t>
+          <t>-11.95</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>17.56</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>17.76</v>
+        <v>17.72</v>
       </c>
       <c r="AN2" t="n">
-        <v>20.17</v>
+        <v>20.12</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-125.86</t>
+          <t>-124.70</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>79362471.89829303</t>
+          <t>79260526.45951705</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>4158988.0</t>
+          <t>5061922.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>7933373.8</v>
+        <v>6222972.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>9046031.2</t>
+          <t>8297615.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>35005618.2</v>
+        <v>34897835.5</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1112657</t>
+          <t>-2074642</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2767208.292599764</t>
+          <t>-2787255.310321109</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-2943077.157014593</t>
+          <t>-2897513.907788508</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>4158988.0</t>
+          <t>5061922.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-22.91</t>
+          <t>-22.69</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>360.254</t>
+          <t>236.914</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,102 +1338,102 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-12.30</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-02-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2024-09-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2024-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>40.65</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>39.3</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>44.9</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-55.47</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>-7.61</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>-0.57</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.31</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-28.20</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-02-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-03-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2024-09-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2024-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>40.65</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>39.3</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>44.9</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>44.0</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-55.22</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>-7.61</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>-0.28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>289</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.77</t>
+          <t>-11.92</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.63</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>17.83</v>
+        <v>17.76</v>
       </c>
       <c r="AN3" t="n">
-        <v>20.21</v>
+        <v>20.17</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>15.41</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-126.95</t>
+          <t>-125.86</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>79362471.89829303</t>
+          <t>79260526.45951705</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>6354384.0</t>
+          <t>4158988.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>8797886.800000001</v>
+        <v>7933373.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>12253093.0</t>
+          <t>9046031.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>35217518.76</v>
+        <v>35005618.2</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-3455206</t>
+          <t>-1112657</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2735232.135433431</t>
+          <t>-2767208.292599764</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-2806314.686015621</t>
+          <t>-2943077.157014593</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>6354384.0</t>
+          <t>4158988.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-22.47</t>
+          <t>-22.91</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>17.65</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>17.45</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>17.5</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>17.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>412.077</t>
+          <t>360.254</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-23.56</t>
+          <t>-28.20</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>289</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,58 +1889,58 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>79.37</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.5</t>
+          <t>-11.77</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>17.92</v>
+        <v>17.83</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.25</v>
+        <v>20.21</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.86</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>15.41</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-127.99</t>
+          <t>-126.95</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>79362471.89829303</t>
+          <t>79260526.45951705</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>7219101.0</t>
+          <t>6354384.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>9780529.199999999</v>
+        <v>8797886.800000001</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>12794246.4</t>
+          <t>12253093.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>35322706.48</v>
+        <v>35217518.76</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-3013717</t>
+          <t>-3455206</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-2722308.035327579</t>
+          <t>-2735232.135433431</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-2745935.202945104</t>
+          <t>-2806314.686015621</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>7219101.0</t>
+          <t>6354384.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>473.845</t>
+          <t>412.077</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-24.46</t>
+          <t>-23.56</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-55.34</t>
+          <t>-55.22</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>289</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>61.51</t>
+          <t>79.37</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.09</t>
+          <t>-11.5</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.31</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>18.03</v>
+        <v>17.92</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.28</v>
+        <v>20.25</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>20.86</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-128.88</t>
+          <t>-127.99</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>79362471.89829303</t>
+          <t>79260526.45951705</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>8320468.0</t>
+          <t>7219101.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>11042082.6</v>
+        <v>9780529.199999999</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>14617286.1</t>
+          <t>12794246.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>35513356.96</v>
+        <v>35322706.48</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-3575203</t>
+          <t>-3013717</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-2718012.186669847</t>
+          <t>-2722308.035327579</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-2654257.934167756</t>
+          <t>-2745935.202945104</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>8320468.0</t>
+          <t>7219101.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-22.69</t>
+          <t>-22.47</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>766.683</t>
+          <t>473.845</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-34.08</t>
+          <t>-24.46</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-54.45</t>
+          <t>-55.34</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>289</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>61.51</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-10.68</t>
+          <t>-11.09</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.31</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>18.16</v>
+        <v>18.03</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.33</v>
+        <v>20.28</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>20.93</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-129.55</t>
+          <t>-128.88</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>79362471.89829303</t>
+          <t>79260526.45951705</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>13613928.0</t>
+          <t>8320468.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>10372257.8</v>
+        <v>11042082.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>15735161.0</t>
+          <t>14617286.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>35709154.84</v>
+        <v>35513356.96</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-5362903</t>
+          <t>-3575203</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-2729603.868942955</t>
+          <t>-2718012.186669847</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-2546499.088265551</t>
+          <t>-2654257.934167756</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>13613928.0</t>
+          <t>8320468.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-21.15</t>
+          <t>-22.69</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>492.348</t>
+          <t>766.683</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-35.03</t>
+          <t>-34.08</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-56.49</t>
+          <t>-54.45</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>289</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-10.33</t>
+          <t>-10.68</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>18.26</v>
+        <v>18.16</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.36</v>
+        <v>20.33</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-129.97</t>
+          <t>-129.55</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>79362471.89829303</t>
+          <t>79260526.45951705</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>8481553.0</t>
+          <t>13613928.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>10158688.6</v>
+        <v>10372257.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>15635933.7</t>
+          <t>15735161.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>36006631.54</v>
+        <v>35709154.84</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-5477245</t>
+          <t>-5362903</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-2762895.647247938</t>
+          <t>-2729603.868942955</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-2868767.912395775</t>
+          <t>-2546499.088265551</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>8481553.0</t>
+          <t>13613928.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-24.67</t>
+          <t>-21.15</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>659.489</t>
+          <t>492.348</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-35.03</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-56.36</t>
+          <t>-56.49</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,22 +3594,22 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>289</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
@@ -3619,48 +3619,48 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-9.91</t>
+          <t>-10.33</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>18.41</v>
+        <v>18.26</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.43</v>
+        <v>20.36</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-129.81</t>
+          <t>-129.97</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>79362471.89829303</t>
+          <t>79260526.45951705</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>11267596.0</t>
+          <t>8481553.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>15708299.2</v>
+        <v>10158688.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>16935768.7</t>
+          <t>15635933.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>36089158.58</v>
+        <v>36006631.54</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1227469</t>
+          <t>-5477245</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-2743646.144493785</t>
+          <t>-2762895.647247938</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-2676798.628567677</t>
+          <t>-2868767.912395775</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>11267596.0</t>
+          <t>8481553.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-24.45</t>
+          <t>-24.67</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>801.363</t>
+          <t>659.489</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-10.56</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-57.12</t>
+          <t>-56.36</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>289</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-6.94</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.91</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>18.57</v>
+        <v>18.41</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.5</v>
+        <v>20.43</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-129.41</t>
+          <t>-129.81</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>79362471.89829303</t>
+          <t>79260526.45951705</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>13526868.0</t>
+          <t>11267596.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>15807963.6</v>
+        <v>15708299.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>17674597.8</t>
+          <t>16935768.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>36309850.68</v>
+        <v>36089158.58</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1866634</t>
+          <t>-1227469</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-2755800.238298532</t>
+          <t>-2743646.144493785</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-2605461.450650116</t>
+          <t>-2676798.628567677</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>13526868.0</t>
+          <t>11267596.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-25.77</t>
+          <t>-24.45</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>16.7</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>17.15</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>16.7</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>16.85</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>286.781</t>
+          <t>801.363</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>-10.56</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-56.11</t>
+          <t>-57.12</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,17 +4454,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>289</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>13.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-7.11</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>18.77</v>
+        <v>18.57</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.58</v>
+        <v>20.5</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-9.69</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-128.75</t>
+          <t>-129.41</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>79362471.89829303</t>
+          <t>79260526.45951705</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>4971344.0</t>
+          <t>13526868.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>18192489.6</v>
+        <v>15807963.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17817474.1</t>
+          <t>17674597.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>36286025.3</v>
+        <v>36309850.68</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>375015</t>
+          <t>-1866634</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-2783134.563325516</t>
+          <t>-2755800.238298532</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-2652563.858958956</t>
+          <t>-2605461.450650116</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>4971344.0</t>
+          <t>13526868.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-24.01</t>
+          <t>-25.77</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>17.05</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>17.15</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>17.6</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>732.465</t>
+          <t>286.781</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-56.62</t>
+          <t>-56.11</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>289</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.79</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-7.11</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>17.64</t>
+          <t>17.44</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>19</v>
+        <v>18.77</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.66</v>
+        <v>20.58</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>21.37</t>
+          <t>21.29</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-12.62</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-128.05</t>
+          <t>-128.75</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>79362471.89829303</t>
+          <t>79260526.45951705</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>12546082.0</t>
+          <t>4971344.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>21098064.2</v>
+        <v>18192489.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>19015490.5</t>
+          <t>17817474.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>36438805.22</v>
+        <v>36286025.3</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>2082573</t>
+          <t>375015</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-2806874.691392164</t>
+          <t>-2783134.563325516</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1708455.304437336</t>
+          <t>-2652563.858958956</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>12546082.0</t>
+          <t>4971344.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-24.89</t>
+          <t>-24.01</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2045.558</t>
+          <t>732.465</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-55.85</t>
+          <t>-56.62</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>289</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-7.15</t>
+          <t>-8.04</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>17.93</t>
+          <t>17.64</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>19.27</v>
+        <v>19</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.75</v>
+        <v>20.66</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.37</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-12.70</t>
+          <t>-12.62</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-127.17</t>
+          <t>-128.05</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>79362471.89829303</t>
+          <t>79260526.45951705</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>36229606.0</t>
+          <t>12546082.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>21113178.8</v>
+        <v>21098064.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>19952648.9</t>
+          <t>19015490.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>36367077.28</v>
+        <v>36438805.22</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1160529</t>
+          <t>2082573</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3006587.307202132</t>
+          <t>-2806874.691392164</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1110291.608533688</t>
+          <t>-1708455.304437336</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>36229606.0</t>
+          <t>12546082.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-23.57</t>
+          <t>-24.89</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/齒輪箱.xlsx
+++ b/Result/checksun_type/齒輪箱.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>289.07</t>
+          <t>325.585</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-31.86</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-55.34</t>
+          <t>-55.22</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>63.69</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.95</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>17.72</v>
+        <v>17.66</v>
       </c>
       <c r="AN2" t="n">
-        <v>20.12</v>
+        <v>20.07</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-124.70</t>
+          <t>-123.50</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>79260526.45951705</t>
+          <t>79160301.62978724</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>5061922.0</t>
+          <t>5734681.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>6222972.6</v>
+        <v>5705815.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>8297615.2</t>
+          <t>8373948.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>34897835.5</v>
+        <v>33871198.22</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2074642</t>
+          <t>-2668133</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2787255.310321109</t>
+          <t>-2780404.471907943</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-2897513.907788508</t>
+          <t>-2742724.860635535</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>5061922.0</t>
+          <t>5734681.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-22.69</t>
+          <t>-22.47</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>17.75</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>17.5</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>17.65</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>236.914</t>
+          <t>289.07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-12.30</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-55.47</t>
+          <t>-55.34</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.92</t>
+          <t>-11.95</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>17.56</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>17.76</v>
+        <v>17.72</v>
       </c>
       <c r="AN3" t="n">
-        <v>20.17</v>
+        <v>20.12</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-125.86</t>
+          <t>-124.70</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>79260526.45951705</t>
+          <t>79160301.62978724</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4158988.0</t>
+          <t>5061922.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>7933373.8</v>
+        <v>6222972.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>9046031.2</t>
+          <t>8297615.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>35005618.2</v>
+        <v>34897835.5</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1112657</t>
+          <t>-2074642</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2767208.292599764</t>
+          <t>-2787255.310321109</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-2943077.157014593</t>
+          <t>-2897513.907788508</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>4158988.0</t>
+          <t>5061922.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-22.91</t>
+          <t>-22.69</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>360.254</t>
+          <t>236.914</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-28.20</t>
+          <t>-12.30</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-55.22</t>
+          <t>-55.47</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.77</t>
+          <t>-11.92</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.63</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>17.83</v>
+        <v>17.76</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.21</v>
+        <v>20.17</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>15.41</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-126.95</t>
+          <t>-125.86</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>79260526.45951705</t>
+          <t>79160301.62978724</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>6354384.0</t>
+          <t>4158988.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>8797886.800000001</v>
+        <v>7933373.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>12253093.0</t>
+          <t>9046031.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>35217518.76</v>
+        <v>35005618.2</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-3455206</t>
+          <t>-1112657</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-2735232.135433431</t>
+          <t>-2767208.292599764</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-2806314.686015621</t>
+          <t>-2943077.157014593</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>6354384.0</t>
+          <t>4158988.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-22.47</t>
+          <t>-22.91</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>17.65</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>17.45</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>17.5</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>17.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>412.077</t>
+          <t>360.254</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2198,102 +2198,102 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-28.20</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-02-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2024-09-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2024-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>40.65</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>39.3</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>44.9</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-55.22</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>-7.61</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>-0.28</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-23.56</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-02-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-03-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2024-09-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2024-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>40.65</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>39.3</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>44.9</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>44.0</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-55.22</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>-7.61</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>4.46</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>1.16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>79.37</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.5</t>
+          <t>-11.77</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>17.92</v>
+        <v>17.83</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.25</v>
+        <v>20.21</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.86</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>15.41</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-127.99</t>
+          <t>-126.95</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>79260526.45951705</t>
+          <t>79160301.62978724</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>7219101.0</t>
+          <t>6354384.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>9780529.199999999</v>
+        <v>8797886.800000001</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>12794246.4</t>
+          <t>12253093.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>35322706.48</v>
+        <v>35217518.76</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-3013717</t>
+          <t>-3455206</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-2722308.035327579</t>
+          <t>-2735232.135433431</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-2745935.202945104</t>
+          <t>-2806314.686015621</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>7219101.0</t>
+          <t>6354384.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,17 +2556,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>473.845</t>
+          <t>412.077</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-24.46</t>
+          <t>-23.56</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-55.34</t>
+          <t>-55.22</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>61.51</t>
+          <t>79.37</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.01</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.09</t>
+          <t>-11.5</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.31</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>18.03</v>
+        <v>17.92</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.28</v>
+        <v>20.25</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>20.86</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-128.88</t>
+          <t>-127.99</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>79260526.45951705</t>
+          <t>79160301.62978724</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>8320468.0</t>
+          <t>7219101.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>11042082.6</v>
+        <v>9780529.199999999</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>14617286.1</t>
+          <t>12794246.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>35513356.96</v>
+        <v>35322706.48</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-3575203</t>
+          <t>-3013717</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-2718012.186669847</t>
+          <t>-2722308.035327579</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-2654257.934167756</t>
+          <t>-2745935.202945104</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>8320468.0</t>
+          <t>7219101.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-22.69</t>
+          <t>-22.47</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>766.683</t>
+          <t>473.845</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-34.08</t>
+          <t>-24.46</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-54.45</t>
+          <t>-55.34</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>61.51</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-4.01</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-10.68</t>
+          <t>-11.09</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.31</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>18.16</v>
+        <v>18.03</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.33</v>
+        <v>20.28</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>20.93</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-129.55</t>
+          <t>-128.88</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>79260526.45951705</t>
+          <t>79160301.62978724</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>13613928.0</t>
+          <t>8320468.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>10372257.8</v>
+        <v>11042082.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>15735161.0</t>
+          <t>14617286.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>35709154.84</v>
+        <v>35513356.96</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-5362903</t>
+          <t>-3575203</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-2729603.868942955</t>
+          <t>-2718012.186669847</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-2546499.088265551</t>
+          <t>-2654257.934167756</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>13613928.0</t>
+          <t>8320468.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-21.15</t>
+          <t>-22.69</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>492.348</t>
+          <t>766.683</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-35.03</t>
+          <t>-34.08</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-56.49</t>
+          <t>-54.45</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-4.98</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-10.33</t>
+          <t>-10.68</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>18.26</v>
+        <v>18.16</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.36</v>
+        <v>20.33</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-129.97</t>
+          <t>-129.55</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>79260526.45951705</t>
+          <t>79160301.62978724</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>8481553.0</t>
+          <t>13613928.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>10158688.6</v>
+        <v>10372257.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>15635933.7</t>
+          <t>15735161.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>36006631.54</v>
+        <v>35709154.84</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-5477245</t>
+          <t>-5362903</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-2762895.647247938</t>
+          <t>-2729603.868942955</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-2868767.912395775</t>
+          <t>-2546499.088265551</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>8481553.0</t>
+          <t>13613928.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-24.67</t>
+          <t>-21.15</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>659.489</t>
+          <t>492.348</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-35.03</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-56.36</t>
+          <t>-56.49</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,22 +4024,22 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
@@ -4049,48 +4049,48 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-6.94</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-9.91</t>
+          <t>-10.33</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>18.41</v>
+        <v>18.26</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.43</v>
+        <v>20.36</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-129.81</t>
+          <t>-129.97</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>79260526.45951705</t>
+          <t>79160301.62978724</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>11267596.0</t>
+          <t>8481553.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>15708299.2</v>
+        <v>10158688.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>16935768.7</t>
+          <t>15635933.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>36089158.58</v>
+        <v>36006631.54</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1227469</t>
+          <t>-5477245</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-2743646.144493785</t>
+          <t>-2762895.647247938</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-2676798.628567677</t>
+          <t>-2868767.912395775</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>11267596.0</t>
+          <t>8481553.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-24.45</t>
+          <t>-24.67</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>801.363</t>
+          <t>659.489</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-10.56</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-57.12</t>
+          <t>-56.36</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-6.94</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.91</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>18.57</v>
+        <v>18.41</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.5</v>
+        <v>20.43</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-129.41</t>
+          <t>-129.81</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>79260526.45951705</t>
+          <t>79160301.62978724</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>13526868.0</t>
+          <t>11267596.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>15807963.6</v>
+        <v>15708299.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17674597.8</t>
+          <t>16935768.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>36309850.68</v>
+        <v>36089158.58</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1866634</t>
+          <t>-1227469</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-2755800.238298532</t>
+          <t>-2743646.144493785</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-2605461.450650116</t>
+          <t>-2676798.628567677</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>13526868.0</t>
+          <t>11267596.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-25.77</t>
+          <t>-24.45</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>16.7</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
           <t>17.15</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>16.7</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>16.85</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>286.781</t>
+          <t>801.363</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>-10.56</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-56.11</t>
+          <t>-57.12</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,17 +4884,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>13.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-7.11</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>18.77</v>
+        <v>18.57</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.58</v>
+        <v>20.5</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-9.69</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-128.75</t>
+          <t>-129.41</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>79260526.45951705</t>
+          <t>79160301.62978724</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>4971344.0</t>
+          <t>13526868.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>18192489.6</v>
+        <v>15807963.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>17817474.1</t>
+          <t>17674597.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>36286025.3</v>
+        <v>36309850.68</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>375015</t>
+          <t>-1866634</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-2783134.563325516</t>
+          <t>-2755800.238298532</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-2652563.858958956</t>
+          <t>-2605461.450650116</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>4971344.0</t>
+          <t>13526868.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-24.01</t>
+          <t>-25.77</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>17.05</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>17.15</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>17.6</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>732.465</t>
+          <t>286.781</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-56.62</t>
+          <t>-56.11</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.79</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-7.11</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-8.78</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>17.64</t>
+          <t>17.44</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>19</v>
+        <v>18.77</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.66</v>
+        <v>20.58</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>21.37</t>
+          <t>21.29</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-12.62</t>
+          <t>-9.69</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-128.05</t>
+          <t>-128.75</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>79260526.45951705</t>
+          <t>79160301.62978724</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>12546082.0</t>
+          <t>4971344.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>21098064.2</v>
+        <v>18192489.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>19015490.5</t>
+          <t>17817474.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>36438805.22</v>
+        <v>36286025.3</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>2082573</t>
+          <t>375015</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-2806874.691392164</t>
+          <t>-2783134.563325516</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1708455.304437336</t>
+          <t>-2652563.858958956</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>12546082.0</t>
+          <t>4971344.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-24.89</t>
+          <t>-24.01</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/齒輪箱.xlsx
+++ b/Result/checksun_type/齒輪箱.xlsx
@@ -871,11 +871,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>1589</t>
@@ -883,12 +879,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>325.585</t>
+          <t>540.792</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +894,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +909,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-31.86</t>
+          <t>-22.70</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +979,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-55.22</t>
+          <t>-55.73</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +989,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,74 +1010,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>541</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>63.69</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-0.54</t>
-        </is>
+          <t>55.56</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-0.45</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>-11.91</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.57</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>17.66</v>
+        <v>17.61</v>
       </c>
       <c r="AN2" t="n">
-        <v>20.07</v>
+        <v>19.99</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>20.58</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.65</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.81</t>
-        </is>
+          <t>20.43</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-0.78</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1090,7 +1078,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-123.50</t>
+          <t>-122.35</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1088,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>79160301.62978724</t>
+          <t>79068359.35410765</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>5734681.0</t>
+          <t>9499370.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>5705815.2</v>
+        <v>6161869</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>8373948.9</t>
+          <t>7971199.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>33871198.22</v>
+        <v>31954701.94</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2668133</t>
+          <t>-1809330</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2780404.471907943</t>
+          <t>-2703950.357939424</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-2742724.860635535</t>
+          <t>-2283452.731112565</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>5734681.0</t>
+          <t>9499370.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1144,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-22.47</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,12 +1189,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1241,12 +1229,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1254,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1301,11 +1289,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>1589</t>
@@ -1313,12 +1297,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>289.07</t>
+          <t>325.585</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1312,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1322,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-31.86</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1397,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-55.34</t>
+          <t>-55.22</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1407,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,74 +1428,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>541</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>66.67</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>-0.89</t>
-        </is>
+          <t>63.69</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-0.54</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.95</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>17.72</v>
+        <v>17.66</v>
       </c>
       <c r="AN3" t="n">
-        <v>20.12</v>
+        <v>20.07</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>18.66</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.70</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
+          <t>20.58</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1496,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-124.70</t>
+          <t>-123.50</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1506,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>79160301.62978724</t>
+          <t>79068359.35410765</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5061922.0</t>
+          <t>5734681.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>6222972.6</v>
+        <v>5705815.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>8297615.2</t>
+          <t>8373948.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>34897835.5</v>
+        <v>33871198.22</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2074642</t>
+          <t>-2668133</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2787255.310321109</t>
+          <t>-2780404.471907943</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-2897513.907788508</t>
+          <t>-2742724.860635535</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>5061922.0</t>
+          <t>5734681.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1562,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-22.69</t>
+          <t>-22.47</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1607,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1671,12 +1647,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1672,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>17.75</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>17.5</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>17.65</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1731,11 +1707,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>1589</t>
@@ -1743,12 +1715,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>236.914</t>
+          <t>289.07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1730,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1740,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-12.30</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1815,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-55.47</t>
+          <t>-55.34</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1825,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,74 +1846,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>541</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>68.25</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-0.74</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
+          <t>66.67</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-0.89</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.92</t>
+          <t>-11.95</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>17.56</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>17.76</v>
+        <v>17.72</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.17</v>
+        <v>20.12</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>16.91</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.75</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.90</t>
-        </is>
+          <t>18.66</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0.86</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1914,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-125.86</t>
+          <t>-124.70</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1924,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>79160301.62978724</t>
+          <t>79068359.35410765</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4158988.0</t>
+          <t>5061922.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>7933373.8</v>
+        <v>6222972.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>9046031.2</t>
+          <t>8297615.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>35005618.2</v>
+        <v>34897835.5</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1112657</t>
+          <t>-2074642</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-2767208.292599764</t>
+          <t>-2787255.310321109</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-2943077.157014593</t>
+          <t>-2897513.907788508</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>4158988.0</t>
+          <t>5061922.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +1980,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-22.91</t>
+          <t>-22.69</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2025,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2101,12 +2065,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,7 +2090,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2141,7 +2105,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2161,11 +2125,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>1589</t>
@@ -2173,12 +2133,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>360.254</t>
+          <t>236.914</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2148,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2158,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-28.20</t>
+          <t>-12.30</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2233,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-55.22</t>
+          <t>-55.47</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2243,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,74 +2264,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>541</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>69.84</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-1.57</t>
-        </is>
+          <t>68.25</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.75</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.77</t>
+          <t>-11.92</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.63</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>17.83</v>
+        <v>17.76</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.21</v>
+        <v>20.17</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>15.41</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.79</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.93</t>
-        </is>
+          <t>16.91</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0.9</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2332,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-126.95</t>
+          <t>-125.86</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2342,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>79160301.62978724</t>
+          <t>79068359.35410765</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>6354384.0</t>
+          <t>4158988.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>8797886.800000001</v>
+        <v>7933373.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>12253093.0</t>
+          <t>9046031.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>35217518.76</v>
+        <v>35005618.2</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-3455206</t>
+          <t>-1112657</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-2735232.135433431</t>
+          <t>-2767208.292599764</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-2806314.686015621</t>
+          <t>-2943077.157014593</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>6354384.0</t>
+          <t>4158988.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2398,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-22.47</t>
+          <t>-22.91</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2443,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2531,12 +2483,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2508,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>17.65</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>17.45</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>17.5</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>17.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2591,11 +2543,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>1589</t>
@@ -2603,12 +2551,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>412.077</t>
+          <t>360.254</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2628,17 +2576,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-23.56</t>
+          <t>-28.20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2713,17 +2661,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2682,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>541</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,59 +2697,51 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>79.37</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0.80</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-2.55</t>
-        </is>
+          <t>69.84</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-1.57</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.5</t>
+          <t>-11.77</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>17.92</v>
+        <v>17.83</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.25</v>
+        <v>20.21</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.86</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>12.69</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.85</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.97</t>
-        </is>
+          <t>15.41</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0.93</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2750,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-127.99</t>
+          <t>-126.95</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2760,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>79160301.62978724</t>
+          <t>79068359.35410765</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>7219101.0</t>
+          <t>6354384.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>9780529.199999999</v>
+        <v>8797886.800000001</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>12794246.4</t>
+          <t>12253093.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>35322706.48</v>
+        <v>35217518.76</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-3013717</t>
+          <t>-3455206</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-2722308.035327579</t>
+          <t>-2735232.135433431</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-2745935.202945104</t>
+          <t>-2806314.686015621</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>7219101.0</t>
+          <t>6354384.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2921,7 +2861,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2901,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,17 +2926,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3021,11 +2961,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>1589</t>
@@ -3033,12 +2969,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>473.845</t>
+          <t>412.077</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +2984,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +2994,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-24.46</t>
+          <t>-23.56</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3069,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-55.34</t>
+          <t>-55.22</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3079,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,74 +3100,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>541</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>61.51</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-4.01</t>
-        </is>
+          <t>79.37</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-2.55</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.09</t>
+          <t>-11.5</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17.31</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>18.03</v>
+        <v>17.92</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.28</v>
+        <v>20.25</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>20.86</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>9.35</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.91</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-1.00</t>
-        </is>
+          <t>12.69</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0.97</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3240,7 +3168,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-128.88</t>
+          <t>-127.99</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3178,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>79160301.62978724</t>
+          <t>79068359.35410765</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>8320468.0</t>
+          <t>7219101.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>11042082.6</v>
+        <v>9780529.199999999</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>14617286.1</t>
+          <t>12794246.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>35513356.96</v>
+        <v>35322706.48</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-3575203</t>
+          <t>-3013717</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-2718012.186669847</t>
+          <t>-2722308.035327579</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-2654257.934167756</t>
+          <t>-2745935.202945104</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>8320468.0</t>
+          <t>7219101.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3234,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-22.69</t>
+          <t>-22.47</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,12 +3279,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3391,12 +3319,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3344,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3451,11 +3379,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>1589</t>
@@ -3463,12 +3387,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>766.683</t>
+          <t>473.845</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3402,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3412,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-34.08</t>
+          <t>-24.46</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3487,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-54.45</t>
+          <t>-55.34</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3497,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,74 +3518,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>541</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>45.35</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>3.77</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-4.98</t>
-        </is>
+          <t>61.51</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-4.01</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-10.68</t>
+          <t>-11.09</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.31</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>18.16</v>
+        <v>18.03</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.33</v>
+        <v>20.28</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>20.93</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>5.71</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.97</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-1.02</t>
-        </is>
+          <t>9.35</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-1</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3586,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-129.55</t>
+          <t>-128.88</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3596,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>79160301.62978724</t>
+          <t>79068359.35410765</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>13613928.0</t>
+          <t>8320468.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>10372257.8</v>
+        <v>11042082.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>15735161.0</t>
+          <t>14617286.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>35709154.84</v>
+        <v>35513356.96</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-5362903</t>
+          <t>-3575203</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-2729603.868942955</t>
+          <t>-2718012.186669847</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-2546499.088265551</t>
+          <t>-2654257.934167756</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>13613928.0</t>
+          <t>8320468.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3652,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-21.15</t>
+          <t>-22.69</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3697,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,12 +3737,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3762,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3881,11 +3797,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>1589</t>
@@ -3893,12 +3805,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>492.348</t>
+          <t>766.683</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3820,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3830,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-35.03</t>
+          <t>-34.08</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3905,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-56.49</t>
+          <t>-54.45</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +3915,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,74 +3936,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>541</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>12.01</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-6.46</t>
-        </is>
+          <t>45.35</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-4.98</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-10.33</t>
+          <t>-10.68</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>18.26</v>
+        <v>18.16</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.36</v>
+        <v>20.33</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-2.24</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-1.06</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-1.04</t>
-        </is>
+          <t>5.71</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-1.02</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4004,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-129.97</t>
+          <t>-129.55</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4014,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>79160301.62978724</t>
+          <t>79068359.35410765</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>8481553.0</t>
+          <t>13613928.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>10158688.6</v>
+        <v>10372257.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>15635933.7</t>
+          <t>15735161.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>36006631.54</v>
+        <v>35709154.84</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-5477245</t>
+          <t>-5362903</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-2762895.647247938</t>
+          <t>-2729603.868942955</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-2868767.912395775</t>
+          <t>-2546499.088265551</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>8481553.0</t>
+          <t>13613928.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4070,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-24.67</t>
+          <t>-21.15</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4115,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,12 +4155,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4180,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4227,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>659.489</t>
+          <t>492.348</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4242,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4252,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-35.03</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4327,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-56.36</t>
+          <t>-56.49</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4337,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,74 +4358,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>541</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>10.66</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-6.94</t>
-        </is>
+          <t>12.01</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-6.46</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-9.91</t>
+          <t>-10.33</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>18.41</v>
+        <v>18.26</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.43</v>
+        <v>20.36</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-5.34</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-1.09</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-1.03</t>
-        </is>
+          <t>-2.24</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-1.04</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4530,7 +4426,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-129.81</t>
+          <t>-129.97</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4436,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>79160301.62978724</t>
+          <t>79068359.35410765</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>11267596.0</t>
+          <t>8481553.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>15708299.2</v>
+        <v>10158688.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>16935768.7</t>
+          <t>15635933.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>36089158.58</v>
+        <v>36006631.54</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1227469</t>
+          <t>-5477245</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-2743646.144493785</t>
+          <t>-2762895.647247938</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-2676798.628567677</t>
+          <t>-2868767.912395775</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>11267596.0</t>
+          <t>8481553.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4492,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-24.45</t>
+          <t>-24.67</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4537,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4681,12 +4577,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4602,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4649,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>801.363</t>
+          <t>659.489</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4664,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4674,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-10.56</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4749,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-57.12</t>
+          <t>-56.36</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4759,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,74 +4780,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>541</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>4.6</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-2.26</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-7.14</t>
-        </is>
+          <t>10.66</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-6.94</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.91</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>18.57</v>
+        <v>18.41</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.5</v>
+        <v>20.43</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-8.98</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-1.11</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-1.02</t>
-        </is>
+          <t>-5.34</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-1.03</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4960,7 +4848,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-129.41</t>
+          <t>-129.81</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4858,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>79160301.62978724</t>
+          <t>79068359.35410765</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>13526868.0</t>
+          <t>11267596.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>15807963.6</v>
+        <v>15708299.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>17674597.8</t>
+          <t>16935768.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>36309850.68</v>
+        <v>36089158.58</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1866634</t>
+          <t>-1227469</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-2755800.238298532</t>
+          <t>-2743646.144493785</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-2605461.450650116</t>
+          <t>-2676798.628567677</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>13526868.0</t>
+          <t>11267596.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +4914,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-25.77</t>
+          <t>-24.45</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +4959,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5111,12 +4999,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5024,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>16.7</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>17.15</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>16.7</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>16.85</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5071,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>286.781</t>
+          <t>801.363</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5086,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5096,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>-10.56</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5171,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-56.11</t>
+          <t>-57.12</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5181,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,17 +5202,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>541</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>13.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5332,56 +5220,48 @@
           <t>4.6</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>-1.09</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>-7.11</t>
-        </is>
+      <c r="AH12" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-7.14</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>18.77</v>
+        <v>18.57</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.58</v>
+        <v>20.5</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-9.69</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-1.09</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-1.00</t>
-        </is>
+          <t>-8.98</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-1.02</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5270,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-128.75</t>
+          <t>-129.41</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5280,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>79160301.62978724</t>
+          <t>79068359.35410765</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4971344.0</t>
+          <t>13526868.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>18192489.6</v>
+        <v>15807963.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>17817474.1</t>
+          <t>17674597.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>36286025.3</v>
+        <v>36309850.68</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>375015</t>
+          <t>-1866634</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-2783134.563325516</t>
+          <t>-2755800.238298532</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-2652563.858958956</t>
+          <t>-2605461.450650116</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>4971344.0</t>
+          <t>13526868.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5336,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-24.01</t>
+          <t>-25.77</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5381,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5391,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,12 +5421,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5446,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>17.05</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>17.15</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>17.6</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/齒輪箱.xlsx
+++ b/Result/checksun_type/齒輪箱.xlsx
@@ -871,7 +871,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>1589</t>
@@ -879,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>540.792</t>
+          <t>1055.915</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -894,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -909,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-22.70</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -979,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-55.73</t>
+          <t>-57.12</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -989,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1010,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.74</v>
+        <v>-3.05</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.45</v>
+        <v>-0.88</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.91</t>
+          <t>-11.9</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.38</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>17.61</v>
+        <v>17.54</v>
       </c>
       <c r="AN2" t="n">
-        <v>19.99</v>
+        <v>19.9</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>20.48</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.62</v>
+        <v>-0.63</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.78</v>
+        <v>-0.75</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1078,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-122.35</t>
+          <t>-121.52</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1088,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>79068359.35410765</t>
+          <t>78994578.71287128</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>9499370.0</t>
+          <t>17936964.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>6161869</v>
+        <v>8478385</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>7971199.1</t>
+          <t>8638135.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>31954701.94</v>
+        <v>31544466.74</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1809330</t>
+          <t>-159750</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2703950.357939424</t>
+          <t>-2483658.975513155</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-2283452.731112565</t>
+          <t>-1272056.372168673</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>9499370.0</t>
+          <t>17936964.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1144,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.77</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1189,17 +1193,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1229,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1254,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1289,7 +1293,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>1589</t>
@@ -1297,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>325.585</t>
+          <t>540.792</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1312,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1322,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-31.86</t>
+          <t>-22.70</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1397,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-55.22</t>
+          <t>-55.73</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1407,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1428,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>63.69</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.17</v>
+        <v>-0.74</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.54</v>
+        <v>-0.45</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>-11.91</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.57</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>17.66</v>
+        <v>17.61</v>
       </c>
       <c r="AN3" t="n">
-        <v>20.07</v>
+        <v>19.99</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.65</v>
+        <v>-0.62</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.78</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1496,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-123.50</t>
+          <t>-122.35</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1506,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>79068359.35410765</t>
+          <t>78994578.71287128</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5734681.0</t>
+          <t>9499370.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>5705815.2</v>
+        <v>6161869</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>8373948.9</t>
+          <t>7971199.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>33871198.22</v>
+        <v>31954701.94</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2668133</t>
+          <t>-1809330</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2780404.471907943</t>
+          <t>-2703950.357939424</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-2742724.860635535</t>
+          <t>-2283452.731112565</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>5734681.0</t>
+          <t>9499370.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1562,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-22.47</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1607,12 +1615,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1647,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1672,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1707,7 +1715,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>1589</t>
@@ -1715,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>289.07</t>
+          <t>325.585</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1730,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1740,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-31.86</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1815,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-55.34</t>
+          <t>-55.22</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1825,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1846,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>63.69</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.06</v>
+        <v>0.17</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.89</v>
+        <v>-0.54</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.95</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>17.72</v>
+        <v>17.66</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.12</v>
+        <v>20.07</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.7</v>
+        <v>-0.65</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.86</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1914,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-124.70</t>
+          <t>-123.50</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1924,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>79068359.35410765</t>
+          <t>78994578.71287128</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>5061922.0</t>
+          <t>5734681.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>6222972.6</v>
+        <v>5705815.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>8297615.2</t>
+          <t>8373948.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>34897835.5</v>
+        <v>33871198.22</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2074642</t>
+          <t>-2668133</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-2787255.310321109</t>
+          <t>-2780404.471907943</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-2897513.907788508</t>
+          <t>-2742724.860635535</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>5061922.0</t>
+          <t>5734681.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1980,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-22.69</t>
+          <t>-22.47</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2025,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2065,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2090,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>17.75</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>17.5</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>17.65</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2125,7 +2137,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>1589</t>
@@ -2133,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>236.914</t>
+          <t>289.07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2148,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2158,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-12.30</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2233,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-55.47</t>
+          <t>-55.34</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2243,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2264,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.74</v>
+        <v>-0.06</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.75</v>
+        <v>-0.89</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.92</t>
+          <t>-11.95</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>17.56</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>17.76</v>
+        <v>17.72</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.17</v>
+        <v>20.12</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.75</v>
+        <v>-0.7</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.9</v>
+        <v>-0.86</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2332,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-125.86</t>
+          <t>-124.70</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2342,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>79068359.35410765</t>
+          <t>78994578.71287128</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4158988.0</t>
+          <t>5061922.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>7933373.8</v>
+        <v>6222972.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>9046031.2</t>
+          <t>8297615.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>35005618.2</v>
+        <v>34897835.5</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1112657</t>
+          <t>-2074642</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-2767208.292599764</t>
+          <t>-2787255.310321109</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-2943077.157014593</t>
+          <t>-2897513.907788508</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>4158988.0</t>
+          <t>5061922.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2398,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-22.91</t>
+          <t>-22.69</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2443,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2483,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2508,7 +2524,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2523,7 +2539,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2543,7 +2559,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>1589</t>
@@ -2551,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>360.254</t>
+          <t>236.914</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2566,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2576,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-28.20</t>
+          <t>-12.30</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2651,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-55.22</t>
+          <t>-55.47</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2661,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2682,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.28</v>
+        <v>-0.74</v>
       </c>
       <c r="AI6" t="n">
-        <v>-1.57</v>
+        <v>-0.75</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.77</t>
+          <t>-11.92</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.63</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>17.83</v>
+        <v>17.76</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.21</v>
+        <v>20.17</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>15.41</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.79</v>
+        <v>-0.75</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.93</v>
+        <v>-0.9</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2750,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-126.95</t>
+          <t>-125.86</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2760,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>79068359.35410765</t>
+          <t>78994578.71287128</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>6354384.0</t>
+          <t>4158988.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>8797886.800000001</v>
+        <v>7933373.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>12253093.0</t>
+          <t>9046031.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>35217518.76</v>
+        <v>35005618.2</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-3455206</t>
+          <t>-1112657</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-2735232.135433431</t>
+          <t>-2767208.292599764</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-2806314.686015621</t>
+          <t>-2943077.157014593</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>6354384.0</t>
+          <t>4158988.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2816,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-22.47</t>
+          <t>-22.91</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2861,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2901,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2926,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>17.65</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>17.45</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>17.5</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>17.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2961,7 +2981,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>1589</t>
@@ -2969,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>412.077</t>
+          <t>360.254</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2994,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-23.56</t>
+          <t>-28.20</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3079,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3100,12 +3124,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3115,51 +3139,51 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>79.37</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.8</v>
+        <v>0.28</v>
       </c>
       <c r="AI7" t="n">
-        <v>-2.55</v>
+        <v>-1.57</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.5</t>
+          <t>-11.77</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>17.92</v>
+        <v>17.83</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.25</v>
+        <v>20.21</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.86</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>15.41</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.85</v>
+        <v>-0.79</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.97</v>
+        <v>-0.93</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3168,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-127.99</t>
+          <t>-126.95</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3178,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>79068359.35410765</t>
+          <t>78994578.71287128</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>7219101.0</t>
+          <t>6354384.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>9780529.199999999</v>
+        <v>8797886.800000001</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>12794246.4</t>
+          <t>12253093.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>35322706.48</v>
+        <v>35217518.76</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-3013717</t>
+          <t>-3455206</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-2722308.035327579</t>
+          <t>-2735232.135433431</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-2745935.202945104</t>
+          <t>-2806314.686015621</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>7219101.0</t>
+          <t>6354384.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3279,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3319,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3344,17 +3368,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3379,7 +3403,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>1589</t>
@@ -3387,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>473.845</t>
+          <t>412.077</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3402,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3412,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-24.46</t>
+          <t>-23.56</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3487,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-55.34</t>
+          <t>-55.22</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3497,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3518,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>61.51</t>
+          <t>79.37</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>1.39</v>
+        <v>0.8</v>
       </c>
       <c r="AI8" t="n">
-        <v>-4.01</v>
+        <v>-2.55</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.09</t>
+          <t>-11.5</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>17.31</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>18.03</v>
+        <v>17.92</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.28</v>
+        <v>20.25</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>20.86</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.91</v>
+        <v>-0.85</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1</v>
+        <v>-0.97</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3586,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-128.88</t>
+          <t>-127.99</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3596,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>79068359.35410765</t>
+          <t>78994578.71287128</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>8320468.0</t>
+          <t>7219101.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>11042082.6</v>
+        <v>9780529.199999999</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>14617286.1</t>
+          <t>12794246.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>35513356.96</v>
+        <v>35322706.48</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-3575203</t>
+          <t>-3013717</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-2718012.186669847</t>
+          <t>-2722308.035327579</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-2654257.934167756</t>
+          <t>-2745935.202945104</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>8320468.0</t>
+          <t>7219101.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3652,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-22.69</t>
+          <t>-22.47</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3697,12 +3725,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3737,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3762,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3797,7 +3825,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>1589</t>
@@ -3805,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>766.683</t>
+          <t>473.845</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3820,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3830,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-34.08</t>
+          <t>-24.46</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3905,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-54.45</t>
+          <t>-55.34</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3915,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3936,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>61.51</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>3.77</v>
+        <v>1.39</v>
       </c>
       <c r="AI9" t="n">
-        <v>-4.98</v>
+        <v>-4.01</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-10.68</t>
+          <t>-11.09</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.31</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>18.16</v>
+        <v>18.03</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.33</v>
+        <v>20.28</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>20.93</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.97</v>
+        <v>-0.91</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1.02</v>
+        <v>-1</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4004,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-129.55</t>
+          <t>-128.88</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4014,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>79068359.35410765</t>
+          <t>78994578.71287128</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>13613928.0</t>
+          <t>8320468.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>10372257.8</v>
+        <v>11042082.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>15735161.0</t>
+          <t>14617286.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>35709154.84</v>
+        <v>35513356.96</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-5362903</t>
+          <t>-3575203</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-2729603.868942955</t>
+          <t>-2718012.186669847</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-2546499.088265551</t>
+          <t>-2654257.934167756</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>13613928.0</t>
+          <t>8320468.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4070,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-21.15</t>
+          <t>-22.69</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4115,17 +4147,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4155,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4180,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4217,7 +4249,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4227,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>492.348</t>
+          <t>766.683</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4242,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4252,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-35.03</t>
+          <t>-34.08</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4327,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-56.49</t>
+          <t>-54.45</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4337,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4358,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.12</v>
+        <v>3.77</v>
       </c>
       <c r="AI10" t="n">
-        <v>-6.46</v>
+        <v>-4.98</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-10.33</t>
+          <t>-10.68</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>18.26</v>
+        <v>18.16</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.36</v>
+        <v>20.33</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.06</v>
+        <v>-0.97</v>
       </c>
       <c r="AR10" t="n">
-        <v>-1.04</v>
+        <v>-1.02</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4426,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-129.97</t>
+          <t>-129.55</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4436,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>79068359.35410765</t>
+          <t>78994578.71287128</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>8481553.0</t>
+          <t>13613928.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>10158688.6</v>
+        <v>10372257.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>15635933.7</t>
+          <t>15735161.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>36006631.54</v>
+        <v>35709154.84</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-5477245</t>
+          <t>-5362903</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-2762895.647247938</t>
+          <t>-2729603.868942955</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-2868767.912395775</t>
+          <t>-2546499.088265551</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>8481553.0</t>
+          <t>13613928.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4492,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-24.67</t>
+          <t>-21.15</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4537,17 +4569,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4577,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4602,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4649,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>659.489</t>
+          <t>492.348</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4664,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4674,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-35.03</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4749,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-56.36</t>
+          <t>-56.49</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4759,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4780,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="AH11" t="n">
         <v>0.12</v>
       </c>
       <c r="AI11" t="n">
-        <v>-6.94</v>
+        <v>-6.46</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-9.91</t>
+          <t>-10.33</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>18.41</v>
+        <v>18.26</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.43</v>
+        <v>20.36</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.09</v>
+        <v>-1.06</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1.03</v>
+        <v>-1.04</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4848,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-129.81</t>
+          <t>-129.97</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4858,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>79068359.35410765</t>
+          <t>78994578.71287128</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>11267596.0</t>
+          <t>8481553.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>15708299.2</v>
+        <v>10158688.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>16935768.7</t>
+          <t>15635933.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>36089158.58</v>
+        <v>36006631.54</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1227469</t>
+          <t>-5477245</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-2743646.144493785</t>
+          <t>-2762895.647247938</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-2676798.628567677</t>
+          <t>-2868767.912395775</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>11267596.0</t>
+          <t>8481553.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4914,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-24.45</t>
+          <t>-24.67</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4959,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -4999,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5024,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5071,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>801.363</t>
+          <t>659.489</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5086,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5096,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-10.56</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5171,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-57.12</t>
+          <t>-56.36</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5181,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5202,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-2.26</v>
+        <v>0.12</v>
       </c>
       <c r="AI12" t="n">
-        <v>-7.14</v>
+        <v>-6.94</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.91</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>18.57</v>
+        <v>18.41</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.5</v>
+        <v>20.43</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-1.11</v>
+        <v>-1.09</v>
       </c>
       <c r="AR12" t="n">
-        <v>-1.02</v>
+        <v>-1.03</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5270,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-129.41</t>
+          <t>-129.81</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5280,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>79068359.35410765</t>
+          <t>78994578.71287128</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>13526868.0</t>
+          <t>11267596.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>15807963.6</v>
+        <v>15708299.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>17674597.8</t>
+          <t>16935768.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>36309850.68</v>
+        <v>36089158.58</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1866634</t>
+          <t>-1227469</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-2755800.238298532</t>
+          <t>-2743646.144493785</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-2605461.450650116</t>
+          <t>-2676798.628567677</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>13526868.0</t>
+          <t>11267596.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5336,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-25.77</t>
+          <t>-24.45</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5381,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5421,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5446,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>16.7</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>17.15</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>16.7</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>16.85</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/齒輪箱.xlsx
+++ b/Result/checksun_type/齒輪箱.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1055.915</t>
+          <t>404.617</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-57.12</t>
+          <t>-57.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>405</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>14.72</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-3.05</v>
+        <v>-2.09</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.88</v>
+        <v>-1.23</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.9</t>
+          <t>-11.82</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>17.54</v>
+        <v>17.48</v>
       </c>
       <c r="AN2" t="n">
-        <v>19.9</v>
+        <v>19.82</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.48</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>12.97</t>
         </is>
       </c>
       <c r="AQ2" t="n">
         <v>-0.63</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.75</v>
+        <v>-0.72</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-121.52</t>
+          <t>-120.84</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>78994578.71287128</t>
+          <t>78897466.22033899</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>17936964.0</t>
+          <t>6825956.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>8478385</v>
+        <v>9011778.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>8638135.9</t>
+          <t>8472576.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>31544466.74</v>
+        <v>31196728.32</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-159750</t>
+          <t>539202</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2483658.975513155</t>
+          <t>-2311650.381065551</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1272056.372168673</t>
+          <t>-1365603.111603733</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>17936964.0</t>
+          <t>6825956.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-25.77</t>
+          <t>-25.55</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>540.792</t>
+          <t>1055.915</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,102 +1330,102 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-1.85</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-02-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2024-09-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2024-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>40.65</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>39.3</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>44.9</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-57.12</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>-7.61</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11.42</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>-3.26</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-22.70</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-02-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-03-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2024-09-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2024-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>40.65</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>39.3</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>44.9</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>44.0</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-55.73</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>-7.61</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>5.85</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>-3.16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>405</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.74</v>
+        <v>-3.05</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.45</v>
+        <v>-0.88</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.91</t>
+          <t>-11.9</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.38</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>17.61</v>
+        <v>17.54</v>
       </c>
       <c r="AN3" t="n">
-        <v>19.99</v>
+        <v>19.9</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>20.48</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.62</v>
+        <v>-0.63</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.78</v>
+        <v>-0.75</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-122.35</t>
+          <t>-121.52</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>78994578.71287128</t>
+          <t>78897466.22033899</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>9499370.0</t>
+          <t>17936964.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>6161869</v>
+        <v>8478385</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>7971199.1</t>
+          <t>8638135.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>31954701.94</v>
+        <v>31544466.74</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1809330</t>
+          <t>-159750</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2703950.357939424</t>
+          <t>-2483658.975513155</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-2283452.731112565</t>
+          <t>-1272056.372168673</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>9499370.0</t>
+          <t>17936964.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.77</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1615,17 +1615,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>325.585</t>
+          <t>540.792</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-31.86</t>
+          <t>-22.70</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-55.22</t>
+          <t>-55.73</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>405</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>63.69</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.17</v>
+        <v>-0.74</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.54</v>
+        <v>-0.45</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>-11.91</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.57</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>17.66</v>
+        <v>17.61</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.07</v>
+        <v>19.99</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.65</v>
+        <v>-0.62</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.78</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-123.50</t>
+          <t>-122.35</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>78994578.71287128</t>
+          <t>78897466.22033899</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>5734681.0</t>
+          <t>9499370.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>5705815.2</v>
+        <v>6161869</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>8373948.9</t>
+          <t>7971199.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>33871198.22</v>
+        <v>31954701.94</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2668133</t>
+          <t>-1809330</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-2780404.471907943</t>
+          <t>-2703950.357939424</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-2742724.860635535</t>
+          <t>-2283452.731112565</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>5734681.0</t>
+          <t>9499370.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-22.47</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2037,12 +2037,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>289.07</t>
+          <t>325.585</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-31.86</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-55.34</t>
+          <t>-55.22</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>405</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>63.69</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.06</v>
+        <v>0.17</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.89</v>
+        <v>-0.54</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.95</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>17.72</v>
+        <v>17.66</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.12</v>
+        <v>20.07</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.7</v>
+        <v>-0.65</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.86</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-124.70</t>
+          <t>-123.50</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>78994578.71287128</t>
+          <t>78897466.22033899</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>5061922.0</t>
+          <t>5734681.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>6222972.6</v>
+        <v>5705815.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>8297615.2</t>
+          <t>8373948.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>34897835.5</v>
+        <v>33871198.22</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2074642</t>
+          <t>-2668133</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-2787255.310321109</t>
+          <t>-2780404.471907943</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-2897513.907788508</t>
+          <t>-2742724.860635535</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>5061922.0</t>
+          <t>5734681.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-22.69</t>
+          <t>-22.47</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>17.75</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>17.5</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>17.65</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>236.914</t>
+          <t>289.07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-12.30</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-55.47</t>
+          <t>-55.34</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>405</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-0.74</v>
+        <v>-0.06</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.75</v>
+        <v>-0.89</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.92</t>
+          <t>-11.95</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>17.56</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>17.76</v>
+        <v>17.72</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.17</v>
+        <v>20.12</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.75</v>
+        <v>-0.7</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.9</v>
+        <v>-0.86</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-125.86</t>
+          <t>-124.70</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>78994578.71287128</t>
+          <t>78897466.22033899</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4158988.0</t>
+          <t>5061922.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>7933373.8</v>
+        <v>6222972.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>9046031.2</t>
+          <t>8297615.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>35005618.2</v>
+        <v>34897835.5</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1112657</t>
+          <t>-2074642</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-2767208.292599764</t>
+          <t>-2787255.310321109</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-2943077.157014593</t>
+          <t>-2897513.907788508</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>4158988.0</t>
+          <t>5061922.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-22.91</t>
+          <t>-22.69</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>360.254</t>
+          <t>236.914</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-28.20</t>
+          <t>-12.30</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-55.22</t>
+          <t>-55.47</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>405</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.28</v>
+        <v>-0.74</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1.57</v>
+        <v>-0.75</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.77</t>
+          <t>-11.92</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.63</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>17.83</v>
+        <v>17.76</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.21</v>
+        <v>20.17</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>15.41</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.79</v>
+        <v>-0.75</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.93</v>
+        <v>-0.9</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-126.95</t>
+          <t>-125.86</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>78994578.71287128</t>
+          <t>78897466.22033899</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>6354384.0</t>
+          <t>4158988.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>8797886.800000001</v>
+        <v>7933373.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>12253093.0</t>
+          <t>9046031.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>35217518.76</v>
+        <v>35005618.2</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-3455206</t>
+          <t>-1112657</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-2735232.135433431</t>
+          <t>-2767208.292599764</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-2806314.686015621</t>
+          <t>-2943077.157014593</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>6354384.0</t>
+          <t>4158988.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-22.47</t>
+          <t>-22.91</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>17.65</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>17.45</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>17.5</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>17.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>412.077</t>
+          <t>360.254</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-23.56</t>
+          <t>-28.20</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,12 +3546,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>405</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3561,51 +3561,51 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>79.37</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.8</v>
+        <v>0.28</v>
       </c>
       <c r="AI8" t="n">
-        <v>-2.55</v>
+        <v>-1.57</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.5</t>
+          <t>-11.77</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>17.92</v>
+        <v>17.83</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.25</v>
+        <v>20.21</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.86</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>15.41</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.85</v>
+        <v>-0.79</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.97</v>
+        <v>-0.93</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-127.99</t>
+          <t>-126.95</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>78994578.71287128</t>
+          <t>78897466.22033899</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>7219101.0</t>
+          <t>6354384.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>9780529.199999999</v>
+        <v>8797886.800000001</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>12794246.4</t>
+          <t>12253093.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>35322706.48</v>
+        <v>35217518.76</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-3013717</t>
+          <t>-3455206</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-2722308.035327579</t>
+          <t>-2735232.135433431</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-2745935.202945104</t>
+          <t>-2806314.686015621</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>7219101.0</t>
+          <t>6354384.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,17 +3790,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>473.845</t>
+          <t>412.077</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-24.46</t>
+          <t>-23.56</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-55.34</t>
+          <t>-55.22</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>405</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>61.51</t>
+          <t>79.37</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.39</v>
+        <v>0.8</v>
       </c>
       <c r="AI9" t="n">
-        <v>-4.01</v>
+        <v>-2.55</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-11.09</t>
+          <t>-11.5</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>17.31</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>18.03</v>
+        <v>17.92</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.28</v>
+        <v>20.25</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>20.86</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.91</v>
+        <v>-0.85</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1</v>
+        <v>-0.97</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-128.88</t>
+          <t>-127.99</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>78994578.71287128</t>
+          <t>78897466.22033899</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>8320468.0</t>
+          <t>7219101.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>11042082.6</v>
+        <v>9780529.199999999</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>14617286.1</t>
+          <t>12794246.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>35513356.96</v>
+        <v>35322706.48</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-3575203</t>
+          <t>-3013717</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-2718012.186669847</t>
+          <t>-2722308.035327579</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-2654257.934167756</t>
+          <t>-2745935.202945104</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>8320468.0</t>
+          <t>7219101.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-22.69</t>
+          <t>-22.47</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>766.683</t>
+          <t>473.845</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-34.08</t>
+          <t>-24.46</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-54.45</t>
+          <t>-55.34</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>405</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>61.51</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>3.77</v>
+        <v>1.39</v>
       </c>
       <c r="AI10" t="n">
-        <v>-4.98</v>
+        <v>-4.01</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-10.68</t>
+          <t>-11.09</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.31</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>18.16</v>
+        <v>18.03</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.33</v>
+        <v>20.28</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>20.93</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.97</v>
+        <v>-0.91</v>
       </c>
       <c r="AR10" t="n">
-        <v>-1.02</v>
+        <v>-1</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-129.55</t>
+          <t>-128.88</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>78994578.71287128</t>
+          <t>78897466.22033899</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>13613928.0</t>
+          <t>8320468.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>10372257.8</v>
+        <v>11042082.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>15735161.0</t>
+          <t>14617286.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>35709154.84</v>
+        <v>35513356.96</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-5362903</t>
+          <t>-3575203</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-2729603.868942955</t>
+          <t>-2718012.186669847</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-2546499.088265551</t>
+          <t>-2654257.934167756</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>13613928.0</t>
+          <t>8320468.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-21.15</t>
+          <t>-22.69</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4569,17 +4569,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4671,7 +4671,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>492.348</t>
+          <t>766.683</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-5.92</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-35.03</t>
+          <t>-34.08</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-56.49</t>
+          <t>-54.45</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>405</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.12</v>
+        <v>3.77</v>
       </c>
       <c r="AI11" t="n">
-        <v>-6.46</v>
+        <v>-4.98</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-10.33</t>
+          <t>-10.68</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>18.26</v>
+        <v>18.16</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.36</v>
+        <v>20.33</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.06</v>
+        <v>-0.97</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1.04</v>
+        <v>-1.02</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-129.97</t>
+          <t>-129.55</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>78994578.71287128</t>
+          <t>78897466.22033899</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>8481553.0</t>
+          <t>13613928.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>10158688.6</v>
+        <v>10372257.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>15635933.7</t>
+          <t>15735161.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>36006631.54</v>
+        <v>35709154.84</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-5477245</t>
+          <t>-5362903</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-2762895.647247938</t>
+          <t>-2729603.868942955</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-2868767.912395775</t>
+          <t>-2546499.088265551</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>8481553.0</t>
+          <t>13613928.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-24.67</t>
+          <t>-21.15</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>659.489</t>
+          <t>492.348</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-35.03</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-56.36</t>
+          <t>-56.49</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>405</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>17.86</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="AH12" t="n">
         <v>0.12</v>
       </c>
       <c r="AI12" t="n">
-        <v>-6.94</v>
+        <v>-6.46</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-9.91</t>
+          <t>-10.33</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>17.08</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>18.41</v>
+        <v>18.26</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.43</v>
+        <v>20.36</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>21.06</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-1.09</v>
+        <v>-1.06</v>
       </c>
       <c r="AR12" t="n">
-        <v>-1.03</v>
+        <v>-1.04</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-129.81</t>
+          <t>-129.97</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>78994578.71287128</t>
+          <t>78897466.22033899</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>11267596.0</t>
+          <t>8481553.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>15708299.2</v>
+        <v>10158688.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>16935768.7</t>
+          <t>15635933.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>36089158.58</v>
+        <v>36006631.54</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1227469</t>
+          <t>-5477245</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-2743646.144493785</t>
+          <t>-2762895.647247938</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-2676798.628567677</t>
+          <t>-2868767.912395775</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>11267596.0</t>
+          <t>8481553.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-24.45</t>
+          <t>-24.67</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/齒輪箱.xlsx
+++ b/Result/checksun_type/齒輪箱.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>404.617</t>
+          <t>1265.747</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>33.03</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-57.00</t>
+          <t>-55.60</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>13.69</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>14.72</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-2.09</v>
+        <v>1.22</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1.23</v>
+        <v>-1.05</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>-11.57</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>17.48</v>
+        <v>17.42</v>
       </c>
       <c r="AN2" t="n">
-        <v>19.82</v>
+        <v>19.7</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.34</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>16.79</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.63</v>
+        <v>-0.58</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.72</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-120.84</t>
+          <t>-120.00</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>78897466.22033899</t>
+          <t>78832319.73977433</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>6825956.0</t>
+          <t>21805741.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>9011778.6</v>
+        <v>12360542.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>8472576.2</t>
+          <t>9291757.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>31196728.32</v>
+        <v>29496090.52</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>539202</t>
+          <t>3068784</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2311650.381065551</t>
+          <t>-1998082.91881211</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1365603.111603733</t>
+          <t>-273461.8764181808</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>6825956.0</t>
+          <t>21805741.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-25.55</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1193,17 +1193,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1055.915</t>
+          <t>404.617</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-57.12</t>
+          <t>-57.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>14.72</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-3.05</v>
+        <v>-2.09</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.88</v>
+        <v>-1.23</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.9</t>
+          <t>-11.82</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>17.54</v>
+        <v>17.48</v>
       </c>
       <c r="AN3" t="n">
-        <v>19.9</v>
+        <v>19.82</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.48</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>12.97</t>
         </is>
       </c>
       <c r="AQ3" t="n">
         <v>-0.63</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.75</v>
+        <v>-0.72</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-121.52</t>
+          <t>-120.84</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>78897466.22033899</t>
+          <t>78832319.73977433</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>17936964.0</t>
+          <t>6825956.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>8478385</v>
+        <v>9011778.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>8638135.9</t>
+          <t>8472576.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>31544466.74</v>
+        <v>31196728.32</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-159750</t>
+          <t>539202</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2483658.975513155</t>
+          <t>-2311650.381065551</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1272056.372168673</t>
+          <t>-1365603.111603733</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>17936964.0</t>
+          <t>6825956.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-25.77</t>
+          <t>-25.55</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>540.792</t>
+          <t>1055.915</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-22.70</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-55.73</t>
+          <t>-57.12</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.74</v>
+        <v>-3.05</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.45</v>
+        <v>-0.88</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.91</t>
+          <t>-11.9</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.38</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>17.61</v>
+        <v>17.54</v>
       </c>
       <c r="AN4" t="n">
-        <v>19.99</v>
+        <v>19.9</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>20.48</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.62</v>
+        <v>-0.63</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.78</v>
+        <v>-0.75</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-122.35</t>
+          <t>-121.52</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>78897466.22033899</t>
+          <t>78832319.73977433</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>9499370.0</t>
+          <t>17936964.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>6161869</v>
+        <v>8478385</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>7971199.1</t>
+          <t>8638135.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>31954701.94</v>
+        <v>31544466.74</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1809330</t>
+          <t>-159750</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-2703950.357939424</t>
+          <t>-2483658.975513155</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-2283452.731112565</t>
+          <t>-1272056.372168673</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>9499370.0</t>
+          <t>17936964.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.77</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2037,17 +2037,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>325.585</t>
+          <t>540.792</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-31.86</t>
+          <t>-22.70</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-55.22</t>
+          <t>-55.73</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>63.69</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.17</v>
+        <v>-0.74</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.54</v>
+        <v>-0.45</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>-11.91</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.57</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>17.66</v>
+        <v>17.61</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.07</v>
+        <v>19.99</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.65</v>
+        <v>-0.62</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.78</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-123.50</t>
+          <t>-122.35</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>78897466.22033899</t>
+          <t>78832319.73977433</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>5734681.0</t>
+          <t>9499370.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>5705815.2</v>
+        <v>6161869</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>8373948.9</t>
+          <t>7971199.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>33871198.22</v>
+        <v>31954701.94</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2668133</t>
+          <t>-1809330</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-2780404.471907943</t>
+          <t>-2703950.357939424</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-2742724.860635535</t>
+          <t>-2283452.731112565</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>5734681.0</t>
+          <t>9499370.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-22.47</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>289.07</t>
+          <t>325.585</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-31.86</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-55.34</t>
+          <t>-55.22</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>63.69</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-0.06</v>
+        <v>0.17</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.89</v>
+        <v>-0.54</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-11.95</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>17.72</v>
+        <v>17.66</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.12</v>
+        <v>20.07</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.7</v>
+        <v>-0.65</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.86</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-124.70</t>
+          <t>-123.50</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>78897466.22033899</t>
+          <t>78832319.73977433</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>5061922.0</t>
+          <t>5734681.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>6222972.6</v>
+        <v>5705815.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>8297615.2</t>
+          <t>8373948.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>34897835.5</v>
+        <v>33871198.22</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-2074642</t>
+          <t>-2668133</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-2787255.310321109</t>
+          <t>-2780404.471907943</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-2897513.907788508</t>
+          <t>-2742724.860635535</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>5061922.0</t>
+          <t>5734681.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-22.69</t>
+          <t>-22.47</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>17.75</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>17.5</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>17.65</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,42 +2993,42 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>0.29</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>289.07</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>17.55</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>-0.57</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>236.914</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>17.5</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-3.55</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-12.30</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-55.47</t>
+          <t>-55.34</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-0.74</v>
+        <v>-0.06</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.75</v>
+        <v>-0.89</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.92</t>
+          <t>-11.95</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>17.56</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>17.76</v>
+        <v>17.72</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.17</v>
+        <v>20.12</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.75</v>
+        <v>-0.7</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.9</v>
+        <v>-0.86</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-125.86</t>
+          <t>-124.70</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>78897466.22033899</t>
+          <t>78832319.73977433</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>4158988.0</t>
+          <t>5061922.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>7933373.8</v>
+        <v>6222972.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>9046031.2</t>
+          <t>8297615.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>35005618.2</v>
+        <v>34897835.5</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1112657</t>
+          <t>-2074642</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-2767208.292599764</t>
+          <t>-2787255.310321109</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-2943077.157014593</t>
+          <t>-2897513.907788508</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>4158988.0</t>
+          <t>5061922.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-22.91</t>
+          <t>-22.69</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>360.254</t>
+          <t>236.914</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-28.20</t>
+          <t>-12.30</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-55.22</t>
+          <t>-55.47</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.28</v>
+        <v>-0.74</v>
       </c>
       <c r="AI8" t="n">
-        <v>-1.57</v>
+        <v>-0.75</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.77</t>
+          <t>-11.92</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.63</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>17.83</v>
+        <v>17.76</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.21</v>
+        <v>20.17</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>15.41</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.79</v>
+        <v>-0.75</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.93</v>
+        <v>-0.9</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-126.95</t>
+          <t>-125.86</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>78897466.22033899</t>
+          <t>78832319.73977433</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>6354384.0</t>
+          <t>4158988.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>8797886.800000001</v>
+        <v>7933373.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>12253093.0</t>
+          <t>9046031.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>35217518.76</v>
+        <v>35005618.2</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-3455206</t>
+          <t>-1112657</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-2735232.135433431</t>
+          <t>-2767208.292599764</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-2806314.686015621</t>
+          <t>-2943077.157014593</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>6354384.0</t>
+          <t>4158988.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-22.47</t>
+          <t>-22.91</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>17.65</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>17.45</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>17.5</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>17.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>412.077</t>
+          <t>360.254</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-23.56</t>
+          <t>-28.20</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,12 +3968,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -3983,51 +3983,51 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>79.37</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.8</v>
+        <v>0.28</v>
       </c>
       <c r="AI9" t="n">
-        <v>-2.55</v>
+        <v>-1.57</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-11.5</t>
+          <t>-11.77</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>17.92</v>
+        <v>17.83</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.25</v>
+        <v>20.21</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.86</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>15.41</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.85</v>
+        <v>-0.79</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.97</v>
+        <v>-0.93</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-127.99</t>
+          <t>-126.95</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>78897466.22033899</t>
+          <t>78832319.73977433</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>7219101.0</t>
+          <t>6354384.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>9780529.199999999</v>
+        <v>8797886.800000001</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>12794246.4</t>
+          <t>12253093.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>35322706.48</v>
+        <v>35217518.76</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-3013717</t>
+          <t>-3455206</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-2722308.035327579</t>
+          <t>-2735232.135433431</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-2745935.202945104</t>
+          <t>-2806314.686015621</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>7219101.0</t>
+          <t>6354384.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,17 +4212,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>473.845</t>
+          <t>412.077</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-24.46</t>
+          <t>-23.56</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-55.34</t>
+          <t>-55.22</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>61.51</t>
+          <t>79.37</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>1.39</v>
+        <v>0.8</v>
       </c>
       <c r="AI10" t="n">
-        <v>-4.01</v>
+        <v>-2.55</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-11.09</t>
+          <t>-11.5</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>17.31</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>18.03</v>
+        <v>17.92</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.28</v>
+        <v>20.25</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>20.86</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.91</v>
+        <v>-0.85</v>
       </c>
       <c r="AR10" t="n">
-        <v>-1</v>
+        <v>-0.97</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-128.88</t>
+          <t>-127.99</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>78897466.22033899</t>
+          <t>78832319.73977433</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>8320468.0</t>
+          <t>7219101.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>11042082.6</v>
+        <v>9780529.199999999</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>14617286.1</t>
+          <t>12794246.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>35513356.96</v>
+        <v>35322706.48</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-3575203</t>
+          <t>-3013717</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-2718012.186669847</t>
+          <t>-2722308.035327579</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-2654257.934167756</t>
+          <t>-2745935.202945104</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>8320468.0</t>
+          <t>7219101.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-22.69</t>
+          <t>-22.47</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>766.683</t>
+          <t>473.845</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.92</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-34.08</t>
+          <t>-24.46</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-54.45</t>
+          <t>-55.34</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>61.51</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>3.77</v>
+        <v>1.39</v>
       </c>
       <c r="AI11" t="n">
-        <v>-4.98</v>
+        <v>-4.01</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-10.68</t>
+          <t>-11.09</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.31</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>18.16</v>
+        <v>18.03</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.33</v>
+        <v>20.28</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>20.93</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.97</v>
+        <v>-0.91</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1.02</v>
+        <v>-1</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-129.55</t>
+          <t>-128.88</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>78897466.22033899</t>
+          <t>78832319.73977433</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>13613928.0</t>
+          <t>8320468.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>10372257.8</v>
+        <v>11042082.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>15735161.0</t>
+          <t>14617286.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>35709154.84</v>
+        <v>35513356.96</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-5362903</t>
+          <t>-3575203</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-2729603.868942955</t>
+          <t>-2718012.186669847</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-2546499.088265551</t>
+          <t>-2654257.934167756</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>13613928.0</t>
+          <t>8320468.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-21.15</t>
+          <t>-22.69</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5093,7 +5093,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>492.348</t>
+          <t>766.683</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-35.03</t>
+          <t>-34.08</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-56.49</t>
+          <t>-54.45</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>0.12</v>
+        <v>3.77</v>
       </c>
       <c r="AI12" t="n">
-        <v>-6.46</v>
+        <v>-4.98</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-10.33</t>
+          <t>-10.68</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>18.26</v>
+        <v>18.16</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.36</v>
+        <v>20.33</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-1.06</v>
+        <v>-0.97</v>
       </c>
       <c r="AR12" t="n">
-        <v>-1.04</v>
+        <v>-1.02</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-129.97</t>
+          <t>-129.55</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>78897466.22033899</t>
+          <t>78832319.73977433</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>8481553.0</t>
+          <t>13613928.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>10158688.6</v>
+        <v>10372257.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>15635933.7</t>
+          <t>15735161.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>36006631.54</v>
+        <v>35709154.84</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-5477245</t>
+          <t>-5362903</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-2762895.647247938</t>
+          <t>-2729603.868942955</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-2868767.912395775</t>
+          <t>-2546499.088265551</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>8481553.0</t>
+          <t>13613928.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-24.67</t>
+          <t>-21.15</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/齒輪箱.xlsx
+++ b/Result/checksun_type/齒輪箱.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1265.747</t>
+          <t>368.42</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>33.03</t>
+          <t>37.29</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-55.60</t>
+          <t>-56.11</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13.69</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>368</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>1.22</v>
+        <v>0.47</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1.05</v>
+        <v>-1.17</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-11.27</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>17.42</v>
+        <v>17.37</v>
       </c>
       <c r="AN2" t="n">
-        <v>19.7</v>
+        <v>19.58</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.34</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.58</v>
+        <v>-0.55</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.66</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-120.00</t>
+          <t>-119.15</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>78832319.73977433</t>
+          <t>78734780.5056338</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>21805741.0</t>
+          <t>6386309.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>12360542.4</v>
+        <v>12490868</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>9291757.5</t>
+          <t>9098341.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>29496090.52</v>
+        <v>26165273.46</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>3068784</t>
+          <t>3392526</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1998082.91881211</t>
+          <t>-1792006.14128376</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-273461.8764181808</t>
+          <t>-658583.8648778368</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>21805741.0</t>
+          <t>6386309.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-24.01</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>404.617</t>
+          <t>1265.747</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>33.03</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-57.00</t>
+          <t>-55.60</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>13.69</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>368</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>14.72</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-2.09</v>
+        <v>1.22</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1.23</v>
+        <v>-1.05</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>-11.57</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>17.48</v>
+        <v>17.42</v>
       </c>
       <c r="AN3" t="n">
-        <v>19.82</v>
+        <v>19.7</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.34</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>16.79</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.63</v>
+        <v>-0.58</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.72</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-120.84</t>
+          <t>-120.00</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>78832319.73977433</t>
+          <t>78734780.5056338</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>6825956.0</t>
+          <t>21805741.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>9011778.6</v>
+        <v>12360542.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>8472576.2</t>
+          <t>9291757.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>31196728.32</v>
+        <v>29496090.52</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>539202</t>
+          <t>3068784</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2311650.381065551</t>
+          <t>-1998082.91881211</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1365603.111603733</t>
+          <t>-273461.8764181808</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>6825956.0</t>
+          <t>21805741.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-25.55</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,17 +1615,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1055.915</t>
+          <t>404.617</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-57.12</t>
+          <t>-57.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>368</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>14.72</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-3.05</v>
+        <v>-2.09</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.88</v>
+        <v>-1.23</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-11.9</t>
+          <t>-11.82</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>17.54</v>
+        <v>17.48</v>
       </c>
       <c r="AN4" t="n">
-        <v>19.9</v>
+        <v>19.82</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.48</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>12.97</t>
         </is>
       </c>
       <c r="AQ4" t="n">
         <v>-0.63</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.75</v>
+        <v>-0.72</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-121.52</t>
+          <t>-120.84</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>78832319.73977433</t>
+          <t>78734780.5056338</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>17936964.0</t>
+          <t>6825956.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>8478385</v>
+        <v>9011778.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>8638135.9</t>
+          <t>8472576.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>31544466.74</v>
+        <v>31196728.32</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-159750</t>
+          <t>539202</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-2483658.975513155</t>
+          <t>-2311650.381065551</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1272056.372168673</t>
+          <t>-1365603.111603733</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>17936964.0</t>
+          <t>6825956.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-25.77</t>
+          <t>-25.55</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,12 +2037,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>540.792</t>
+          <t>1055.915</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-22.70</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-55.73</t>
+          <t>-57.12</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>368</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.74</v>
+        <v>-3.05</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.45</v>
+        <v>-0.88</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-11.91</t>
+          <t>-11.9</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.38</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>17.61</v>
+        <v>17.54</v>
       </c>
       <c r="AN5" t="n">
-        <v>19.99</v>
+        <v>19.9</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>20.48</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.62</v>
+        <v>-0.63</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.78</v>
+        <v>-0.75</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-122.35</t>
+          <t>-121.52</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>78832319.73977433</t>
+          <t>78734780.5056338</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>9499370.0</t>
+          <t>17936964.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>6161869</v>
+        <v>8478385</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>7971199.1</t>
+          <t>8638135.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>31954701.94</v>
+        <v>31544466.74</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1809330</t>
+          <t>-159750</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-2703950.357939424</t>
+          <t>-2483658.975513155</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-2283452.731112565</t>
+          <t>-1272056.372168673</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>9499370.0</t>
+          <t>17936964.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.77</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,17 +2459,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>325.585</t>
+          <t>540.792</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-31.86</t>
+          <t>-22.70</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-55.22</t>
+          <t>-55.73</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>368</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>63.69</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.17</v>
+        <v>-0.74</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.54</v>
+        <v>-0.45</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>-11.91</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17.57</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>17.66</v>
+        <v>17.61</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.07</v>
+        <v>19.99</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.65</v>
+        <v>-0.62</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.78</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-123.50</t>
+          <t>-122.35</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>78832319.73977433</t>
+          <t>78734780.5056338</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>5734681.0</t>
+          <t>9499370.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>5705815.2</v>
+        <v>6161869</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>8373948.9</t>
+          <t>7971199.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>33871198.22</v>
+        <v>31954701.94</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-2668133</t>
+          <t>-1809330</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-2780404.471907943</t>
+          <t>-2703950.357939424</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-2742724.860635535</t>
+          <t>-2283452.731112565</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>5734681.0</t>
+          <t>9499370.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-22.47</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>289.07</t>
+          <t>325.585</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-31.86</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-55.34</t>
+          <t>-55.22</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>368</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>63.69</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-0.06</v>
+        <v>0.17</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.89</v>
+        <v>-0.54</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-11.95</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>17.72</v>
+        <v>17.66</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.12</v>
+        <v>20.07</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.7</v>
+        <v>-0.65</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.86</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-124.70</t>
+          <t>-123.50</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>78832319.73977433</t>
+          <t>78734780.5056338</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>5061922.0</t>
+          <t>5734681.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>6222972.6</v>
+        <v>5705815.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>8297615.2</t>
+          <t>8373948.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>34897835.5</v>
+        <v>33871198.22</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-2074642</t>
+          <t>-2668133</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-2787255.310321109</t>
+          <t>-2780404.471907943</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-2897513.907788508</t>
+          <t>-2742724.860635535</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>5061922.0</t>
+          <t>5734681.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-22.69</t>
+          <t>-22.47</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>17.75</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>17.5</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>17.65</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>236.914</t>
+          <t>289.07</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-12.30</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-55.47</t>
+          <t>-55.34</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>368</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-0.74</v>
+        <v>-0.06</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.75</v>
+        <v>-0.89</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-11.92</t>
+          <t>-11.95</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>17.56</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>17.76</v>
+        <v>17.72</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.17</v>
+        <v>20.12</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.75</v>
+        <v>-0.7</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.9</v>
+        <v>-0.86</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-125.86</t>
+          <t>-124.70</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>78832319.73977433</t>
+          <t>78734780.5056338</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4158988.0</t>
+          <t>5061922.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>7933373.8</v>
+        <v>6222972.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>9046031.2</t>
+          <t>8297615.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>35005618.2</v>
+        <v>34897835.5</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1112657</t>
+          <t>-2074642</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-2767208.292599764</t>
+          <t>-2787255.310321109</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-2943077.157014593</t>
+          <t>-2897513.907788508</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>4158988.0</t>
+          <t>5061922.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-22.91</t>
+          <t>-22.69</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>360.254</t>
+          <t>236.914</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-28.20</t>
+          <t>-12.30</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-55.22</t>
+          <t>-55.47</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>368</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.28</v>
+        <v>-0.74</v>
       </c>
       <c r="AI9" t="n">
-        <v>-1.57</v>
+        <v>-0.75</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-11.77</t>
+          <t>-11.92</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.63</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>17.83</v>
+        <v>17.76</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.21</v>
+        <v>20.17</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>15.41</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.79</v>
+        <v>-0.75</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.93</v>
+        <v>-0.9</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-126.95</t>
+          <t>-125.86</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>78832319.73977433</t>
+          <t>78734780.5056338</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>6354384.0</t>
+          <t>4158988.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>8797886.800000001</v>
+        <v>7933373.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>12253093.0</t>
+          <t>9046031.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>35217518.76</v>
+        <v>35005618.2</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-3455206</t>
+          <t>-1112657</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-2735232.135433431</t>
+          <t>-2767208.292599764</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-2806314.686015621</t>
+          <t>-2943077.157014593</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>6354384.0</t>
+          <t>4158988.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-22.47</t>
+          <t>-22.91</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>17.65</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>17.45</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>17.5</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>17.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>412.077</t>
+          <t>360.254</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-23.56</t>
+          <t>-28.20</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,12 +4390,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>368</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4405,51 +4405,51 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>79.37</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.8</v>
+        <v>0.28</v>
       </c>
       <c r="AI10" t="n">
-        <v>-2.55</v>
+        <v>-1.57</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-11.5</t>
+          <t>-11.77</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>17.92</v>
+        <v>17.83</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.25</v>
+        <v>20.21</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>20.86</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>15.41</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.85</v>
+        <v>-0.79</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.97</v>
+        <v>-0.93</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-127.99</t>
+          <t>-126.95</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>78832319.73977433</t>
+          <t>78734780.5056338</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>7219101.0</t>
+          <t>6354384.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>9780529.199999999</v>
+        <v>8797886.800000001</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>12794246.4</t>
+          <t>12253093.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>35322706.48</v>
+        <v>35217518.76</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-3013717</t>
+          <t>-3455206</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-2722308.035327579</t>
+          <t>-2735232.135433431</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-2745935.202945104</t>
+          <t>-2806314.686015621</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>7219101.0</t>
+          <t>6354384.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,17 +4634,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>473.845</t>
+          <t>412.077</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-24.46</t>
+          <t>-23.56</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-55.34</t>
+          <t>-55.22</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>368</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>61.51</t>
+          <t>79.37</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>1.39</v>
+        <v>0.8</v>
       </c>
       <c r="AI11" t="n">
-        <v>-4.01</v>
+        <v>-2.55</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-11.09</t>
+          <t>-11.5</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>17.31</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>18.03</v>
+        <v>17.92</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.28</v>
+        <v>20.25</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>20.93</t>
+          <t>20.86</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.91</v>
+        <v>-0.85</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1</v>
+        <v>-0.97</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-128.88</t>
+          <t>-127.99</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>78832319.73977433</t>
+          <t>78734780.5056338</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>8320468.0</t>
+          <t>7219101.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>11042082.6</v>
+        <v>9780529.199999999</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>14617286.1</t>
+          <t>12794246.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>35513356.96</v>
+        <v>35322706.48</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-3575203</t>
+          <t>-3013717</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-2718012.186669847</t>
+          <t>-2722308.035327579</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-2654257.934167756</t>
+          <t>-2745935.202945104</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>8320468.0</t>
+          <t>7219101.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-22.69</t>
+          <t>-22.47</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>766.683</t>
+          <t>473.845</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-34.08</t>
+          <t>-24.46</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-54.45</t>
+          <t>-55.34</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>368</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>61.51</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>3.77</v>
+        <v>1.39</v>
       </c>
       <c r="AI12" t="n">
-        <v>-4.98</v>
+        <v>-4.01</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-10.68</t>
+          <t>-11.09</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.31</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>18.16</v>
+        <v>18.03</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.33</v>
+        <v>20.28</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>20.93</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.97</v>
+        <v>-0.91</v>
       </c>
       <c r="AR12" t="n">
-        <v>-1.02</v>
+        <v>-1</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-129.55</t>
+          <t>-128.88</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>78832319.73977433</t>
+          <t>78734780.5056338</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>13613928.0</t>
+          <t>8320468.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>10372257.8</v>
+        <v>11042082.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>15735161.0</t>
+          <t>14617286.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>35709154.84</v>
+        <v>35513356.96</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-5362903</t>
+          <t>-3575203</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-2729603.868942955</t>
+          <t>-2718012.186669847</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-2546499.088265551</t>
+          <t>-2654257.934167756</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>13613928.0</t>
+          <t>8320468.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-21.15</t>
+          <t>-22.69</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/齒輪箱.xlsx
+++ b/Result/checksun_type/齒輪箱.xlsx
@@ -913,7 +913,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>503.465</t>
+          <t>1165.573</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -953,12 +953,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>33.44</t>
+          <t>20.76</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-55.60</t>
+          <t>-54.33</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,22 +1068,22 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>12.61</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1094,66 +1094,66 @@
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>71.11</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>1.57</v>
+        <v>3.16</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.99</v>
+        <v>0.2</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-10.81</t>
+          <t>-10.26</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>17.35</v>
+        <v>17.36</v>
       </c>
       <c r="AV2" t="n">
-        <v>19.45</v>
+        <v>19.35</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>20.19</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>20.88</t>
+          <t>29.08</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>-0.5</v>
+        <v>-0.42</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0.63</v>
+        <v>-0.59</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-118.20</t>
+          <t>-116.97</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1172,43 +1172,43 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>78642628.38607596</t>
+          <t>78575959.12921348</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>8809749.0</t>
+          <t>20782745.0</t>
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>12352943.8</v>
+        <v>12922100</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>9257406.4</t>
+          <t>10700242.5</t>
         </is>
       </c>
       <c r="BH2" t="n">
-        <v>21983292</v>
+        <v>21416474.36</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>3095537</t>
+          <t>2221857</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>-1628612.374959743</t>
+          <t>-1357083.894255641</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-729946.6601776518</t>
+          <t>136322.7496169191</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>8809749.0</t>
+          <t>20782745.0</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-20.93</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>368.42</t>
+          <t>503.465</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1410,17 +1410,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.29</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-56.11</t>
+          <t>-55.60</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1530,22 +1530,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1556,66 +1556,66 @@
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>71.11</t>
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>0.47</v>
+        <v>1.57</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-1.17</v>
+        <v>-0.99</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-11.27</t>
+          <t>-10.81</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>-3.40</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>17.37</v>
+        <v>17.35</v>
       </c>
       <c r="AV3" t="n">
-        <v>19.58</v>
+        <v>19.45</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.19</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>20.88</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>-0.55</v>
+        <v>-0.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.66</v>
+        <v>-0.63</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-119.15</t>
+          <t>-118.20</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1634,43 +1634,43 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>78642628.38607596</t>
+          <t>78575959.12921348</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>6386309.0</t>
+          <t>8809749.0</t>
         </is>
       </c>
       <c r="BF3" t="n">
-        <v>12490868</v>
+        <v>12352943.8</v>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>9098341.6</t>
+          <t>9257406.4</t>
         </is>
       </c>
       <c r="BH3" t="n">
-        <v>26165273.46</v>
+        <v>21983292</v>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>3392526</t>
+          <t>3095537</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-1792006.14128376</t>
+          <t>-1628612.374959743</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>-658583.8648778368</t>
+          <t>-729946.6601776518</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>6386309.0</t>
+          <t>8809749.0</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-24.01</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1800,22 +1800,22 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1265.747</t>
+          <t>368.42</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1872,142 +1872,142 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>37.29</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-02-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2024-09-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2024-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>40.65</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>39.3</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>44.9</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-56.11</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>-7.61</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025/02/18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>40.65</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>2025/11/05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>18.45</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>2025/04/07</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>31.95</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>33.03</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-02-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-03-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2024-09-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2024-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>40.65</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>39.3</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>44.9</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>44.0</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-55.60</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>-7.61</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025/02/18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>40.65</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>2025/11/05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>18.45</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>2025/04/07</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>31.95</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>13.69</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -2018,66 +2018,66 @@
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>1.22</v>
+        <v>0.47</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-1.05</v>
+        <v>-1.17</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-11.27</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>17.42</v>
+        <v>17.37</v>
       </c>
       <c r="AV4" t="n">
-        <v>19.7</v>
+        <v>19.58</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>20.34</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>-0.58</v>
+        <v>-0.55</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.66</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-120.00</t>
+          <t>-119.15</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -2096,43 +2096,43 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>78642628.38607596</t>
+          <t>78575959.12921348</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>21805741.0</t>
+          <t>6386309.0</t>
         </is>
       </c>
       <c r="BF4" t="n">
-        <v>12360542.4</v>
+        <v>12490868</v>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>9291757.5</t>
+          <t>9098341.6</t>
         </is>
       </c>
       <c r="BH4" t="n">
-        <v>29496090.52</v>
+        <v>26165273.46</v>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>3068784</t>
+          <t>3392526</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-1998082.91881211</t>
+          <t>-1792006.14128376</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>-273461.8764181808</t>
+          <t>-658583.8648778368</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>21805741.0</t>
+          <t>6386309.0</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-24.01</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2197,12 +2197,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2262,22 +2262,22 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>404.617</t>
+          <t>1265.747</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2334,17 +2334,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>33.03</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-57.00</t>
+          <t>-55.60</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2454,22 +2454,22 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>13.69</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2480,66 +2480,66 @@
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>14.72</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>-2.09</v>
+        <v>1.22</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-1.23</v>
+        <v>-1.05</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>-11.57</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>17.48</v>
+        <v>17.42</v>
       </c>
       <c r="AV5" t="n">
-        <v>19.82</v>
+        <v>19.7</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.34</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>16.79</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>-0.63</v>
+        <v>-0.58</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.72</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-120.84</t>
+          <t>-120.00</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2558,43 +2558,43 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>78642628.38607596</t>
+          <t>78575959.12921348</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>6825956.0</t>
+          <t>21805741.0</t>
         </is>
       </c>
       <c r="BF5" t="n">
-        <v>9011778.6</v>
+        <v>12360542.4</v>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>8472576.2</t>
+          <t>9291757.5</t>
         </is>
       </c>
       <c r="BH5" t="n">
-        <v>31196728.32</v>
+        <v>29496090.52</v>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>539202</t>
+          <t>3068784</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-2311650.381065551</t>
+          <t>-1998082.91881211</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-1365603.111603733</t>
+          <t>-273461.8764181808</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>6825956.0</t>
+          <t>21805741.0</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-25.55</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2659,17 +2659,17 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2724,22 +2724,22 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1055.915</t>
+          <t>404.617</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-57.12</t>
+          <t>-57.00</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2916,22 +2916,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2942,66 +2942,66 @@
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>14.72</t>
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>-3.05</v>
+        <v>-2.09</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.88</v>
+        <v>-1.23</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-11.9</t>
+          <t>-11.82</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>17.54</v>
+        <v>17.48</v>
       </c>
       <c r="AV6" t="n">
-        <v>19.9</v>
+        <v>19.82</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>20.48</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>12.97</t>
         </is>
       </c>
       <c r="AY6" t="n">
         <v>-0.63</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.75</v>
+        <v>-0.72</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-121.52</t>
+          <t>-120.84</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -3020,43 +3020,43 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>78642628.38607596</t>
+          <t>78575959.12921348</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>17936964.0</t>
+          <t>6825956.0</t>
         </is>
       </c>
       <c r="BF6" t="n">
-        <v>8478385</v>
+        <v>9011778.6</v>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>8638135.9</t>
+          <t>8472576.2</t>
         </is>
       </c>
       <c r="BH6" t="n">
-        <v>31544466.74</v>
+        <v>31196728.32</v>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>-159750</t>
+          <t>539202</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>-2483658.975513155</t>
+          <t>-2311650.381065551</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-1272056.372168673</t>
+          <t>-1365603.111603733</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>17936964.0</t>
+          <t>6825956.0</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-25.77</t>
+          <t>-25.55</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3121,12 +3121,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3186,22 +3186,22 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>540.792</t>
+          <t>1055.915</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3258,17 +3258,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-22.70</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-55.73</t>
+          <t>-57.12</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3378,22 +3378,22 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3404,66 +3404,66 @@
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>-0.74</v>
+        <v>-3.05</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.45</v>
+        <v>-0.88</v>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-11.91</t>
+          <t>-11.9</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.38</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>17.61</v>
+        <v>17.54</v>
       </c>
       <c r="AV7" t="n">
-        <v>19.99</v>
+        <v>19.9</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>20.48</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>-0.62</v>
+        <v>-0.63</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0.78</v>
+        <v>-0.75</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-122.35</t>
+          <t>-121.52</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -3482,43 +3482,43 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>78642628.38607596</t>
+          <t>78575959.12921348</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>9499370.0</t>
+          <t>17936964.0</t>
         </is>
       </c>
       <c r="BF7" t="n">
-        <v>6161869</v>
+        <v>8478385</v>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>7971199.1</t>
+          <t>8638135.9</t>
         </is>
       </c>
       <c r="BH7" t="n">
-        <v>31954701.94</v>
+        <v>31544466.74</v>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>-1809330</t>
+          <t>-159750</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-2703950.357939424</t>
+          <t>-2483658.975513155</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-2283452.731112565</t>
+          <t>-1272056.372168673</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>9499370.0</t>
+          <t>17936964.0</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.77</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3583,17 +3583,17 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3648,22 +3648,22 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>325.585</t>
+          <t>540.792</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3720,17 +3720,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-31.86</t>
+          <t>-22.70</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-55.22</t>
+          <t>-55.73</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3840,22 +3840,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3866,66 +3866,66 @@
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>63.69</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>0.17</v>
+        <v>-0.74</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.54</v>
+        <v>-0.45</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>-11.91</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>17.57</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>17.66</v>
+        <v>17.61</v>
       </c>
       <c r="AV8" t="n">
-        <v>20.07</v>
+        <v>19.99</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>-0.65</v>
+        <v>-0.62</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.78</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-123.50</t>
+          <t>-122.35</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3944,43 +3944,43 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>78642628.38607596</t>
+          <t>78575959.12921348</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>5734681.0</t>
+          <t>9499370.0</t>
         </is>
       </c>
       <c r="BF8" t="n">
-        <v>5705815.2</v>
+        <v>6161869</v>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>8373948.9</t>
+          <t>7971199.1</t>
         </is>
       </c>
       <c r="BH8" t="n">
-        <v>33871198.22</v>
+        <v>31954701.94</v>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>-2668133</t>
+          <t>-1809330</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-2780404.471907943</t>
+          <t>-2703950.357939424</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-2742724.860635535</t>
+          <t>-2283452.731112565</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>5734681.0</t>
+          <t>9499370.0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-22.47</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4110,22 +4110,22 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>289.07</t>
+          <t>325.585</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4182,17 +4182,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-31.86</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-55.34</t>
+          <t>-55.22</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4307,17 +4307,17 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -4328,66 +4328,66 @@
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>63.69</t>
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>-0.06</v>
+        <v>0.17</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.89</v>
+        <v>-0.54</v>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-11.95</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>17.72</v>
+        <v>17.66</v>
       </c>
       <c r="AV9" t="n">
-        <v>20.12</v>
+        <v>20.07</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>-0.7</v>
+        <v>-0.65</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-0.86</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-124.70</t>
+          <t>-123.50</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4406,43 +4406,43 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>78642628.38607596</t>
+          <t>78575959.12921348</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>5061922.0</t>
+          <t>5734681.0</t>
         </is>
       </c>
       <c r="BF9" t="n">
-        <v>6222972.6</v>
+        <v>5705815.2</v>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>8297615.2</t>
+          <t>8373948.9</t>
         </is>
       </c>
       <c r="BH9" t="n">
-        <v>34897835.5</v>
+        <v>33871198.22</v>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-2074642</t>
+          <t>-2668133</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-2787255.310321109</t>
+          <t>-2780404.471907943</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-2897513.907788508</t>
+          <t>-2742724.860635535</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>5061922.0</t>
+          <t>5734681.0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-22.69</t>
+          <t>-22.47</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4572,22 +4572,22 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>17.75</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
           <t>17.5</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
-        <is>
-          <t>17.65</t>
-        </is>
-      </c>
-      <c r="CN9" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
-      </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>236.914</t>
+          <t>289.07</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4644,17 +4644,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-12.30</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-55.47</t>
+          <t>-55.34</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4769,17 +4769,17 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4790,66 +4790,66 @@
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AP10" t="n">
-        <v>-0.74</v>
+        <v>-0.06</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.75</v>
+        <v>-0.89</v>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-11.92</t>
+          <t>-11.95</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>17.56</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>17.76</v>
+        <v>17.72</v>
       </c>
       <c r="AV10" t="n">
-        <v>20.17</v>
+        <v>20.12</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>-0.75</v>
+        <v>-0.7</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0.9</v>
+        <v>-0.86</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-125.86</t>
+          <t>-124.70</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4868,43 +4868,43 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>78642628.38607596</t>
+          <t>78575959.12921348</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>4158988.0</t>
+          <t>5061922.0</t>
         </is>
       </c>
       <c r="BF10" t="n">
-        <v>7933373.8</v>
+        <v>6222972.6</v>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>9046031.2</t>
+          <t>8297615.2</t>
         </is>
       </c>
       <c r="BH10" t="n">
-        <v>35005618.2</v>
+        <v>34897835.5</v>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>-1112657</t>
+          <t>-2074642</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>-2767208.292599764</t>
+          <t>-2787255.310321109</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-2943077.157014593</t>
+          <t>-2897513.907788508</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>4158988.0</t>
+          <t>5061922.0</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-22.91</t>
+          <t>-22.69</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>360.254</t>
+          <t>236.914</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5106,17 +5106,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-28.20</t>
+          <t>-12.30</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-55.22</t>
+          <t>-55.47</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -5252,66 +5252,66 @@
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AP11" t="n">
-        <v>0.28</v>
+        <v>-0.74</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.57</v>
+        <v>-0.75</v>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-11.77</t>
+          <t>-11.92</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.63</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>17.83</v>
+        <v>17.76</v>
       </c>
       <c r="AV11" t="n">
-        <v>20.21</v>
+        <v>20.17</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>15.41</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>-0.79</v>
+        <v>-0.75</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0.93</v>
+        <v>-0.9</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-126.95</t>
+          <t>-125.86</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -5330,43 +5330,43 @@
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>78642628.38607596</t>
+          <t>78575959.12921348</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>6354384.0</t>
+          <t>4158988.0</t>
         </is>
       </c>
       <c r="BF11" t="n">
-        <v>8797886.800000001</v>
+        <v>7933373.8</v>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>12253093.0</t>
+          <t>9046031.2</t>
         </is>
       </c>
       <c r="BH11" t="n">
-        <v>35217518.76</v>
+        <v>35005618.2</v>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>-3455206</t>
+          <t>-1112657</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>-2735232.135433431</t>
+          <t>-2767208.292599764</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>-2806314.686015621</t>
+          <t>-2943077.157014593</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>6354384.0</t>
+          <t>4158988.0</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-22.47</t>
+          <t>-22.91</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5496,22 +5496,22 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="CM11" t="inlineStr">
+        <is>
+          <t>17.65</t>
+        </is>
+      </c>
+      <c r="CN11" t="inlineStr">
+        <is>
+          <t>17.45</t>
+        </is>
+      </c>
+      <c r="CO11" t="inlineStr">
+        <is>
           <t>17.5</t>
-        </is>
-      </c>
-      <c r="CM11" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
-      <c r="CN11" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
-      </c>
-      <c r="CO11" t="inlineStr">
-        <is>
-          <t>17.6</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>412.077</t>
+          <t>360.254</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-23.56</t>
+          <t>-28.20</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5688,22 +5688,22 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5714,12 +5714,12 @@
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5729,51 +5729,51 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>79.37</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AP12" t="n">
-        <v>0.8</v>
+        <v>0.28</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-2.55</v>
+        <v>-1.57</v>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-11.5</t>
+          <t>-11.77</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>17.92</v>
+        <v>17.83</v>
       </c>
       <c r="AV12" t="n">
-        <v>20.25</v>
+        <v>20.21</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>20.86</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>15.41</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>-0.85</v>
+        <v>-0.79</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.97</v>
+        <v>-0.93</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-127.99</t>
+          <t>-126.95</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5792,43 +5792,43 @@
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>78642628.38607596</t>
+          <t>78575959.12921348</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>7219101.0</t>
+          <t>6354384.0</t>
         </is>
       </c>
       <c r="BF12" t="n">
-        <v>9780529.199999999</v>
+        <v>8797886.800000001</v>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>12794246.4</t>
+          <t>12253093.0</t>
         </is>
       </c>
       <c r="BH12" t="n">
-        <v>35322706.48</v>
+        <v>35217518.76</v>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>-3013717</t>
+          <t>-3455206</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>-2722308.035327579</t>
+          <t>-2735232.135433431</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>-2745935.202945104</t>
+          <t>-2806314.686015621</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>7219101.0</t>
+          <t>6354384.0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -5958,17 +5958,17 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">

--- a/Result/checksun_type/齒輪箱.xlsx
+++ b/Result/checksun_type/齒輪箱.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR12"/>
+  <dimension ref="A1:CV12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,345 +566,365 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>MA_death_cross_d</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_hist_diff</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>MACD_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -1048,325 +1068,345 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>2025/11/05</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>18.45</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>31.95</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>22.35</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>12.61</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>2.94</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>1166</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>77.78</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AT2" t="n">
         <v>3.16</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AU2" t="n">
         <v>0.2</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>-10.26</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>-3.87</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>17.4</t>
         </is>
       </c>
-      <c r="AU2" t="n">
+      <c r="AY2" t="n">
         <v>17.36</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>19.35</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>20.13</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>29.08</t>
         </is>
       </c>
-      <c r="AY2" t="n">
+      <c r="BC2" t="n">
         <v>-0.42</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BD2" t="n">
         <v>-0.59</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>-116.97</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>78575959.12921348</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>20782745.0</t>
         </is>
       </c>
-      <c r="BF2" t="n">
+      <c r="BJ2" t="n">
         <v>12922100</v>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>10700242.5</t>
         </is>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>21416474.36</v>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>2221857</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>-1357083.894255641</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>136322.7496169191</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>20782745.0</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
         <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>-20.93</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>-5.144408598338474</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>-0.037516559435726</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>14.85780924490866</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>0.31</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
         <is>
           <t>15.74</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
         <is>
           <t>7.87%</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>-5.22%</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>42.22</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>2749</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>再生能源類鑄件45.14%、其他鑄件30.51%、注塑機鑄件24.35% (2024年)</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>永冠-KY-電機機械-上市</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>17.45</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>18.15</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>17.25</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>17.95</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>58.42</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>** 電機機械 - 鋼鑄鐵元件** 風力發電 - 齒輪箱、其他配件、風場開發** 能源元件 - 原材料</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1510,325 +1550,345 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>2025/11/05</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>18.45</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>31.95</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>22.35</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>5.45</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>5.45</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>1166</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>80.0</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>71.11</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="AT3" t="n">
         <v>1.57</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AU3" t="n">
         <v>-0.99</v>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>-10.81</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>-3.66</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>17.18</t>
         </is>
       </c>
-      <c r="AU3" t="n">
+      <c r="AY3" t="n">
         <v>17.35</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AZ3" t="n">
         <v>19.45</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>20.19</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>20.88</t>
         </is>
       </c>
-      <c r="AY3" t="n">
+      <c r="BC3" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BD3" t="n">
         <v>-0.63</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>-118.20</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>78575959.12921348</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>8809749.0</t>
         </is>
       </c>
-      <c r="BF3" t="n">
+      <c r="BJ3" t="n">
         <v>12352943.8</v>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>9257406.4</t>
         </is>
       </c>
-      <c r="BH3" t="n">
+      <c r="BL3" t="n">
         <v>21983292</v>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>3095537</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>-1628612.374959743</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-729946.6601776518</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>8809749.0</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
         <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>-23.13</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>-5.144408598338474</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>-0.037516559435726</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>14.85780924490866</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>0.30</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
         <is>
           <t>15.74</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
         <is>
           <t>7.87%</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>-5.22%</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>42.22</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>2749</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>再生能源類鑄件45.14%、其他鑄件30.51%、注塑機鑄件24.35% (2024年)</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>永冠-KY-電機機械-上市</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>17.3</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>17.65</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>17.25</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>17.45</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>58.42</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>** 電機機械 - 鋼鑄鐵元件** 風力發電 - 齒輪箱、其他配件、風場開發** 能源元件 - 原材料</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1972,325 +2032,345 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>2025/11/05</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>18.45</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>31.95</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>22.35</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>3.99</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>-1.73</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>1166</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>53.33</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>46.67</t>
         </is>
       </c>
-      <c r="AP4" t="n">
+      <c r="AT4" t="n">
         <v>0.47</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AU4" t="n">
         <v>-1.17</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>-11.27</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>-3.40</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>17.17</t>
         </is>
       </c>
-      <c r="AU4" t="n">
+      <c r="AY4" t="n">
         <v>17.37</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AZ4" t="n">
         <v>19.58</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>20.27</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>17.78</t>
         </is>
       </c>
-      <c r="AY4" t="n">
+      <c r="BC4" t="n">
         <v>-0.55</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BD4" t="n">
         <v>-0.66</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>-119.15</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>78575959.12921348</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>6386309.0</t>
         </is>
       </c>
-      <c r="BF4" t="n">
+      <c r="BJ4" t="n">
         <v>12490868</v>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>9098341.6</t>
         </is>
       </c>
-      <c r="BH4" t="n">
+      <c r="BL4" t="n">
         <v>26165273.46</v>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>3392526</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>-1792006.14128376</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-658583.8648778368</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>6386309.0</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
         <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>-24.01</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>-5.144408598338474</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>-0.037516559435726</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>14.85780924490866</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>0.30</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
         <is>
           <t>15.74</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
         <is>
           <t>7.87%</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>-5.22%</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>42.22</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>2749</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>再生能源類鑄件45.14%、其他鑄件30.51%、注塑機鑄件24.35% (2024年)</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>永冠-KY-電機機械-上市</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>17.6</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>17.7</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>17.1</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>17.25</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>58.42</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>** 電機機械 - 鋼鑄鐵元件** 風力發電 - 齒輪箱、其他配件、風場開發** 能源元件 - 原材料</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2434,325 +2514,345 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>2025/11/05</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>18.45</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>31.95</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>22.35</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>13.69</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>2.97</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>1166</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>80.0</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>28.89</t>
         </is>
       </c>
-      <c r="AP5" t="n">
+      <c r="AT5" t="n">
         <v>1.22</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AU5" t="n">
         <v>-1.05</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>-11.57</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>-3.13</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>17.24</t>
         </is>
       </c>
-      <c r="AU5" t="n">
+      <c r="AY5" t="n">
         <v>17.42</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AZ5" t="n">
         <v>19.7</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>20.34</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>16.79</t>
         </is>
       </c>
-      <c r="AY5" t="n">
+      <c r="BC5" t="n">
         <v>-0.58</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BD5" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>-120.00</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>78575959.12921348</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>21805741.0</t>
         </is>
       </c>
-      <c r="BF5" t="n">
+      <c r="BJ5" t="n">
         <v>12360542.4</v>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>9291757.5</t>
         </is>
       </c>
-      <c r="BH5" t="n">
+      <c r="BL5" t="n">
         <v>29496090.52</v>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>3068784</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>-1998082.91881211</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-273461.8764181808</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>21805741.0</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
         <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>-23.13</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>-5.144408598338474</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>-0.037516559435726</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>14.85780924490866</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>價漲量增</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>0.30</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
         <is>
           <t>15.74</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
         <is>
           <t>7.87%</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>-5.22%</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>42.22</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>2749</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>再生能源類鑄件45.14%、其他鑄件30.51%、注塑機鑄件24.35% (2024年)</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>永冠-KY-電機機械-上市</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>16.9</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>17.5</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>16.9</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>17.45</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>58.42</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>** 電機機械 - 鋼鑄鐵元件** 風力發電 - 齒輪箱、其他配件、風場開發** 能源元件 - 原材料</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2896,325 +2996,345 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>2025/11/05</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>18.45</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>31.95</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>22.35</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>4.38</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>0.62</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>1166</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>6.67</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>14.72</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="AT6" t="n">
         <v>-2.09</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AU6" t="n">
         <v>-1.23</v>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>-11.82</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>-2.87</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>17.26</t>
         </is>
       </c>
-      <c r="AU6" t="n">
+      <c r="AY6" t="n">
         <v>17.48</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AZ6" t="n">
         <v>19.82</v>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>20.4</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>12.97</t>
         </is>
       </c>
-      <c r="AY6" t="n">
+      <c r="BC6" t="n">
         <v>-0.63</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BD6" t="n">
         <v>-0.72</v>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>-120.84</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>78575959.12921348</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>6825956.0</t>
         </is>
       </c>
-      <c r="BF6" t="n">
+      <c r="BJ6" t="n">
         <v>9011778.6</v>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>8472576.2</t>
         </is>
       </c>
-      <c r="BH6" t="n">
+      <c r="BL6" t="n">
         <v>31196728.32</v>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>539202</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-2311650.381065551</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-1365603.111603733</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>6825956.0</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
         <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>-25.55</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>-5.144408598338474</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CA6" t="inlineStr">
         <is>
           <t>-0.037516559435726</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>14.85780924490866</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>0.29</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
         <is>
           <t>15.74</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
         <is>
           <t>7.87%</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>-5.22%</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>42.22</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>2749</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>再生能源類鑄件45.14%、其他鑄件30.51%、注塑機鑄件24.35% (2024年)</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>永冠-KY-電機機械-上市</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>17.1</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>17.1</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>16.6</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>16.9</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>58.42</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>** 電機機械 - 鋼鑄鐵元件** 風力發電 - 齒輪箱、其他配件、風場開發** 能源元件 - 原材料</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3358,325 +3478,345 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>2025/11/05</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>18.45</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>31.95</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>22.35</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>11.42</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>-3.26</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>1166</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>33.33</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AT7" t="n">
         <v>-3.05</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AU7" t="n">
         <v>-0.88</v>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>-11.9</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>-2.80</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>17.38</t>
         </is>
       </c>
-      <c r="AU7" t="n">
+      <c r="AY7" t="n">
         <v>17.54</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AZ7" t="n">
         <v>19.9</v>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>20.48</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>15.58</t>
         </is>
       </c>
-      <c r="AY7" t="n">
+      <c r="BC7" t="n">
         <v>-0.63</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BD7" t="n">
         <v>-0.75</v>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>-121.52</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>78575959.12921348</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>17936964.0</t>
         </is>
       </c>
-      <c r="BF7" t="n">
+      <c r="BJ7" t="n">
         <v>8478385</v>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>8638135.9</t>
         </is>
       </c>
-      <c r="BH7" t="n">
+      <c r="BL7" t="n">
         <v>31544466.74</v>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>-159750</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-2483658.975513155</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-1272056.372168673</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>17936964.0</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
         <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>-25.77</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>-5.144408598338474</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>-0.037516559435726</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>14.85780924490866</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>價跌量增</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>0.29</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
         <is>
           <t>15.74</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
         <is>
           <t>7.87%</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>-5.22%</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>42.22</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>2749</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>再生能源類鑄件45.14%、其他鑄件30.51%、注塑機鑄件24.35% (2024年)</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>永冠-KY-電機機械-上市</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>17.4</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>17.4</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>16.85</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>16.85</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>58.42</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>** 電機機械 - 鋼鑄鐵元件** 風力發電 - 齒輪箱、其他配件、風場開發** 能源元件 - 原材料</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3820,325 +3960,345 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
           <t>2025/11/05</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>18.45</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>31.95</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>22.35</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>5.85</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>-3.16</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr">
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>1166</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>37.5</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>55.56</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AT8" t="n">
         <v>-0.74</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AU8" t="n">
         <v>-0.45</v>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>-11.91</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>-2.70</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>17.53</t>
         </is>
       </c>
-      <c r="AU8" t="n">
+      <c r="AY8" t="n">
         <v>17.61</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AZ8" t="n">
         <v>19.99</v>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>20.54</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>20.43</t>
         </is>
       </c>
-      <c r="AY8" t="n">
+      <c r="BC8" t="n">
         <v>-0.62</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BD8" t="n">
         <v>-0.78</v>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>-122.35</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>78575959.12921348</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>9499370.0</t>
         </is>
       </c>
-      <c r="BF8" t="n">
+      <c r="BJ8" t="n">
         <v>6161869</v>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>7971199.1</t>
         </is>
       </c>
-      <c r="BH8" t="n">
+      <c r="BL8" t="n">
         <v>31954701.94</v>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>-1809330</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-2703950.357939424</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-2283452.731112565</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>9499370.0</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
         <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>-23.35</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>-5.144408598338474</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>-0.037516559435726</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>14.85780924490866</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>0.30</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
         <is>
           <t>15.74</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
         <is>
           <t>7.87%</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>-5.22%</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>42.22</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>2749</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>再生能源類鑄件45.14%、其他鑄件30.51%、注塑機鑄件24.35% (2024年)</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>永冠-KY-電機機械-上市</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CL8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>17.65</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>18.0</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>17.35</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>17.4</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>58.42</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>** 電機機械 - 鋼鑄鐵元件** 風力發電 - 齒輪箱、其他配件、風場開發** 能源元件 - 原材料</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4282,325 +4442,345 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>2025/11/05</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>18.45</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>31.95</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>22.35</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>3.52</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>-0.28</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>1166</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>62.5</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>63.69</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AT9" t="n">
         <v>0.17</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AU9" t="n">
         <v>-0.54</v>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>-12.0</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>-2.58</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>17.57</t>
         </is>
       </c>
-      <c r="AU9" t="n">
+      <c r="AY9" t="n">
         <v>17.66</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AZ9" t="n">
         <v>20.07</v>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>20.6</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>20.58</t>
         </is>
       </c>
-      <c r="AY9" t="n">
+      <c r="BC9" t="n">
         <v>-0.65</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BD9" t="n">
         <v>-0.8100000000000001</v>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>-123.50</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>78575959.12921348</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>5734681.0</t>
         </is>
       </c>
-      <c r="BF9" t="n">
+      <c r="BJ9" t="n">
         <v>5705815.2</v>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>8373948.9</t>
         </is>
       </c>
-      <c r="BH9" t="n">
+      <c r="BL9" t="n">
         <v>33871198.22</v>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>-2668133</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>-2780404.471907943</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-2742724.860635535</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>5734681.0</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
         <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>-22.47</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>-5.144408598338474</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>-0.037516559435726</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>14.85780924490866</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>0.30</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
         <is>
           <t>15.74</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
         <is>
           <t>7.87%</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>-5.22%</t>
         </is>
       </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>42.22</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>2749</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>再生能源類鑄件45.14%、其他鑄件30.51%、注塑機鑄件24.35% (2024年)</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>永冠-KY-電機機械-上市</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>17.6</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>17.75</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>17.5</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>17.6</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>58.42</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>** 電機機械 - 鋼鑄鐵元件** 風力發電 - 齒輪箱、其他配件、風場開發** 能源元件 - 原材料</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4744,325 +4924,345 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>2025/11/05</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>18.45</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>31.95</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>22.35</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>3.13</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr">
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>1166</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>66.67</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>66.67</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="AT10" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AU10" t="n">
         <v>-0.89</v>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>-11.95</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>-2.62</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>17.56</t>
         </is>
       </c>
-      <c r="AU10" t="n">
+      <c r="AY10" t="n">
         <v>17.72</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AZ10" t="n">
         <v>20.12</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>20.66</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>18.66</t>
         </is>
       </c>
-      <c r="AY10" t="n">
+      <c r="BC10" t="n">
         <v>-0.7</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BD10" t="n">
         <v>-0.86</v>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>-124.70</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>78575959.12921348</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>5061922.0</t>
         </is>
       </c>
-      <c r="BF10" t="n">
+      <c r="BJ10" t="n">
         <v>6222972.6</v>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>8297615.2</t>
         </is>
       </c>
-      <c r="BH10" t="n">
+      <c r="BL10" t="n">
         <v>34897835.5</v>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>-2074642</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>-2787255.310321109</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-2897513.907788508</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>5061922.0</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
         <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>-22.69</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>-5.144408598338474</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>-0.037516559435726</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>14.85780924490866</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>0.30</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
         <is>
           <t>15.74</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
         <is>
           <t>7.87%</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>-5.22%</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>42.22</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>2749</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>再生能源類鑄件45.14%、其他鑄件30.51%、注塑機鑄件24.35% (2024年)</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>永冠-KY-電機機械-上市</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>17.5</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>17.65</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>17.45</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>17.55</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>58.42</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>** 電機機械 - 鋼鑄鐵元件** 風力發電 - 齒輪箱、其他配件、風場開發** 能源元件 - 原材料</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5206,325 +5406,345 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>2025/11/05</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>18.45</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>31.95</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>22.35</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>2.56</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>-0.57</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr">
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>1166</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>61.9</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>68.25</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="AT11" t="n">
         <v>-0.74</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AU11" t="n">
         <v>-0.75</v>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>-11.92</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>-2.68</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>17.63</t>
         </is>
       </c>
-      <c r="AU11" t="n">
+      <c r="AY11" t="n">
         <v>17.76</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
         <v>20.17</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>20.72</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>16.91</t>
         </is>
       </c>
-      <c r="AY11" t="n">
+      <c r="BC11" t="n">
         <v>-0.75</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BD11" t="n">
         <v>-0.9</v>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>-125.86</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>78575959.12921348</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>4158988.0</t>
         </is>
       </c>
-      <c r="BF11" t="n">
+      <c r="BJ11" t="n">
         <v>7933373.8</v>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>9046031.2</t>
         </is>
       </c>
-      <c r="BH11" t="n">
+      <c r="BL11" t="n">
         <v>35005618.2</v>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>-1112657</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>-2767208.292599764</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-2943077.157014593</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>4158988.0</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
         <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>-22.91</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>-5.144408598338474</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>-0.037516559435726</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>14.85780924490866</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>0.30</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
         <is>
           <t>15.74</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
         <is>
           <t>7.87%</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>-5.22%</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>42.22</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>2749</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>再生能源類鑄件45.14%、其他鑄件30.51%、注塑機鑄件24.35% (2024年)</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>永冠-KY-電機機械-上市</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>17.6</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>17.65</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>17.45</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>17.5</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>58.42</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>** 電機機械 - 鋼鑄鐵元件** 風力發電 - 齒輪箱、其他配件、風場開發** 能源元件 - 原材料</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5668,325 +5888,345 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>2025/11/05</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>18.45</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>2025/04/07</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>31.95</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>22.35</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>3.90</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>-0.28</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr">
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>1166</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>71.43</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>69.84</t>
         </is>
       </c>
-      <c r="AP12" t="n">
+      <c r="AT12" t="n">
         <v>0.28</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AU12" t="n">
         <v>-1.57</v>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AV12" t="inlineStr">
         <is>
           <t>-11.77</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>-2.81</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>17.55</t>
         </is>
       </c>
-      <c r="AU12" t="n">
+      <c r="AY12" t="n">
         <v>17.83</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AZ12" t="n">
         <v>20.21</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>20.79</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>15.41</t>
         </is>
       </c>
-      <c r="AY12" t="n">
+      <c r="BC12" t="n">
         <v>-0.79</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BD12" t="n">
         <v>-0.93</v>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>-126.95</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>78575959.12921348</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>6354384.0</t>
         </is>
       </c>
-      <c r="BF12" t="n">
+      <c r="BJ12" t="n">
         <v>8797886.800000001</v>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>12253093.0</t>
         </is>
       </c>
-      <c r="BH12" t="n">
+      <c r="BL12" t="n">
         <v>35217518.76</v>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>-3455206</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>-2735232.135433431</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-2806314.686015621</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>6354384.0</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
         <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>-22.47</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>永冠-KY</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>-5.144408598338474</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
         <is>
           <t>-0.037516559435726</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>14.85780924490866</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CE12" t="inlineStr">
         <is>
           <t>0.30</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
         <is>
           <t>15.74</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CI12" t="inlineStr">
         <is>
           <t>7.87%</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>-5.22%</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>42.22</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
         <is>
           <t>2749</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CM12" t="inlineStr">
         <is>
           <t>再生能源類鑄件45.14%、其他鑄件30.51%、注塑機鑄件24.35% (2024年)</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CN12" t="inlineStr">
         <is>
           <t>永冠-KY-電機機械-上市</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="CL12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>17.5</t>
         </is>
       </c>
-      <c r="CM12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>17.8</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>17.45</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>17.6</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>58.42</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>** 電機機械 - 鋼鑄鐵元件** 風力發電 - 齒輪箱、其他配件、風場開發** 能源元件 - 原材料</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/齒輪箱.xlsx
+++ b/Result/checksun_type/齒輪箱.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1165.573</t>
+          <t>1300.307</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>28.09</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-54.33</t>
+          <t>-56.11</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>12.61</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,66 +1134,66 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>72.12</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>3.16</v>
+        <v>-1.26</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.2</v>
+        <v>0.63</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-10.26</t>
+          <t>-9.72</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="AY2" t="n">
         <v>17.36</v>
       </c>
       <c r="AZ2" t="n">
-        <v>19.35</v>
+        <v>19.23</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>26.74</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-0.42</v>
+        <v>-0.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.59</v>
+        <v>-0.55</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-116.97</t>
+          <t>-115.90</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>78575959.12921348</t>
+          <t>78513049.03085554</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>20782745.0</t>
+          <t>22480706.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>12922100</v>
+        <v>16053050</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>10700242.5</t>
+          <t>12532414.3</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>21416474.36</v>
+        <v>20840577.04</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>2221857</t>
+          <t>3520635</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-1357083.894255641</t>
+          <t>-1014970.934718974</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>136322.7496169191</t>
+          <t>866650.3427326959</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>20782745.0</t>
+          <t>22480706.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-20.93</t>
+          <t>-24.01</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1313,17 +1313,17 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.48</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
           <t>17.25</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>17.95</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>503.465</t>
+          <t>1165.573</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>33.44</t>
+          <t>20.76</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-55.60</t>
+          <t>-54.33</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>12.61</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,66 +1616,66 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>71.11</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>1.57</v>
+        <v>3.16</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.99</v>
+        <v>0.2</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-10.81</t>
+          <t>-10.26</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>17.35</v>
+        <v>17.36</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19.45</v>
+        <v>19.35</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>20.19</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>20.88</t>
+          <t>29.08</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-0.5</v>
+        <v>-0.42</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.63</v>
+        <v>-0.59</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-118.20</t>
+          <t>-116.97</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>78575959.12921348</t>
+          <t>78513049.03085554</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>8809749.0</t>
+          <t>20782745.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>12352943.8</v>
+        <v>12922100</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>9257406.4</t>
+          <t>10700242.5</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>21983292</v>
+        <v>21416474.36</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>3095537</t>
+          <t>2221857</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-1628612.374959743</t>
+          <t>-1357083.894255641</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-729946.6601776518</t>
+          <t>136322.7496169191</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>8809749.0</t>
+          <t>20782745.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-20.93</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.48</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,12 +1860,12 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>368.42</t>
+          <t>503.465</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>37.29</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-56.11</t>
+          <t>-55.60</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,66 +2098,66 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>71.11</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>0.47</v>
+        <v>1.57</v>
       </c>
       <c r="AU4" t="n">
-        <v>-1.17</v>
+        <v>-0.99</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-11.27</t>
+          <t>-10.81</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-3.40</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>17.37</v>
+        <v>17.35</v>
       </c>
       <c r="AZ4" t="n">
-        <v>19.58</v>
+        <v>19.45</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.19</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>20.88</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-0.55</v>
+        <v>-0.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.66</v>
+        <v>-0.63</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-119.15</t>
+          <t>-118.20</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>78575959.12921348</t>
+          <t>78513049.03085554</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>6386309.0</t>
+          <t>8809749.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>12490868</v>
+        <v>12352943.8</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>9098341.6</t>
+          <t>9257406.4</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>26165273.46</v>
+        <v>21983292</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>3392526</t>
+          <t>3095537</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-1792006.14128376</t>
+          <t>-1628612.374959743</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-658583.8648778368</t>
+          <t>-729946.6601776518</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>6386309.0</t>
+          <t>8809749.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-24.01</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.48</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1265.747</t>
+          <t>368.42</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>33.03</t>
+          <t>37.29</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-55.60</t>
+          <t>-56.11</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>13.69</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,66 +2580,66 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>1.22</v>
+        <v>0.47</v>
       </c>
       <c r="AU5" t="n">
-        <v>-1.05</v>
+        <v>-1.17</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-11.27</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>17.42</v>
+        <v>17.37</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19.7</v>
+        <v>19.58</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>20.34</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-0.58</v>
+        <v>-0.55</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.66</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-120.00</t>
+          <t>-119.15</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>78575959.12921348</t>
+          <t>78513049.03085554</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>21805741.0</t>
+          <t>6386309.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>12360542.4</v>
+        <v>12490868</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>9291757.5</t>
+          <t>9098341.6</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>29496090.52</v>
+        <v>26165273.46</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>3068784</t>
+          <t>3392526</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-1998082.91881211</t>
+          <t>-1792006.14128376</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-273461.8764181808</t>
+          <t>-658583.8648778368</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>21805741.0</t>
+          <t>6386309.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-24.01</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2759,12 +2759,12 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.48</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>404.617</t>
+          <t>1265.747</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>33.03</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-57.00</t>
+          <t>-55.60</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>13.69</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,66 +3062,66 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>14.72</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-2.09</v>
+        <v>1.22</v>
       </c>
       <c r="AU6" t="n">
-        <v>-1.23</v>
+        <v>-1.05</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>-11.57</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>17.48</v>
+        <v>17.42</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19.82</v>
+        <v>19.7</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.34</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>16.79</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-0.63</v>
+        <v>-0.58</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.72</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-120.84</t>
+          <t>-120.00</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>78575959.12921348</t>
+          <t>78513049.03085554</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>6825956.0</t>
+          <t>21805741.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>9011778.6</v>
+        <v>12360542.4</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>8472576.2</t>
+          <t>9291757.5</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>31196728.32</v>
+        <v>29496090.52</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>539202</t>
+          <t>3068784</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-2311650.381065551</t>
+          <t>-1998082.91881211</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-1365603.111603733</t>
+          <t>-273461.8764181808</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>6825956.0</t>
+          <t>21805741.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-25.55</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3241,17 +3241,17 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.48</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1055.915</t>
+          <t>404.617</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-57.12</t>
+          <t>-57.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,66 +3544,66 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>14.72</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-3.05</v>
+        <v>-2.09</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.88</v>
+        <v>-1.23</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-11.9</t>
+          <t>-11.82</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>17.54</v>
+        <v>17.48</v>
       </c>
       <c r="AZ7" t="n">
-        <v>19.9</v>
+        <v>19.82</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>20.48</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>12.97</t>
         </is>
       </c>
       <c r="BC7" t="n">
         <v>-0.63</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.75</v>
+        <v>-0.72</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-121.52</t>
+          <t>-120.84</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>78575959.12921348</t>
+          <t>78513049.03085554</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>17936964.0</t>
+          <t>6825956.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>8478385</v>
+        <v>9011778.6</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>8638135.9</t>
+          <t>8472576.2</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>31544466.74</v>
+        <v>31196728.32</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-159750</t>
+          <t>539202</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-2483658.975513155</t>
+          <t>-2311650.381065551</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-1272056.372168673</t>
+          <t>-1365603.111603733</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>17936964.0</t>
+          <t>6825956.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-25.77</t>
+          <t>-25.55</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.48</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>540.792</t>
+          <t>1055.915</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-22.70</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-55.73</t>
+          <t>-57.12</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,66 +4026,66 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>-0.74</v>
+        <v>-3.05</v>
       </c>
       <c r="AU8" t="n">
-        <v>-0.45</v>
+        <v>-0.88</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-11.91</t>
+          <t>-11.9</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.38</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>17.61</v>
+        <v>17.54</v>
       </c>
       <c r="AZ8" t="n">
-        <v>19.99</v>
+        <v>19.9</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>20.48</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-0.62</v>
+        <v>-0.63</v>
       </c>
       <c r="BD8" t="n">
-        <v>-0.78</v>
+        <v>-0.75</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-122.35</t>
+          <t>-121.52</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>78575959.12921348</t>
+          <t>78513049.03085554</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>9499370.0</t>
+          <t>17936964.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>6161869</v>
+        <v>8478385</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>7971199.1</t>
+          <t>8638135.9</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>31954701.94</v>
+        <v>31544466.74</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-1809330</t>
+          <t>-159750</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-2703950.357939424</t>
+          <t>-2483658.975513155</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-2283452.731112565</t>
+          <t>-1272056.372168673</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>9499370.0</t>
+          <t>17936964.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.77</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -4205,17 +4205,17 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.48</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>325.585</t>
+          <t>540.792</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-31.86</t>
+          <t>-22.70</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-55.22</t>
+          <t>-55.73</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,66 +4508,66 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>63.69</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>0.17</v>
+        <v>-0.74</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.54</v>
+        <v>-0.45</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>-11.91</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>17.57</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>17.66</v>
+        <v>17.61</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20.07</v>
+        <v>19.99</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-0.65</v>
+        <v>-0.62</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.78</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-123.50</t>
+          <t>-122.35</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>78575959.12921348</t>
+          <t>78513049.03085554</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>5734681.0</t>
+          <t>9499370.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>5705815.2</v>
+        <v>6161869</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>8373948.9</t>
+          <t>7971199.1</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>33871198.22</v>
+        <v>31954701.94</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-2668133</t>
+          <t>-1809330</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-2780404.471907943</t>
+          <t>-2703950.357939424</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-2742724.860635535</t>
+          <t>-2283452.731112565</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>5734681.0</t>
+          <t>9499370.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-22.47</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.48</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>289.07</t>
+          <t>325.585</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-31.86</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-55.34</t>
+          <t>-55.22</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,66 +4990,66 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>63.69</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>-0.06</v>
+        <v>0.17</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.89</v>
+        <v>-0.54</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-11.95</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>17.72</v>
+        <v>17.66</v>
       </c>
       <c r="AZ10" t="n">
-        <v>20.12</v>
+        <v>20.07</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-0.7</v>
+        <v>-0.65</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.86</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-124.70</t>
+          <t>-123.50</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>78575959.12921348</t>
+          <t>78513049.03085554</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>5061922.0</t>
+          <t>5734681.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>6222972.6</v>
+        <v>5705815.2</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>8297615.2</t>
+          <t>8373948.9</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>34897835.5</v>
+        <v>33871198.22</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-2074642</t>
+          <t>-2668133</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-2787255.310321109</t>
+          <t>-2780404.471907943</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-2897513.907788508</t>
+          <t>-2742724.860635535</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>5061922.0</t>
+          <t>5734681.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-22.69</t>
+          <t>-22.47</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.48</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>17.75</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
           <t>17.5</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
-        <is>
-          <t>17.65</t>
-        </is>
-      </c>
-      <c r="CR10" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
-      </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>236.914</t>
+          <t>289.07</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-12.30</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-55.47</t>
+          <t>-55.34</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,66 +5472,66 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>-0.74</v>
+        <v>-0.06</v>
       </c>
       <c r="AU11" t="n">
-        <v>-0.75</v>
+        <v>-0.89</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-11.92</t>
+          <t>-11.95</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>17.56</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>17.76</v>
+        <v>17.72</v>
       </c>
       <c r="AZ11" t="n">
-        <v>20.17</v>
+        <v>20.12</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-0.75</v>
+        <v>-0.7</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.9</v>
+        <v>-0.86</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-125.86</t>
+          <t>-124.70</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>78575959.12921348</t>
+          <t>78513049.03085554</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>4158988.0</t>
+          <t>5061922.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>7933373.8</v>
+        <v>6222972.6</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>9046031.2</t>
+          <t>8297615.2</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>35005618.2</v>
+        <v>34897835.5</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-1112657</t>
+          <t>-2074642</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-2767208.292599764</t>
+          <t>-2787255.310321109</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-2943077.157014593</t>
+          <t>-2897513.907788508</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>4158988.0</t>
+          <t>5061922.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-22.91</t>
+          <t>-22.69</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.48</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>360.254</t>
+          <t>236.914</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-28.20</t>
+          <t>-12.30</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-55.22</t>
+          <t>-55.47</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,66 +5954,66 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>68.25</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>0.28</v>
+        <v>-0.74</v>
       </c>
       <c r="AU12" t="n">
-        <v>-1.57</v>
+        <v>-0.75</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-11.77</t>
+          <t>-11.92</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.63</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>17.83</v>
+        <v>17.76</v>
       </c>
       <c r="AZ12" t="n">
-        <v>20.21</v>
+        <v>20.17</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>15.41</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-0.79</v>
+        <v>-0.75</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.93</v>
+        <v>-0.9</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-126.95</t>
+          <t>-125.86</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>78575959.12921348</t>
+          <t>78513049.03085554</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>6354384.0</t>
+          <t>4158988.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>8797886.800000001</v>
+        <v>7933373.8</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>12253093.0</t>
+          <t>9046031.2</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>35217518.76</v>
+        <v>35005618.2</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-3455206</t>
+          <t>-1112657</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-2735232.135433431</t>
+          <t>-2767208.292599764</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-2806314.686015621</t>
+          <t>-2943077.157014593</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>6354384.0</t>
+          <t>4158988.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>-22.47</t>
+          <t>-22.91</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.48</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>17.65</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>17.45</t>
+        </is>
+      </c>
+      <c r="CS12" t="inlineStr">
+        <is>
           <t>17.5</t>
-        </is>
-      </c>
-      <c r="CQ12" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
-      <c r="CR12" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
-      </c>
-      <c r="CS12" t="inlineStr">
-        <is>
-          <t>17.6</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/齒輪箱.xlsx
+++ b/Result/checksun_type/齒輪箱.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1300.307</t>
+          <t>529.139</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>28.09</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-56.11</t>
+          <t>-56.49</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,66 +1134,66 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>529</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>72.12</t>
+          <t>53.03</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-1.26</v>
+        <v>-1.72</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.63</v>
+        <v>0.22</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-9.72</t>
+          <t>-9.15</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AY2" t="n">
         <v>17.36</v>
       </c>
       <c r="AZ2" t="n">
-        <v>19.23</v>
+        <v>19.11</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>26.74</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="BC2" t="n">
         <v>-0.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.55</v>
+        <v>-0.52</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-115.90</t>
+          <t>-115.04</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>78513049.03085554</t>
+          <t>78422242.09453782</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>22480706.0</t>
+          <t>9117931.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>16053050</v>
+        <v>13515488</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>12532414.3</t>
+          <t>12938015.2</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>20840577.04</v>
+        <v>20517351.2</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>3520635</t>
+          <t>577472</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-1014970.934718974</t>
+          <t>-804359.2102475285</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>866650.3427326959</t>
+          <t>354005.2743454222</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>22480706.0</t>
+          <t>9117931.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-24.01</t>
+          <t>-24.67</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,17 +1313,17 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>41.48</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1165.573</t>
+          <t>1300.307</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>28.09</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-54.33</t>
+          <t>-56.11</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>12.61</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,66 +1616,66 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>529</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>72.12</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>3.16</v>
+        <v>-1.26</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.2</v>
+        <v>0.63</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-10.26</t>
+          <t>-9.72</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="AY3" t="n">
         <v>17.36</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19.35</v>
+        <v>19.23</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>26.74</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-0.42</v>
+        <v>-0.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.59</v>
+        <v>-0.55</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-116.97</t>
+          <t>-115.90</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>78513049.03085554</t>
+          <t>78422242.09453782</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>20782745.0</t>
+          <t>22480706.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>12922100</v>
+        <v>16053050</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>10700242.5</t>
+          <t>12532414.3</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>21416474.36</v>
+        <v>20840577.04</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>2221857</t>
+          <t>3520635</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-1357083.894255641</t>
+          <t>-1014970.934718974</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>136322.7496169191</t>
+          <t>866650.3427326959</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>20782745.0</t>
+          <t>22480706.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-20.93</t>
+          <t>-24.01</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,17 +1795,17 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>41.48</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
           <t>17.25</t>
-        </is>
-      </c>
-      <c r="CS3" t="inlineStr">
-        <is>
-          <t>17.95</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1897,7 +1897,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>503.465</t>
+          <t>1165.573</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>33.44</t>
+          <t>20.76</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-55.60</t>
+          <t>-54.33</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>12.61</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,66 +2098,66 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>529</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>71.11</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>1.57</v>
+        <v>3.16</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.99</v>
+        <v>0.2</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-10.81</t>
+          <t>-10.26</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>17.35</v>
+        <v>17.36</v>
       </c>
       <c r="AZ4" t="n">
-        <v>19.45</v>
+        <v>19.35</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>20.19</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>20.88</t>
+          <t>29.08</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-0.5</v>
+        <v>-0.42</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.63</v>
+        <v>-0.59</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-118.20</t>
+          <t>-116.97</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>78513049.03085554</t>
+          <t>78422242.09453782</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>8809749.0</t>
+          <t>20782745.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>12352943.8</v>
+        <v>12922100</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>9257406.4</t>
+          <t>10700242.5</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>21983292</v>
+        <v>21416474.36</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>3095537</t>
+          <t>2221857</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-1628612.374959743</t>
+          <t>-1357083.894255641</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-729946.6601776518</t>
+          <t>136322.7496169191</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>8809749.0</t>
+          <t>20782745.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-20.93</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>41.48</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>368.42</t>
+          <t>503.465</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>37.29</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-56.11</t>
+          <t>-55.60</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,66 +2580,66 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>529</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>71.11</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>0.47</v>
+        <v>1.57</v>
       </c>
       <c r="AU5" t="n">
-        <v>-1.17</v>
+        <v>-0.99</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-11.27</t>
+          <t>-10.81</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-3.40</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>17.37</v>
+        <v>17.35</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19.58</v>
+        <v>19.45</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.19</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>20.88</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-0.55</v>
+        <v>-0.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.66</v>
+        <v>-0.63</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-119.15</t>
+          <t>-118.20</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>78513049.03085554</t>
+          <t>78422242.09453782</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>6386309.0</t>
+          <t>8809749.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>12490868</v>
+        <v>12352943.8</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>9098341.6</t>
+          <t>9257406.4</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>26165273.46</v>
+        <v>21983292</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>3392526</t>
+          <t>3095537</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-1792006.14128376</t>
+          <t>-1628612.374959743</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-658583.8648778368</t>
+          <t>-729946.6601776518</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>6386309.0</t>
+          <t>8809749.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-24.01</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>41.48</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1265.747</t>
+          <t>368.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>33.03</t>
+          <t>37.29</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-55.60</t>
+          <t>-56.11</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>13.69</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,66 +3062,66 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>529</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1.22</v>
+        <v>0.47</v>
       </c>
       <c r="AU6" t="n">
-        <v>-1.05</v>
+        <v>-1.17</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-11.27</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>17.42</v>
+        <v>17.37</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19.7</v>
+        <v>19.58</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>20.34</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-0.58</v>
+        <v>-0.55</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.66</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-120.00</t>
+          <t>-119.15</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>78513049.03085554</t>
+          <t>78422242.09453782</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>21805741.0</t>
+          <t>6386309.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>12360542.4</v>
+        <v>12490868</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>9291757.5</t>
+          <t>9098341.6</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>29496090.52</v>
+        <v>26165273.46</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>3068784</t>
+          <t>3392526</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-1998082.91881211</t>
+          <t>-1792006.14128376</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-273461.8764181808</t>
+          <t>-658583.8648778368</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>21805741.0</t>
+          <t>6386309.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-24.01</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>41.48</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>404.617</t>
+          <t>1265.747</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>33.03</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-57.00</t>
+          <t>-55.60</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>13.69</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,66 +3544,66 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>529</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>14.72</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-2.09</v>
+        <v>1.22</v>
       </c>
       <c r="AU7" t="n">
-        <v>-1.23</v>
+        <v>-1.05</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>-11.57</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>17.48</v>
+        <v>17.42</v>
       </c>
       <c r="AZ7" t="n">
-        <v>19.82</v>
+        <v>19.7</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.34</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>16.79</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-0.63</v>
+        <v>-0.58</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.72</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-120.84</t>
+          <t>-120.00</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>78513049.03085554</t>
+          <t>78422242.09453782</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>6825956.0</t>
+          <t>21805741.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>9011778.6</v>
+        <v>12360542.4</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>8472576.2</t>
+          <t>9291757.5</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>31196728.32</v>
+        <v>29496090.52</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>539202</t>
+          <t>3068784</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-2311650.381065551</t>
+          <t>-1998082.91881211</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-1365603.111603733</t>
+          <t>-273461.8764181808</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>6825956.0</t>
+          <t>21805741.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-25.55</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,17 +3723,17 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>41.48</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1055.915</t>
+          <t>404.617</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-57.12</t>
+          <t>-57.00</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,66 +4026,66 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>529</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>14.72</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>-3.05</v>
+        <v>-2.09</v>
       </c>
       <c r="AU8" t="n">
-        <v>-0.88</v>
+        <v>-1.23</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-11.9</t>
+          <t>-11.82</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>17.54</v>
+        <v>17.48</v>
       </c>
       <c r="AZ8" t="n">
-        <v>19.9</v>
+        <v>19.82</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>20.48</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>12.97</t>
         </is>
       </c>
       <c r="BC8" t="n">
         <v>-0.63</v>
       </c>
       <c r="BD8" t="n">
-        <v>-0.75</v>
+        <v>-0.72</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-121.52</t>
+          <t>-120.84</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>78513049.03085554</t>
+          <t>78422242.09453782</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>17936964.0</t>
+          <t>6825956.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>8478385</v>
+        <v>9011778.6</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>8638135.9</t>
+          <t>8472576.2</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>31544466.74</v>
+        <v>31196728.32</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-159750</t>
+          <t>539202</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-2483658.975513155</t>
+          <t>-2311650.381065551</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-1272056.372168673</t>
+          <t>-1365603.111603733</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>17936964.0</t>
+          <t>6825956.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-25.77</t>
+          <t>-25.55</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>41.48</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>540.792</t>
+          <t>1055.915</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-22.70</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-55.73</t>
+          <t>-57.12</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,66 +4508,66 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>529</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>-0.74</v>
+        <v>-3.05</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.45</v>
+        <v>-0.88</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-11.91</t>
+          <t>-11.9</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.38</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>17.61</v>
+        <v>17.54</v>
       </c>
       <c r="AZ9" t="n">
-        <v>19.99</v>
+        <v>19.9</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>20.48</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-0.62</v>
+        <v>-0.63</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.78</v>
+        <v>-0.75</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-122.35</t>
+          <t>-121.52</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>78513049.03085554</t>
+          <t>78422242.09453782</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>9499370.0</t>
+          <t>17936964.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>6161869</v>
+        <v>8478385</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>7971199.1</t>
+          <t>8638135.9</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>31954701.94</v>
+        <v>31544466.74</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-1809330</t>
+          <t>-159750</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-2703950.357939424</t>
+          <t>-2483658.975513155</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-2283452.731112565</t>
+          <t>-1272056.372168673</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>9499370.0</t>
+          <t>17936964.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.77</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,17 +4687,17 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>41.48</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>325.585</t>
+          <t>540.792</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-31.86</t>
+          <t>-22.70</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-55.22</t>
+          <t>-55.73</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,66 +4990,66 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>529</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>63.69</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>0.17</v>
+        <v>-0.74</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.54</v>
+        <v>-0.45</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>-11.91</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>17.57</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>17.66</v>
+        <v>17.61</v>
       </c>
       <c r="AZ10" t="n">
-        <v>20.07</v>
+        <v>19.99</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-0.65</v>
+        <v>-0.62</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.78</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-123.50</t>
+          <t>-122.35</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>78513049.03085554</t>
+          <t>78422242.09453782</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>5734681.0</t>
+          <t>9499370.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>5705815.2</v>
+        <v>6161869</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>8373948.9</t>
+          <t>7971199.1</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>33871198.22</v>
+        <v>31954701.94</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-2668133</t>
+          <t>-1809330</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-2780404.471907943</t>
+          <t>-2703950.357939424</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-2742724.860635535</t>
+          <t>-2283452.731112565</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>5734681.0</t>
+          <t>9499370.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-22.47</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>41.48</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>289.07</t>
+          <t>325.585</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-31.86</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-55.34</t>
+          <t>-55.22</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,66 +5472,66 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>529</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>63.69</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>-0.06</v>
+        <v>0.17</v>
       </c>
       <c r="AU11" t="n">
-        <v>-0.89</v>
+        <v>-0.54</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-11.95</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>17.72</v>
+        <v>17.66</v>
       </c>
       <c r="AZ11" t="n">
-        <v>20.12</v>
+        <v>20.07</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-0.7</v>
+        <v>-0.65</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.86</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-124.70</t>
+          <t>-123.50</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>78513049.03085554</t>
+          <t>78422242.09453782</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>5061922.0</t>
+          <t>5734681.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>6222972.6</v>
+        <v>5705815.2</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>8297615.2</t>
+          <t>8373948.9</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>34897835.5</v>
+        <v>33871198.22</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-2074642</t>
+          <t>-2668133</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-2787255.310321109</t>
+          <t>-2780404.471907943</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-2897513.907788508</t>
+          <t>-2742724.860635535</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>5061922.0</t>
+          <t>5734681.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-22.69</t>
+          <t>-22.47</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>41.48</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>17.75</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
           <t>17.5</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
-        <is>
-          <t>17.65</t>
-        </is>
-      </c>
-      <c r="CR11" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
-      </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>236.914</t>
+          <t>289.07</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-12.30</t>
+          <t>-25.00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-55.47</t>
+          <t>-55.34</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,66 +5954,66 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>529</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>-0.74</v>
+        <v>-0.06</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0.75</v>
+        <v>-0.89</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-11.92</t>
+          <t>-11.95</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>17.56</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>17.76</v>
+        <v>17.72</v>
       </c>
       <c r="AZ12" t="n">
-        <v>20.17</v>
+        <v>20.12</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-0.75</v>
+        <v>-0.7</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.9</v>
+        <v>-0.86</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-125.86</t>
+          <t>-124.70</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>78513049.03085554</t>
+          <t>78422242.09453782</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>4158988.0</t>
+          <t>5061922.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>7933373.8</v>
+        <v>6222972.6</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>9046031.2</t>
+          <t>8297615.2</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>35005618.2</v>
+        <v>34897835.5</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-1112657</t>
+          <t>-2074642</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-2767208.292599764</t>
+          <t>-2787255.310321109</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-2943077.157014593</t>
+          <t>-2897513.907788508</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>4158988.0</t>
+          <t>5061922.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>-22.91</t>
+          <t>-22.69</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>41.48</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/齒輪箱.xlsx
+++ b/Result/checksun_type/齒輪箱.xlsx
@@ -933,7 +933,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>529.139</t>
+          <t>675.654</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-56.49</t>
+          <t>-57.12</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,66 +1134,66 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>676</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>53.03</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-1.72</v>
+        <v>-2.71</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.22</v>
+        <v>-0.13</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-9.15</t>
+          <t>-8.69</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.70</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.32</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>17.36</v>
+        <v>17.34</v>
       </c>
       <c r="AZ2" t="n">
-        <v>19.11</v>
+        <v>18.99</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.93</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-0.4</v>
+        <v>-0.41</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.52</v>
+        <v>-0.5</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-115.04</t>
+          <t>-114.42</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>78422242.09453782</t>
+          <t>78336442.57342657</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>9117931.0</t>
+          <t>11383723.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>13515488</v>
+        <v>14514970.8</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>12938015.2</t>
+          <t>13502919.4</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>20517351.2</v>
+        <v>19808443.86</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>577472</t>
+          <t>1012051</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-804359.2102475285</t>
+          <t>-656575.0248839555</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>354005.2743454222</t>
+          <t>156237.9946156964</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>9117931.0</t>
+          <t>11383723.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-24.67</t>
+          <t>-25.77</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1300.307</t>
+          <t>529.139</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.09</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-56.11</t>
+          <t>-56.49</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,66 +1616,66 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>676</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>72.12</t>
+          <t>53.03</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-1.26</v>
+        <v>-1.72</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.63</v>
+        <v>0.22</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-9.72</t>
+          <t>-9.15</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AY3" t="n">
         <v>17.36</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19.23</v>
+        <v>19.11</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>26.74</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="BC3" t="n">
         <v>-0.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.55</v>
+        <v>-0.52</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-115.90</t>
+          <t>-115.04</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>78422242.09453782</t>
+          <t>78336442.57342657</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>22480706.0</t>
+          <t>9117931.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>16053050</v>
+        <v>13515488</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>12532414.3</t>
+          <t>12938015.2</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>20840577.04</v>
+        <v>20517351.2</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>3520635</t>
+          <t>577472</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-1014970.934718974</t>
+          <t>-804359.2102475285</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>866650.3427326959</t>
+          <t>354005.2743454222</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>22480706.0</t>
+          <t>9117931.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-24.01</t>
+          <t>-24.67</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,17 +1795,17 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,12 +1860,12 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1165.573</t>
+          <t>1300.307</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>28.09</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-54.33</t>
+          <t>-56.11</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>12.61</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,66 +2098,66 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>676</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>72.12</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>3.16</v>
+        <v>-1.26</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.2</v>
+        <v>0.63</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-10.26</t>
+          <t>-9.72</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="AY4" t="n">
         <v>17.36</v>
       </c>
       <c r="AZ4" t="n">
-        <v>19.35</v>
+        <v>19.23</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>26.74</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-0.42</v>
+        <v>-0.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.59</v>
+        <v>-0.55</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-116.97</t>
+          <t>-115.90</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>78422242.09453782</t>
+          <t>78336442.57342657</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>20782745.0</t>
+          <t>22480706.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>12922100</v>
+        <v>16053050</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>10700242.5</t>
+          <t>12532414.3</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>21416474.36</v>
+        <v>20840577.04</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>2221857</t>
+          <t>3520635</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-1357083.894255641</t>
+          <t>-1014970.934718974</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>136322.7496169191</t>
+          <t>866650.3427326959</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>20782745.0</t>
+          <t>22480706.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-20.93</t>
+          <t>-24.01</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,17 +2277,17 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
           <t>17.25</t>
-        </is>
-      </c>
-      <c r="CS4" t="inlineStr">
-        <is>
-          <t>17.95</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2379,7 +2379,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>503.465</t>
+          <t>1165.573</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-6.53</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>33.44</t>
+          <t>20.76</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-55.60</t>
+          <t>-54.33</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>12.61</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,66 +2580,66 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>676</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>71.11</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>1.57</v>
+        <v>3.16</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.99</v>
+        <v>0.2</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-10.81</t>
+          <t>-10.26</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>17.35</v>
+        <v>17.36</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19.45</v>
+        <v>19.35</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>20.19</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>20.88</t>
+          <t>29.08</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-0.5</v>
+        <v>-0.42</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.63</v>
+        <v>-0.59</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-118.20</t>
+          <t>-116.97</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>78422242.09453782</t>
+          <t>78336442.57342657</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>8809749.0</t>
+          <t>20782745.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>12352943.8</v>
+        <v>12922100</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>9257406.4</t>
+          <t>10700242.5</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>21983292</v>
+        <v>21416474.36</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>3095537</t>
+          <t>2221857</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-1628612.374959743</t>
+          <t>-1357083.894255641</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-729946.6601776518</t>
+          <t>136322.7496169191</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>8809749.0</t>
+          <t>20782745.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-20.93</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>368.42</t>
+          <t>503.465</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>37.29</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-56.11</t>
+          <t>-55.60</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,66 +3062,66 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>676</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>71.11</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>0.47</v>
+        <v>1.57</v>
       </c>
       <c r="AU6" t="n">
-        <v>-1.17</v>
+        <v>-0.99</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-11.27</t>
+          <t>-10.81</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-3.40</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>17.37</v>
+        <v>17.35</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19.58</v>
+        <v>19.45</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.19</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>20.88</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-0.55</v>
+        <v>-0.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.66</v>
+        <v>-0.63</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-119.15</t>
+          <t>-118.20</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>78422242.09453782</t>
+          <t>78336442.57342657</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>6386309.0</t>
+          <t>8809749.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>12490868</v>
+        <v>12352943.8</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>9098341.6</t>
+          <t>9257406.4</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>26165273.46</v>
+        <v>21983292</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>3392526</t>
+          <t>3095537</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-1792006.14128376</t>
+          <t>-1628612.374959743</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-658583.8648778368</t>
+          <t>-729946.6601776518</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>6386309.0</t>
+          <t>8809749.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-24.01</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1265.747</t>
+          <t>368.42</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>33.03</t>
+          <t>37.29</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-55.60</t>
+          <t>-56.11</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>13.69</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,66 +3544,66 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>676</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1.22</v>
+        <v>0.47</v>
       </c>
       <c r="AU7" t="n">
-        <v>-1.05</v>
+        <v>-1.17</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-11.27</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>17.42</v>
+        <v>17.37</v>
       </c>
       <c r="AZ7" t="n">
-        <v>19.7</v>
+        <v>19.58</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>20.34</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-0.58</v>
+        <v>-0.55</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.66</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-120.00</t>
+          <t>-119.15</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>78422242.09453782</t>
+          <t>78336442.57342657</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>21805741.0</t>
+          <t>6386309.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>12360542.4</v>
+        <v>12490868</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>9291757.5</t>
+          <t>9098341.6</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>29496090.52</v>
+        <v>26165273.46</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>3068784</t>
+          <t>3392526</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-1998082.91881211</t>
+          <t>-1792006.14128376</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-273461.8764181808</t>
+          <t>-658583.8648778368</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>21805741.0</t>
+          <t>6386309.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-24.01</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>404.617</t>
+          <t>1265.747</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>33.03</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-57.00</t>
+          <t>-55.60</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>13.69</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,66 +4026,66 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>676</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>14.72</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>-2.09</v>
+        <v>1.22</v>
       </c>
       <c r="AU8" t="n">
-        <v>-1.23</v>
+        <v>-1.05</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>-11.57</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>17.48</v>
+        <v>17.42</v>
       </c>
       <c r="AZ8" t="n">
-        <v>19.82</v>
+        <v>19.7</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.34</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>16.79</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-0.63</v>
+        <v>-0.58</v>
       </c>
       <c r="BD8" t="n">
-        <v>-0.72</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-120.84</t>
+          <t>-120.00</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>78422242.09453782</t>
+          <t>78336442.57342657</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>6825956.0</t>
+          <t>21805741.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>9011778.6</v>
+        <v>12360542.4</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>8472576.2</t>
+          <t>9291757.5</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>31196728.32</v>
+        <v>29496090.52</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>539202</t>
+          <t>3068784</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-2311650.381065551</t>
+          <t>-1998082.91881211</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-1365603.111603733</t>
+          <t>-273461.8764181808</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>6825956.0</t>
+          <t>21805741.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-25.55</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,17 +4205,17 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1055.915</t>
+          <t>404.617</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-57.12</t>
+          <t>-57.00</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,66 +4508,66 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>676</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>14.72</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>-3.05</v>
+        <v>-2.09</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.88</v>
+        <v>-1.23</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-11.9</t>
+          <t>-11.82</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>17.54</v>
+        <v>17.48</v>
       </c>
       <c r="AZ9" t="n">
-        <v>19.9</v>
+        <v>19.82</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>20.48</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>12.97</t>
         </is>
       </c>
       <c r="BC9" t="n">
         <v>-0.63</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.75</v>
+        <v>-0.72</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-121.52</t>
+          <t>-120.84</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>78422242.09453782</t>
+          <t>78336442.57342657</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>17936964.0</t>
+          <t>6825956.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>8478385</v>
+        <v>9011778.6</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>8638135.9</t>
+          <t>8472576.2</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>31544466.74</v>
+        <v>31196728.32</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-159750</t>
+          <t>539202</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-2483658.975513155</t>
+          <t>-2311650.381065551</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-1272056.372168673</t>
+          <t>-1365603.111603733</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>17936964.0</t>
+          <t>6825956.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-25.77</t>
+          <t>-25.55</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>540.792</t>
+          <t>1055.915</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-22.70</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-55.73</t>
+          <t>-57.12</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,66 +4990,66 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>676</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>-0.74</v>
+        <v>-3.05</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.45</v>
+        <v>-0.88</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-11.91</t>
+          <t>-11.9</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.38</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>17.61</v>
+        <v>17.54</v>
       </c>
       <c r="AZ10" t="n">
-        <v>19.99</v>
+        <v>19.9</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>20.48</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-0.62</v>
+        <v>-0.63</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.78</v>
+        <v>-0.75</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-122.35</t>
+          <t>-121.52</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>78422242.09453782</t>
+          <t>78336442.57342657</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>9499370.0</t>
+          <t>17936964.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>6161869</v>
+        <v>8478385</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>7971199.1</t>
+          <t>8638135.9</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>31954701.94</v>
+        <v>31544466.74</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-1809330</t>
+          <t>-159750</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-2703950.357939424</t>
+          <t>-2483658.975513155</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-2283452.731112565</t>
+          <t>-1272056.372168673</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>9499370.0</t>
+          <t>17936964.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.77</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,17 +5169,17 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>325.585</t>
+          <t>540.792</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-31.86</t>
+          <t>-22.70</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-55.22</t>
+          <t>-55.73</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,66 +5472,66 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>676</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>63.69</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>0.17</v>
+        <v>-0.74</v>
       </c>
       <c r="AU11" t="n">
-        <v>-0.54</v>
+        <v>-0.45</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>-11.91</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>17.57</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>17.66</v>
+        <v>17.61</v>
       </c>
       <c r="AZ11" t="n">
-        <v>20.07</v>
+        <v>19.99</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>20.43</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-0.65</v>
+        <v>-0.62</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.78</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-123.50</t>
+          <t>-122.35</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>78422242.09453782</t>
+          <t>78336442.57342657</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>5734681.0</t>
+          <t>9499370.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>5705815.2</v>
+        <v>6161869</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>8373948.9</t>
+          <t>7971199.1</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>33871198.22</v>
+        <v>31954701.94</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-2668133</t>
+          <t>-1809330</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-2780404.471907943</t>
+          <t>-2703950.357939424</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-2742724.860635535</t>
+          <t>-2283452.731112565</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>5734681.0</t>
+          <t>9499370.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-22.47</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>289.07</t>
+          <t>325.585</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-25.00</t>
+          <t>-31.86</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-55.34</t>
+          <t>-55.22</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,66 +5954,66 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>676</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>63.69</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>-0.06</v>
+        <v>0.17</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0.89</v>
+        <v>-0.54</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-11.95</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>17.72</v>
+        <v>17.66</v>
       </c>
       <c r="AZ12" t="n">
-        <v>20.12</v>
+        <v>20.07</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>20.58</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-0.7</v>
+        <v>-0.65</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.86</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-124.70</t>
+          <t>-123.50</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>78422242.09453782</t>
+          <t>78336442.57342657</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>5061922.0</t>
+          <t>5734681.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>6222972.6</v>
+        <v>5705815.2</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>8297615.2</t>
+          <t>8373948.9</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>34897835.5</v>
+        <v>33871198.22</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-2074642</t>
+          <t>-2668133</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-2787255.310321109</t>
+          <t>-2780404.471907943</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-2897513.907788508</t>
+          <t>-2742724.860635535</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>5061922.0</t>
+          <t>5734681.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>-22.69</t>
+          <t>-22.47</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>17.75</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
           <t>17.5</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
-        <is>
-          <t>17.65</t>
-        </is>
-      </c>
-      <c r="CR12" t="inlineStr">
-        <is>
-          <t>17.45</t>
-        </is>
-      </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/齒輪箱.xlsx
+++ b/Result/checksun_type/齒輪箱.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>188.761</t>
+          <t>486.967</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>-8.56</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-57.00</t>
+          <t>-56.87</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,66 +1144,66 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>487</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
+          <t>9.09</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
           <t>4.55</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>9.09</t>
-        </is>
-      </c>
       <c r="AU2" t="n">
-        <v>-1.8</v>
+        <v>-0.35</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0.78</v>
+        <v>-1.87</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-8.05</t>
+          <t>-7.41</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>17.21</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="AZ2" t="n">
         <v>17.34</v>
       </c>
       <c r="BA2" t="n">
-        <v>18.86</v>
+        <v>18.72</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>12.83</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.42</v>
+        <v>-0.41</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.48</v>
+        <v>-0.47</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-113.93</t>
+          <t>-113.50</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>78233742.58449721</t>
+          <t>78141855.041841</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>3202167.0</t>
+          <t>8233583.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>13393454.4</v>
+        <v>10883622</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>12873199.1</t>
+          <t>11902861.0</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>19258789.6</v>
+        <v>18219726.48</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>520255</t>
+          <t>-1019239</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-647828.3673726553</t>
+          <t>-661476.976893375</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-599721.7510605045</t>
+          <t>-736544.3292573337</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>3202167.0</t>
+          <t>8233583.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-25.55</t>
+          <t>-25.33</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>41.59</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>675.654</t>
+          <t>188.761</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,167 +1460,167 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>-0.98</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>4.04</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-02-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2024-09-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2024-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>40.65</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>39.3</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>44.9</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-57.00</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>-7.61</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025/02/18</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>40.65</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2025/11/05</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>18.45</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2025/04/07</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>31.95</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>22.35</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/09/03</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>21.25</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2025-09-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
           <t>-0.89</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-02-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-03-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2024-09-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2024-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>40.65</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>39.3</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>44.9</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>44.0</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-57.12</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>-7.61</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025/02/18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>40.65</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2025/11/05</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>18.45</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2025/04/07</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>31.95</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2025/10/17</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>22.35</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>2025/09/03</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>21.25</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>2025-09-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>7.31</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>-0.59</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,66 +1631,66 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>487</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-2.71</v>
+        <v>-1.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.13</v>
+        <v>-0.78</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-8.69</t>
+          <t>-8.05</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-4.70</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>17.21</t>
         </is>
       </c>
       <c r="AZ3" t="n">
         <v>17.34</v>
       </c>
       <c r="BA3" t="n">
-        <v>18.99</v>
+        <v>18.86</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>19.93</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.41</v>
+        <v>-0.42</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.5</v>
+        <v>-0.48</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-114.42</t>
+          <t>-113.93</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>78233742.58449721</t>
+          <t>78141855.041841</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>11383723.0</t>
+          <t>3202167.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>14514970.8</v>
+        <v>13393454.4</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>13502919.4</t>
+          <t>12873199.1</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>19808443.86</v>
+        <v>19258789.6</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>1012051</t>
+          <t>520255</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-656575.0248839555</t>
+          <t>-647828.3673726553</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>156237.9946156964</t>
+          <t>-599721.7510605045</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>11383723.0</t>
+          <t>3202167.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-25.77</t>
+          <t>-25.55</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>41.59</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1912,7 +1912,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>529.139</t>
+          <t>675.654</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-56.49</t>
+          <t>-57.12</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,66 +2118,66 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>487</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>53.03</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-1.72</v>
+        <v>-2.71</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.22</v>
+        <v>-0.13</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-9.15</t>
+          <t>-8.69</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.70</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.32</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>17.36</v>
+        <v>17.34</v>
       </c>
       <c r="BA4" t="n">
-        <v>19.11</v>
+        <v>18.99</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.93</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.4</v>
+        <v>-0.41</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.52</v>
+        <v>-0.5</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-115.04</t>
+          <t>-114.42</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>78233742.58449721</t>
+          <t>78141855.041841</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>9117931.0</t>
+          <t>11383723.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>13515488</v>
+        <v>14514970.8</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>12938015.2</t>
+          <t>13502919.4</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>20517351.2</v>
+        <v>19808443.86</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>577472</t>
+          <t>1012051</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-804359.2102475285</t>
+          <t>-656575.0248839555</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>354005.2743454222</t>
+          <t>156237.9946156964</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>9117931.0</t>
+          <t>11383723.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-24.67</t>
+          <t>-25.77</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>41.59</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1300.307</t>
+          <t>529.139</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>28.09</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-56.11</t>
+          <t>-56.49</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,66 +2605,66 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>487</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>72.12</t>
+          <t>53.03</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-1.26</v>
+        <v>-1.72</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.63</v>
+        <v>0.22</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-9.72</t>
+          <t>-9.15</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
         <v>17.36</v>
       </c>
       <c r="BA5" t="n">
-        <v>19.23</v>
+        <v>19.11</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>26.74</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="BD5" t="n">
         <v>-0.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.55</v>
+        <v>-0.52</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-115.90</t>
+          <t>-115.04</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>78233742.58449721</t>
+          <t>78141855.041841</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>22480706.0</t>
+          <t>9117931.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>16053050</v>
+        <v>13515488</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>12532414.3</t>
+          <t>12938015.2</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>20840577.04</v>
+        <v>20517351.2</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>3520635</t>
+          <t>577472</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-1014970.934718974</t>
+          <t>-804359.2102475285</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>866650.3427326959</t>
+          <t>354005.2743454222</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>22480706.0</t>
+          <t>9117931.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-24.01</t>
+          <t>-24.67</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2784,17 +2784,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>41.59</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1165.573</t>
+          <t>1300.307</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>28.09</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-54.33</t>
+          <t>-56.11</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>12.61</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,66 +3092,66 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>487</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>72.12</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>3.16</v>
+        <v>-1.26</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.2</v>
+        <v>0.63</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-10.26</t>
+          <t>-9.72</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="AZ6" t="n">
         <v>17.36</v>
       </c>
       <c r="BA6" t="n">
-        <v>19.35</v>
+        <v>19.23</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>26.74</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.42</v>
+        <v>-0.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.59</v>
+        <v>-0.55</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-116.97</t>
+          <t>-115.90</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>78233742.58449721</t>
+          <t>78141855.041841</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>20782745.0</t>
+          <t>22480706.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>12922100</v>
+        <v>16053050</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>10700242.5</t>
+          <t>12532414.3</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>21416474.36</v>
+        <v>20840577.04</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>2221857</t>
+          <t>3520635</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-1357083.894255641</t>
+          <t>-1014970.934718974</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>136322.7496169191</t>
+          <t>866650.3427326959</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>20782745.0</t>
+          <t>22480706.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>-20.93</t>
+          <t>-24.01</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3271,17 +3271,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>41.59</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="CT6" t="inlineStr">
+        <is>
           <t>17.25</t>
-        </is>
-      </c>
-      <c r="CT6" t="inlineStr">
-        <is>
-          <t>17.95</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3373,7 +3373,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>503.465</t>
+          <t>1165.573</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-5.9</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>33.44</t>
+          <t>20.76</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-55.60</t>
+          <t>-54.33</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>12.61</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,66 +3579,66 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>487</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>71.11</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>1.57</v>
+        <v>3.16</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.99</v>
+        <v>0.2</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-10.81</t>
+          <t>-10.26</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>17.35</v>
+        <v>17.36</v>
       </c>
       <c r="BA7" t="n">
-        <v>19.45</v>
+        <v>19.35</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>20.19</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>20.88</t>
+          <t>29.08</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.5</v>
+        <v>-0.42</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.63</v>
+        <v>-0.59</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-118.20</t>
+          <t>-116.97</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>78233742.58449721</t>
+          <t>78141855.041841</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>8809749.0</t>
+          <t>20782745.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>12352943.8</v>
+        <v>12922100</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>9257406.4</t>
+          <t>10700242.5</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>21983292</v>
+        <v>21416474.36</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>3095537</t>
+          <t>2221857</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-1628612.374959743</t>
+          <t>-1357083.894255641</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-729946.6601776518</t>
+          <t>136322.7496169191</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>8809749.0</t>
+          <t>20782745.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-20.93</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>41.59</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>368.42</t>
+          <t>503.465</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>37.29</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-56.11</t>
+          <t>-55.60</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,66 +4066,66 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>487</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>71.11</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>0.47</v>
+        <v>1.57</v>
       </c>
       <c r="AV8" t="n">
-        <v>-1.17</v>
+        <v>-0.99</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-11.27</t>
+          <t>-10.81</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-3.40</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>17.37</v>
+        <v>17.35</v>
       </c>
       <c r="BA8" t="n">
-        <v>19.58</v>
+        <v>19.45</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.19</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>20.88</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-0.55</v>
+        <v>-0.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>-0.66</v>
+        <v>-0.63</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-119.15</t>
+          <t>-118.20</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>78233742.58449721</t>
+          <t>78141855.041841</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>6386309.0</t>
+          <t>8809749.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>12490868</v>
+        <v>12352943.8</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>9098341.6</t>
+          <t>9257406.4</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>26165273.46</v>
+        <v>21983292</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>3392526</t>
+          <t>3095537</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-1792006.14128376</t>
+          <t>-1628612.374959743</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-658583.8648778368</t>
+          <t>-729946.6601776518</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>6386309.0</t>
+          <t>8809749.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-24.01</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>41.59</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1265.747</t>
+          <t>368.42</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>33.03</t>
+          <t>37.29</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-55.60</t>
+          <t>-56.11</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>13.69</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,66 +4553,66 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>487</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>1.22</v>
+        <v>0.47</v>
       </c>
       <c r="AV9" t="n">
-        <v>-1.05</v>
+        <v>-1.17</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-11.27</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>17.42</v>
+        <v>17.37</v>
       </c>
       <c r="BA9" t="n">
-        <v>19.7</v>
+        <v>19.58</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>20.34</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>-0.58</v>
+        <v>-0.55</v>
       </c>
       <c r="BE9" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.66</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-120.00</t>
+          <t>-119.15</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>78233742.58449721</t>
+          <t>78141855.041841</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>21805741.0</t>
+          <t>6386309.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>12360542.4</v>
+        <v>12490868</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>9291757.5</t>
+          <t>9098341.6</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>29496090.52</v>
+        <v>26165273.46</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>3068784</t>
+          <t>3392526</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-1998082.91881211</t>
+          <t>-1792006.14128376</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-273461.8764181808</t>
+          <t>-658583.8648778368</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>21805741.0</t>
+          <t>6386309.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-23.13</t>
+          <t>-24.01</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>41.59</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>404.617</t>
+          <t>1265.747</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>33.03</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-57.00</t>
+          <t>-55.60</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>13.69</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,66 +5040,66 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>487</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>14.72</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-2.09</v>
+        <v>1.22</v>
       </c>
       <c r="AV10" t="n">
-        <v>-1.23</v>
+        <v>-1.05</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>-11.57</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>17.48</v>
+        <v>17.42</v>
       </c>
       <c r="BA10" t="n">
-        <v>19.82</v>
+        <v>19.7</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.34</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>16.79</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>-0.63</v>
+        <v>-0.58</v>
       </c>
       <c r="BE10" t="n">
-        <v>-0.72</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-120.84</t>
+          <t>-120.00</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>78233742.58449721</t>
+          <t>78141855.041841</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>6825956.0</t>
+          <t>21805741.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>9011778.6</v>
+        <v>12360542.4</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>8472576.2</t>
+          <t>9291757.5</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>31196728.32</v>
+        <v>29496090.52</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>539202</t>
+          <t>3068784</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-2311650.381065551</t>
+          <t>-1998082.91881211</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-1365603.111603733</t>
+          <t>-273461.8764181808</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>6825956.0</t>
+          <t>21805741.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-25.55</t>
+          <t>-23.13</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -5219,17 +5219,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>41.59</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1055.915</t>
+          <t>404.617</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5356,17 +5356,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-57.12</t>
+          <t>-57.00</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,66 +5527,66 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>487</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>14.72</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-3.05</v>
+        <v>-2.09</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0.88</v>
+        <v>-1.23</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-11.9</t>
+          <t>-11.82</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>17.54</v>
+        <v>17.48</v>
       </c>
       <c r="BA11" t="n">
-        <v>19.9</v>
+        <v>19.82</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>20.48</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>12.97</t>
         </is>
       </c>
       <c r="BD11" t="n">
         <v>-0.63</v>
       </c>
       <c r="BE11" t="n">
-        <v>-0.75</v>
+        <v>-0.72</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-121.52</t>
+          <t>-120.84</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,43 +5605,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>78233742.58449721</t>
+          <t>78141855.041841</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>17936964.0</t>
+          <t>6825956.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>8478385</v>
+        <v>9011778.6</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>8638135.9</t>
+          <t>8472576.2</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>31544466.74</v>
+        <v>31196728.32</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-159750</t>
+          <t>539202</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-2483658.975513155</t>
+          <t>-2311650.381065551</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-1272056.372168673</t>
+          <t>-1365603.111603733</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>17936964.0</t>
+          <t>6825956.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-25.77</t>
+          <t>-25.55</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>41.59</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>540.792</t>
+          <t>1055.915</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-22.70</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-55.73</t>
+          <t>-57.12</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,66 +6014,66 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>487</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-0.74</v>
+        <v>-3.05</v>
       </c>
       <c r="AV12" t="n">
-        <v>-0.45</v>
+        <v>-0.88</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-11.91</t>
+          <t>-11.9</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-2.70</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>17.38</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>17.61</v>
+        <v>17.54</v>
       </c>
       <c r="BA12" t="n">
-        <v>19.99</v>
+        <v>19.9</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>20.48</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>15.58</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.62</v>
+        <v>-0.63</v>
       </c>
       <c r="BE12" t="n">
-        <v>-0.78</v>
+        <v>-0.75</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-122.35</t>
+          <t>-121.52</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,43 +6092,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>78233742.58449721</t>
+          <t>78141855.041841</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>9499370.0</t>
+          <t>17936964.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>6161869</v>
+        <v>8478385</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>7971199.1</t>
+          <t>8638135.9</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>31954701.94</v>
+        <v>31544466.74</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-1809330</t>
+          <t>-159750</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-2703950.357939424</t>
+          <t>-2483658.975513155</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-2283452.731112565</t>
+          <t>-1272056.372168673</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>9499370.0</t>
+          <t>17936964.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-25.77</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>41.59</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">

--- a/Result/checksun_type/齒輪箱.xlsx
+++ b/Result/checksun_type/齒輪箱.xlsx
@@ -953,7 +953,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>486.967</t>
+          <t>525.859</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-8.56</t>
+          <t>-32.58</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-56.87</t>
+          <t>-56.74</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,66 +1144,66 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>526</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
+          <t>13.64</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
           <t>9.09</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>4.55</t>
-        </is>
-      </c>
       <c r="AU2" t="n">
-        <v>-0.35</v>
+        <v>0.24</v>
       </c>
       <c r="AV2" t="n">
-        <v>-1.87</v>
+        <v>-2.14</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-7.41</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>16.96</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>17.34</v>
+        <v>17.33</v>
       </c>
       <c r="BA2" t="n">
-        <v>18.72</v>
+        <v>18.6</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>12.83</t>
+          <t>13.17</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.41</v>
+        <v>-0.39</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.47</v>
+        <v>-0.45</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-113.50</t>
+          <t>-113.07</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>78141855.041841</t>
+          <t>78051568.73189415</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>8233583.0</t>
+          <t>8877523.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>10883622</v>
+        <v>8162985.4</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>11902861.0</t>
+          <t>12108017.7</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>18219726.48</v>
+        <v>17595571.52</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-1019239</t>
+          <t>-3945032</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-661476.976893375</t>
+          <t>-677497.5997964991</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-736544.3292573337</t>
+          <t>-765611.0257636812</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>8233583.0</t>
+          <t>8877523.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-25.33</t>
+          <t>-25.11</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>42.25</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>2596</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1393,17 +1393,17 @@
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>16.75</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>188.761</t>
+          <t>486.967</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>-8.56</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-57.00</t>
+          <t>-56.87</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,66 +1631,66 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>526</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
+          <t>9.09</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
           <t>4.55</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>9.09</t>
-        </is>
-      </c>
       <c r="AU3" t="n">
-        <v>-1.8</v>
+        <v>-0.35</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.78</v>
+        <v>-1.87</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-8.05</t>
+          <t>-7.41</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>17.21</t>
+          <t>17.01</t>
         </is>
       </c>
       <c r="AZ3" t="n">
         <v>17.34</v>
       </c>
       <c r="BA3" t="n">
-        <v>18.86</v>
+        <v>18.72</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>12.83</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.42</v>
+        <v>-0.41</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.48</v>
+        <v>-0.47</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-113.93</t>
+          <t>-113.50</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>78141855.041841</t>
+          <t>78051568.73189415</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>3202167.0</t>
+          <t>8233583.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>13393454.4</v>
+        <v>10883622</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>12873199.1</t>
+          <t>11902861.0</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>19258789.6</v>
+        <v>18219726.48</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>520255</t>
+          <t>-1019239</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-647828.3673726553</t>
+          <t>-661476.976893375</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-599721.7510605045</t>
+          <t>-736544.3292573337</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>3202167.0</t>
+          <t>8233583.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-25.55</t>
+          <t>-25.33</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>42.25</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>2596</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>675.654</t>
+          <t>188.761</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-57.12</t>
+          <t>-57.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,66 +2118,66 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>526</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-2.71</v>
+        <v>-1.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0.13</v>
+        <v>-0.78</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-8.69</t>
+          <t>-8.05</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-4.70</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>17.32</t>
+          <t>17.21</t>
         </is>
       </c>
       <c r="AZ4" t="n">
         <v>17.34</v>
       </c>
       <c r="BA4" t="n">
-        <v>18.99</v>
+        <v>18.86</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>19.93</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.41</v>
+        <v>-0.42</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.5</v>
+        <v>-0.48</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-114.42</t>
+          <t>-113.93</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>78141855.041841</t>
+          <t>78051568.73189415</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>11383723.0</t>
+          <t>3202167.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>14514970.8</v>
+        <v>13393454.4</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>13502919.4</t>
+          <t>12873199.1</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>19808443.86</v>
+        <v>19258789.6</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>1012051</t>
+          <t>520255</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-656575.0248839555</t>
+          <t>-647828.3673726553</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>156237.9946156964</t>
+          <t>-599721.7510605045</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>11383723.0</t>
+          <t>3202167.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-25.77</t>
+          <t>-25.55</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>42.25</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>2596</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>529.139</t>
+          <t>675.654</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-56.49</t>
+          <t>-57.12</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,66 +2605,66 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>526</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>53.03</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-1.72</v>
+        <v>-2.71</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.22</v>
+        <v>-0.13</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-9.15</t>
+          <t>-8.69</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-4.70</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.32</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>17.36</v>
+        <v>17.34</v>
       </c>
       <c r="BA5" t="n">
-        <v>19.11</v>
+        <v>18.99</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.93</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.4</v>
+        <v>-0.41</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.52</v>
+        <v>-0.5</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-115.04</t>
+          <t>-114.42</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>78141855.041841</t>
+          <t>78051568.73189415</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>9117931.0</t>
+          <t>11383723.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>13515488</v>
+        <v>14514970.8</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>12938015.2</t>
+          <t>13502919.4</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>20517351.2</v>
+        <v>19808443.86</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>577472</t>
+          <t>1012051</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-804359.2102475285</t>
+          <t>-656575.0248839555</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>354005.2743454222</t>
+          <t>156237.9946156964</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>9117931.0</t>
+          <t>11383723.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-24.67</t>
+          <t>-25.77</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,12 +2784,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>42.25</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>2596</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1300.307</t>
+          <t>529.139</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>28.09</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-56.11</t>
+          <t>-56.49</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,66 +3092,66 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>526</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>72.12</t>
+          <t>53.03</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-1.26</v>
+        <v>-1.72</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.63</v>
+        <v>0.22</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-9.72</t>
+          <t>-9.15</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
         <v>17.36</v>
       </c>
       <c r="BA6" t="n">
-        <v>19.23</v>
+        <v>19.11</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>26.74</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="BD6" t="n">
         <v>-0.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.55</v>
+        <v>-0.52</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-115.90</t>
+          <t>-115.04</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>78141855.041841</t>
+          <t>78051568.73189415</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>22480706.0</t>
+          <t>9117931.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>16053050</v>
+        <v>13515488</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>12532414.3</t>
+          <t>12938015.2</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>20840577.04</v>
+        <v>20517351.2</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>3520635</t>
+          <t>577472</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-1014970.934718974</t>
+          <t>-804359.2102475285</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>866650.3427326959</t>
+          <t>354005.2743454222</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>22480706.0</t>
+          <t>9117931.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>-24.01</t>
+          <t>-24.67</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,17 +3271,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>42.25</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>2596</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1165.573</t>
+          <t>1300.307</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.9</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>28.09</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-54.33</t>
+          <t>-56.11</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>12.61</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,66 +3579,66 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>526</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>72.12</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>3.16</v>
+        <v>-1.26</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.2</v>
+        <v>0.63</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-10.26</t>
+          <t>-9.72</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.47</t>
         </is>
       </c>
       <c r="AZ7" t="n">
         <v>17.36</v>
       </c>
       <c r="BA7" t="n">
-        <v>19.35</v>
+        <v>19.23</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>26.74</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.42</v>
+        <v>-0.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.59</v>
+        <v>-0.55</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-116.97</t>
+          <t>-115.90</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>78141855.041841</t>
+          <t>78051568.73189415</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>20782745.0</t>
+          <t>22480706.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>12922100</v>
+        <v>16053050</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>10700242.5</t>
+          <t>12532414.3</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>21416474.36</v>
+        <v>20840577.04</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>2221857</t>
+          <t>3520635</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-1357083.894255641</t>
+          <t>-1014970.934718974</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>136322.7496169191</t>
+          <t>866650.3427326959</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>20782745.0</t>
+          <t>22480706.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-20.93</t>
+          <t>-24.01</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,17 +3758,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>42.25</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>2596</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="CT7" t="inlineStr">
+        <is>
           <t>17.25</t>
-        </is>
-      </c>
-      <c r="CT7" t="inlineStr">
-        <is>
-          <t>17.95</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3860,7 +3860,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>503.465</t>
+          <t>1165.573</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="J